--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="F14" t="n">
-        <v>11.16</v>
+        <v>10.98</v>
       </c>
       <c r="G14" t="n">
-        <v>334.7</v>
+        <v>330.7</v>
       </c>
       <c r="H14" t="n">
-        <v>85.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-185.79</v>
+        <v>-245.52</v>
       </c>
       <c r="K14" t="n">
-        <v>92.20999999999999</v>
+        <v>104.1</v>
       </c>
       <c r="L14" t="n">
-        <v>207.41</v>
+        <v>266.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:08:03</t>
+          <t>08:07:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="F15" t="n">
-        <v>10.22</v>
+        <v>11.14</v>
       </c>
       <c r="G15" t="n">
-        <v>333.9</v>
+        <v>341.7</v>
       </c>
       <c r="H15" t="n">
-        <v>73.7</v>
+        <v>83.7</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>227.51</v>
+        <v>-239.69</v>
       </c>
       <c r="K15" t="n">
-        <v>-81.05</v>
+        <v>-63.85</v>
       </c>
       <c r="L15" t="n">
-        <v>241.52</v>
+        <v>248.05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:09:28</t>
+          <t>08:08:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.22</v>
+        <v>4.21</v>
       </c>
       <c r="F16" t="n">
-        <v>10.37</v>
+        <v>10.8</v>
       </c>
       <c r="G16" t="n">
-        <v>338</v>
+        <v>342.2</v>
       </c>
       <c r="H16" t="n">
-        <v>81.2</v>
+        <v>82.5</v>
       </c>
       <c r="I16" t="n">
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>30.14</v>
+        <v>59.75</v>
       </c>
       <c r="K16" t="n">
-        <v>-44.51</v>
+        <v>-70.28</v>
       </c>
       <c r="L16" t="n">
-        <v>53.76</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:13:24</t>
+          <t>08:13:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.72</v>
+        <v>4.38</v>
       </c>
       <c r="F17" t="n">
-        <v>10.57</v>
+        <v>10.03</v>
       </c>
       <c r="G17" t="n">
-        <v>346.5</v>
+        <v>340.3</v>
       </c>
       <c r="H17" t="n">
-        <v>76.2</v>
+        <v>87.7</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>215.3</v>
+        <v>280.89</v>
       </c>
       <c r="K17" t="n">
-        <v>-79.06999999999999</v>
+        <v>-133.59</v>
       </c>
       <c r="L17" t="n">
-        <v>229.36</v>
+        <v>311.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:15:47</t>
+          <t>08:14:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="F18" t="n">
-        <v>10.08</v>
+        <v>10.21</v>
       </c>
       <c r="G18" t="n">
-        <v>337.4</v>
+        <v>330.9</v>
       </c>
       <c r="H18" t="n">
-        <v>83.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-164.08</v>
+        <v>307.74</v>
       </c>
       <c r="K18" t="n">
-        <v>52.27</v>
+        <v>247.76</v>
       </c>
       <c r="L18" t="n">
-        <v>172.2</v>
+        <v>395.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:17:38</t>
+          <t>08:16:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="F19" t="n">
-        <v>10.81</v>
+        <v>11.01</v>
       </c>
       <c r="G19" t="n">
-        <v>333.4</v>
+        <v>330.9</v>
       </c>
       <c r="H19" t="n">
-        <v>84.8</v>
+        <v>76.2</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>63</v>
+        <v>104.94</v>
       </c>
       <c r="K19" t="n">
-        <v>-38.61</v>
+        <v>266.41</v>
       </c>
       <c r="L19" t="n">
-        <v>73.89</v>
+        <v>286.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:22:11</t>
+          <t>08:22:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="F20" t="n">
-        <v>10.91</v>
+        <v>10.5</v>
       </c>
       <c r="G20" t="n">
-        <v>347.4</v>
+        <v>332.7</v>
       </c>
       <c r="H20" t="n">
-        <v>76.3</v>
+        <v>78.5</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>-383.52</v>
+        <v>24.62</v>
       </c>
       <c r="K20" t="n">
-        <v>-170.75</v>
+        <v>206.34</v>
       </c>
       <c r="L20" t="n">
-        <v>419.81</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:23:42</t>
+          <t>08:24:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.78</v>
+        <v>3.86</v>
       </c>
       <c r="F21" t="n">
-        <v>10.81</v>
+        <v>10.88</v>
       </c>
       <c r="G21" t="n">
-        <v>330.3</v>
+        <v>335.2</v>
       </c>
       <c r="H21" t="n">
-        <v>86.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-156.18</v>
+        <v>326.37</v>
       </c>
       <c r="K21" t="n">
-        <v>486.63</v>
+        <v>86.5</v>
       </c>
       <c r="L21" t="n">
-        <v>511.08</v>
+        <v>337.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:25:46</t>
+          <t>08:26:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.88</v>
+        <v>4.14</v>
       </c>
       <c r="F22" t="n">
-        <v>10.67</v>
+        <v>11.81</v>
       </c>
       <c r="G22" t="n">
-        <v>336.7</v>
+        <v>335.9</v>
       </c>
       <c r="H22" t="n">
-        <v>83.2</v>
+        <v>77.5</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-347.95</v>
+        <v>103.6</v>
       </c>
       <c r="K22" t="n">
-        <v>-150.19</v>
+        <v>217.92</v>
       </c>
       <c r="L22" t="n">
-        <v>378.98</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:29:55</t>
+          <t>08:29:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.15</v>
+        <v>3.44</v>
       </c>
       <c r="F23" t="n">
-        <v>11.08</v>
+        <v>10.74</v>
       </c>
       <c r="G23" t="n">
-        <v>340.8</v>
+        <v>334.6</v>
       </c>
       <c r="H23" t="n">
-        <v>81.7</v>
+        <v>82.3</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>52.8</v>
+        <v>-435.13</v>
       </c>
       <c r="K23" t="n">
-        <v>-659.04</v>
+        <v>258.8</v>
       </c>
       <c r="L23" t="n">
-        <v>661.15</v>
+        <v>506.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:31:20</t>
+          <t>08:31:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.48</v>
+        <v>3.31</v>
       </c>
       <c r="F24" t="n">
-        <v>10.53</v>
+        <v>10.78</v>
       </c>
       <c r="G24" t="n">
-        <v>345.7</v>
+        <v>330.6</v>
       </c>
       <c r="H24" t="n">
-        <v>78.2</v>
+        <v>75.3</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>283.65</v>
+        <v>-412.28</v>
       </c>
       <c r="K24" t="n">
-        <v>-73.38</v>
+        <v>-114.64</v>
       </c>
       <c r="L24" t="n">
-        <v>292.99</v>
+        <v>427.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:33:54</t>
+          <t>08:32:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="F25" t="n">
-        <v>10.57</v>
+        <v>10.92</v>
       </c>
       <c r="G25" t="n">
-        <v>340.8</v>
+        <v>320.7</v>
       </c>
       <c r="H25" t="n">
-        <v>76.8</v>
+        <v>83.7</v>
       </c>
       <c r="I25" t="n">
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>327.9</v>
+        <v>-338.7</v>
       </c>
       <c r="K25" t="n">
-        <v>-256.69</v>
+        <v>42.5</v>
       </c>
       <c r="L25" t="n">
-        <v>416.42</v>
+        <v>341.35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:38:51</t>
+          <t>08:36:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
       <c r="F26" t="n">
-        <v>10.96</v>
+        <v>10.41</v>
       </c>
       <c r="G26" t="n">
-        <v>332.2</v>
+        <v>336.8</v>
       </c>
       <c r="H26" t="n">
-        <v>76.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>621.14</v>
+        <v>423.39</v>
       </c>
       <c r="K26" t="n">
-        <v>764.6900000000001</v>
+        <v>510.66</v>
       </c>
       <c r="L26" t="n">
-        <v>985.17</v>
+        <v>663.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:41:02</t>
+          <t>08:38:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="F27" t="n">
-        <v>11.29</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>344.3</v>
+        <v>329.4</v>
       </c>
       <c r="H27" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-298.29</v>
+        <v>-326.77</v>
       </c>
       <c r="K27" t="n">
-        <v>-221.12</v>
+        <v>114.74</v>
       </c>
       <c r="L27" t="n">
-        <v>371.31</v>
+        <v>346.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:43:09</t>
+          <t>08:40:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="F28" t="n">
-        <v>11.19</v>
+        <v>10.74</v>
       </c>
       <c r="G28" t="n">
-        <v>338.7</v>
+        <v>350</v>
       </c>
       <c r="H28" t="n">
-        <v>83.2</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-628.67</v>
+        <v>-30.35</v>
       </c>
       <c r="K28" t="n">
-        <v>-934.58</v>
+        <v>468.89</v>
       </c>
       <c r="L28" t="n">
-        <v>1126.35</v>
+        <v>469.87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:54:01</t>
+          <t>08:50:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.27</v>
+        <v>3.89</v>
       </c>
       <c r="F29" t="n">
-        <v>11.17</v>
+        <v>10.78</v>
       </c>
       <c r="G29" t="n">
-        <v>326.9</v>
+        <v>333.9</v>
       </c>
       <c r="H29" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="I29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-51.14</v>
+        <v>71.52</v>
       </c>
       <c r="K29" t="n">
-        <v>-124.61</v>
+        <v>-68.59</v>
       </c>
       <c r="L29" t="n">
-        <v>134.69</v>
+        <v>99.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:54:56</t>
+          <t>08:51:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.14</v>
+        <v>4.31</v>
       </c>
       <c r="F30" t="n">
-        <v>10.68</v>
+        <v>11.15</v>
       </c>
       <c r="G30" t="n">
-        <v>351.3</v>
+        <v>355.3</v>
       </c>
       <c r="H30" t="n">
-        <v>78.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-116.37</v>
+        <v>-9.24</v>
       </c>
       <c r="K30" t="n">
-        <v>-18.73</v>
+        <v>-235.95</v>
       </c>
       <c r="L30" t="n">
-        <v>117.87</v>
+        <v>236.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:56:48</t>
+          <t>08:53:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
       <c r="F31" t="n">
-        <v>10.67</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>338.8</v>
+        <v>345.8</v>
       </c>
       <c r="H31" t="n">
-        <v>78.7</v>
+        <v>71.8</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>33.15</v>
+        <v>249.23</v>
       </c>
       <c r="K31" t="n">
-        <v>21.92</v>
+        <v>-85.92</v>
       </c>
       <c r="L31" t="n">
-        <v>39.74</v>
+        <v>263.62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09:01:48</t>
+          <t>08:57:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="F32" t="n">
-        <v>10.68</v>
+        <v>10.65</v>
       </c>
       <c r="G32" t="n">
-        <v>357.2</v>
+        <v>328</v>
       </c>
       <c r="H32" t="n">
-        <v>81.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-23.48</v>
+        <v>-11.98</v>
       </c>
       <c r="K32" t="n">
-        <v>69.33</v>
+        <v>-248.95</v>
       </c>
       <c r="L32" t="n">
-        <v>73.2</v>
+        <v>249.24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:04:00</t>
+          <t>09:00:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.33</v>
+        <v>4.51</v>
       </c>
       <c r="F33" t="n">
-        <v>10.71</v>
+        <v>11.71</v>
       </c>
       <c r="G33" t="n">
-        <v>341.5</v>
+        <v>338.6</v>
       </c>
       <c r="H33" t="n">
-        <v>76.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-210</v>
+        <v>-42.13</v>
       </c>
       <c r="K33" t="n">
-        <v>46.87</v>
+        <v>123.83</v>
       </c>
       <c r="L33" t="n">
-        <v>215.17</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:05:36</t>
+          <t>09:02:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.29</v>
+        <v>4.95</v>
       </c>
       <c r="F34" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="G34" t="n">
-        <v>331.8</v>
+        <v>339.3</v>
       </c>
       <c r="H34" t="n">
-        <v>80.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>91.31</v>
+        <v>190.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-217.56</v>
+        <v>-86.66</v>
       </c>
       <c r="L34" t="n">
-        <v>235.95</v>
+        <v>209.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:10:54</t>
+          <t>09:07:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="F35" t="n">
-        <v>10.98</v>
+        <v>11.18</v>
       </c>
       <c r="G35" t="n">
-        <v>339.2</v>
+        <v>345.2</v>
       </c>
       <c r="H35" t="n">
-        <v>68</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>243.63</v>
+        <v>-122.6</v>
       </c>
       <c r="K35" t="n">
-        <v>-95.48999999999999</v>
+        <v>-347.07</v>
       </c>
       <c r="L35" t="n">
-        <v>261.68</v>
+        <v>368.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:12:38</t>
+          <t>09:09:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.07</v>
+        <v>4.41</v>
       </c>
       <c r="F36" t="n">
-        <v>10.97</v>
+        <v>10.57</v>
       </c>
       <c r="G36" t="n">
-        <v>326.6</v>
+        <v>337.8</v>
       </c>
       <c r="H36" t="n">
-        <v>82.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>256.33</v>
+        <v>-333.62</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.85</v>
+        <v>102.56</v>
       </c>
       <c r="L36" t="n">
-        <v>256.51</v>
+        <v>349.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:14:02</t>
+          <t>09:11:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="F37" t="n">
-        <v>11.24</v>
+        <v>10.79</v>
       </c>
       <c r="G37" t="n">
-        <v>327</v>
+        <v>330.9</v>
       </c>
       <c r="H37" t="n">
-        <v>79.8</v>
+        <v>84.8</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>404.05</v>
+        <v>-149.98</v>
       </c>
       <c r="K37" t="n">
-        <v>-222.94</v>
+        <v>269.94</v>
       </c>
       <c r="L37" t="n">
-        <v>461.48</v>
+        <v>308.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:17:29</t>
+          <t>09:15:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="F38" t="n">
-        <v>10.29</v>
+        <v>10.64</v>
       </c>
       <c r="G38" t="n">
-        <v>335.3</v>
+        <v>331.7</v>
       </c>
       <c r="H38" t="n">
-        <v>81.8</v>
+        <v>73.8</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>12.18</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-591.22</v>
+        <v>-149.22</v>
       </c>
       <c r="L38" t="n">
-        <v>591.34</v>
+        <v>164.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:19:35</t>
+          <t>09:17:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="F39" t="n">
-        <v>10.93</v>
+        <v>11.18</v>
       </c>
       <c r="G39" t="n">
-        <v>333.6</v>
+        <v>334.2</v>
       </c>
       <c r="H39" t="n">
-        <v>84.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>139.31</v>
+        <v>-148.11</v>
       </c>
       <c r="K39" t="n">
-        <v>-250.69</v>
+        <v>-60.94</v>
       </c>
       <c r="L39" t="n">
-        <v>286.8</v>
+        <v>160.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:21:01</t>
+          <t>09:18:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.7</v>
+        <v>4.72</v>
       </c>
       <c r="F40" t="n">
-        <v>11.07</v>
+        <v>11.44</v>
       </c>
       <c r="G40" t="n">
-        <v>338.5</v>
+        <v>345.2</v>
       </c>
       <c r="H40" t="n">
-        <v>82.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I40" t="n">
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-70.98999999999999</v>
+        <v>-320.63</v>
       </c>
       <c r="K40" t="n">
-        <v>94.19</v>
+        <v>351.67</v>
       </c>
       <c r="L40" t="n">
-        <v>117.94</v>
+        <v>475.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:25:33</t>
+          <t>09:23:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="F41" t="n">
-        <v>10.83</v>
+        <v>10.32</v>
       </c>
       <c r="G41" t="n">
-        <v>318.8</v>
+        <v>340.8</v>
       </c>
       <c r="H41" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-369.9</v>
+        <v>162.08</v>
       </c>
       <c r="K41" t="n">
-        <v>-170.07</v>
+        <v>695.96</v>
       </c>
       <c r="L41" t="n">
-        <v>407.12</v>
+        <v>714.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:27:48</t>
+          <t>09:24:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="F42" t="n">
-        <v>10.36</v>
+        <v>11.29</v>
       </c>
       <c r="G42" t="n">
-        <v>353.1</v>
+        <v>339.6</v>
       </c>
       <c r="H42" t="n">
-        <v>86.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-402.31</v>
+        <v>-509.42</v>
       </c>
       <c r="K42" t="n">
-        <v>-217.46</v>
+        <v>402.35</v>
       </c>
       <c r="L42" t="n">
-        <v>457.32</v>
+        <v>649.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:29:46</t>
+          <t>09:25:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.55</v>
+        <v>4.23</v>
       </c>
       <c r="F43" t="n">
-        <v>11.19</v>
+        <v>10.78</v>
       </c>
       <c r="G43" t="n">
-        <v>339.9</v>
+        <v>343.1</v>
       </c>
       <c r="H43" t="n">
-        <v>86.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>74.31999999999999</v>
+        <v>932.3099999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>553.72</v>
+        <v>138.92</v>
       </c>
       <c r="L43" t="n">
-        <v>558.6799999999999</v>
+        <v>942.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:40:45</t>
+          <t>09:37:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.97</v>
+        <v>4.82</v>
       </c>
       <c r="F44" t="n">
-        <v>10.28</v>
+        <v>10.61</v>
       </c>
       <c r="G44" t="n">
-        <v>333.5</v>
+        <v>345</v>
       </c>
       <c r="H44" t="n">
-        <v>80.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-119.51</v>
+        <v>66.95</v>
       </c>
       <c r="K44" t="n">
-        <v>102.86</v>
+        <v>-238.11</v>
       </c>
       <c r="L44" t="n">
-        <v>157.68</v>
+        <v>247.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:41:48</t>
+          <t>09:39:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.15</v>
+        <v>4.72</v>
       </c>
       <c r="F45" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="G45" t="n">
-        <v>338.3</v>
+        <v>333.7</v>
       </c>
       <c r="H45" t="n">
-        <v>82.2</v>
+        <v>78</v>
       </c>
       <c r="I45" t="n">
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>19.05</v>
+        <v>-108.55</v>
       </c>
       <c r="K45" t="n">
-        <v>104.86</v>
+        <v>136.33</v>
       </c>
       <c r="L45" t="n">
-        <v>106.57</v>
+        <v>174.27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:42:55</t>
+          <t>09:41:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.98</v>
+        <v>4.11</v>
       </c>
       <c r="F46" t="n">
-        <v>11.29</v>
+        <v>10.33</v>
       </c>
       <c r="G46" t="n">
-        <v>325.7</v>
+        <v>338.8</v>
       </c>
       <c r="H46" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>11.8</v>
+        <v>-47.29</v>
       </c>
       <c r="K46" t="n">
-        <v>-99.2</v>
+        <v>95.86</v>
       </c>
       <c r="L46" t="n">
-        <v>99.90000000000001</v>
+        <v>106.89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:46:41</t>
+          <t>09:45:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.74</v>
+        <v>4.32</v>
       </c>
       <c r="F47" t="n">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="G47" t="n">
-        <v>331.7</v>
+        <v>341</v>
       </c>
       <c r="H47" t="n">
-        <v>77.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>129.49</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-188.87</v>
+        <v>-240.1</v>
       </c>
       <c r="L47" t="n">
-        <v>229</v>
+        <v>240.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:48:58</t>
+          <t>09:47:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="F48" t="n">
-        <v>11.32</v>
+        <v>10.68</v>
       </c>
       <c r="G48" t="n">
-        <v>329.9</v>
+        <v>343.8</v>
       </c>
       <c r="H48" t="n">
-        <v>75.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>124.29</v>
+        <v>-17.78</v>
       </c>
       <c r="K48" t="n">
-        <v>-21.36</v>
+        <v>158.64</v>
       </c>
       <c r="L48" t="n">
-        <v>126.11</v>
+        <v>159.63</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:49:27</t>
+          <t>09:49:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.23</v>
+        <v>4.53</v>
       </c>
       <c r="F49" t="n">
-        <v>10.86</v>
+        <v>11.32</v>
       </c>
       <c r="G49" t="n">
-        <v>330.9</v>
+        <v>342.9</v>
       </c>
       <c r="H49" t="n">
-        <v>83.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-189.45</v>
+        <v>270.77</v>
       </c>
       <c r="K49" t="n">
-        <v>350.66</v>
+        <v>37.25</v>
       </c>
       <c r="L49" t="n">
-        <v>398.56</v>
+        <v>273.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:54:40</t>
+          <t>09:55:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.56</v>
+        <v>4.05</v>
       </c>
       <c r="F50" t="n">
-        <v>10.48</v>
+        <v>11.3</v>
       </c>
       <c r="G50" t="n">
-        <v>332.1</v>
+        <v>322.7</v>
       </c>
       <c r="H50" t="n">
-        <v>80.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-57.91</v>
+        <v>444.47</v>
       </c>
       <c r="K50" t="n">
-        <v>-328.17</v>
+        <v>2.08</v>
       </c>
       <c r="L50" t="n">
-        <v>333.24</v>
+        <v>444.48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:56:52</t>
+          <t>09:57:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.95</v>
+        <v>4.63</v>
       </c>
       <c r="F51" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="G51" t="n">
-        <v>342.4</v>
+        <v>332</v>
       </c>
       <c r="H51" t="n">
-        <v>82.2</v>
+        <v>79.2</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>330.47</v>
+        <v>-153.91</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.52</v>
+        <v>-290.84</v>
       </c>
       <c r="L51" t="n">
-        <v>330.48</v>
+        <v>329.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:57:56</t>
+          <t>09:58:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.59</v>
+        <v>4.32</v>
       </c>
       <c r="F52" t="n">
-        <v>9.960000000000001</v>
+        <v>11.26</v>
       </c>
       <c r="G52" t="n">
-        <v>337.9</v>
+        <v>336.3</v>
       </c>
       <c r="H52" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>-90.45</v>
+        <v>425.71</v>
       </c>
       <c r="K52" t="n">
-        <v>106.68</v>
+        <v>-129.96</v>
       </c>
       <c r="L52" t="n">
-        <v>139.86</v>
+        <v>445.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:02:51</t>
+          <t>10:03:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.11</v>
+        <v>4.48</v>
       </c>
       <c r="F53" t="n">
-        <v>11.1</v>
+        <v>10.39</v>
       </c>
       <c r="G53" t="n">
-        <v>342.8</v>
+        <v>332</v>
       </c>
       <c r="H53" t="n">
-        <v>77.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>178.27</v>
+        <v>633.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-343.17</v>
+        <v>-82.87</v>
       </c>
       <c r="L53" t="n">
-        <v>386.71</v>
+        <v>638.61</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:04:37</t>
+          <t>10:06:33</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.49</v>
+        <v>4.54</v>
       </c>
       <c r="F54" t="n">
-        <v>10.72</v>
+        <v>10.57</v>
       </c>
       <c r="G54" t="n">
-        <v>328.1</v>
+        <v>337.8</v>
       </c>
       <c r="H54" t="n">
-        <v>80.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-165.34</v>
+        <v>-489.51</v>
       </c>
       <c r="K54" t="n">
-        <v>-89.17</v>
+        <v>25.93</v>
       </c>
       <c r="L54" t="n">
-        <v>187.85</v>
+        <v>490.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:05:42</t>
+          <t>10:08:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.7</v>
+        <v>4.97</v>
       </c>
       <c r="F55" t="n">
-        <v>10.75</v>
+        <v>9.94</v>
       </c>
       <c r="G55" t="n">
-        <v>331</v>
+        <v>331.2</v>
       </c>
       <c r="H55" t="n">
-        <v>75.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>20.1</v>
+        <v>272.78</v>
       </c>
       <c r="K55" t="n">
-        <v>-431.74</v>
+        <v>-301.48</v>
       </c>
       <c r="L55" t="n">
-        <v>432.2</v>
+        <v>406.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:11:27</t>
+          <t>10:13:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.51</v>
+        <v>4.55</v>
       </c>
       <c r="F56" t="n">
-        <v>10.46</v>
+        <v>9.82</v>
       </c>
       <c r="G56" t="n">
-        <v>353.6</v>
+        <v>334.4</v>
       </c>
       <c r="H56" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-104.68</v>
+        <v>257.72</v>
       </c>
       <c r="K56" t="n">
-        <v>136.69</v>
+        <v>885.92</v>
       </c>
       <c r="L56" t="n">
-        <v>172.17</v>
+        <v>922.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:12:18</t>
+          <t>10:14:20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.18</v>
+        <v>4.44</v>
       </c>
       <c r="F57" t="n">
-        <v>10.82</v>
+        <v>10.65</v>
       </c>
       <c r="G57" t="n">
-        <v>338</v>
+        <v>327.8</v>
       </c>
       <c r="H57" t="n">
-        <v>85.7</v>
+        <v>82.2</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-156.74</v>
+        <v>-81.58</v>
       </c>
       <c r="K57" t="n">
-        <v>-536.41</v>
+        <v>427.57</v>
       </c>
       <c r="L57" t="n">
-        <v>558.85</v>
+        <v>435.28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:13:49</t>
+          <t>10:15:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.91</v>
+        <v>3.92</v>
       </c>
       <c r="F58" t="n">
-        <v>11.11</v>
+        <v>10.83</v>
       </c>
       <c r="G58" t="n">
-        <v>339</v>
+        <v>335.3</v>
       </c>
       <c r="H58" t="n">
-        <v>74.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-8.58</v>
+        <v>945.72</v>
       </c>
       <c r="K58" t="n">
-        <v>177.83</v>
+        <v>-223.29</v>
       </c>
       <c r="L58" t="n">
-        <v>178.04</v>
+        <v>971.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:21:41</t>
+          <t>10:26:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.18</v>
+        <v>4.4</v>
       </c>
       <c r="F59" t="n">
-        <v>10.91</v>
+        <v>11.53</v>
       </c>
       <c r="G59" t="n">
-        <v>331.4</v>
+        <v>334</v>
       </c>
       <c r="H59" t="n">
-        <v>77.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-31.11</v>
+        <v>137.26</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.63</v>
+        <v>200.52</v>
       </c>
       <c r="L59" t="n">
-        <v>49.6</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:23:13</t>
+          <t>10:29:06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="F60" t="n">
-        <v>10.57</v>
+        <v>10.26</v>
       </c>
       <c r="G60" t="n">
-        <v>342.1</v>
+        <v>344.2</v>
       </c>
       <c r="H60" t="n">
-        <v>75.2</v>
+        <v>69.7</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>78.11</v>
+        <v>101.32</v>
       </c>
       <c r="K60" t="n">
-        <v>4.99</v>
+        <v>155.87</v>
       </c>
       <c r="L60" t="n">
-        <v>78.27</v>
+        <v>185.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:24:27</t>
+          <t>10:31:08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="F61" t="n">
-        <v>11.24</v>
+        <v>10.62</v>
       </c>
       <c r="G61" t="n">
-        <v>335.3</v>
+        <v>328.7</v>
       </c>
       <c r="H61" t="n">
-        <v>78.7</v>
+        <v>80.3</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>7.01</v>
+        <v>-118.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-192.68</v>
+        <v>-250.4</v>
       </c>
       <c r="L61" t="n">
-        <v>192.81</v>
+        <v>276.84</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:29:31</t>
+          <t>10:36:03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.5</v>
+        <v>4.11</v>
       </c>
       <c r="F62" t="n">
-        <v>10.49</v>
+        <v>10.84</v>
       </c>
       <c r="G62" t="n">
-        <v>331.1</v>
+        <v>335.1</v>
       </c>
       <c r="H62" t="n">
-        <v>85</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-350.34</v>
+        <v>49.37</v>
       </c>
       <c r="K62" t="n">
-        <v>-175.63</v>
+        <v>-17.55</v>
       </c>
       <c r="L62" t="n">
-        <v>391.89</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:31:35</t>
+          <t>10:37:32</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.51</v>
+        <v>4.15</v>
       </c>
       <c r="F63" t="n">
-        <v>10.07</v>
+        <v>10.84</v>
       </c>
       <c r="G63" t="n">
-        <v>334</v>
+        <v>338.2</v>
       </c>
       <c r="H63" t="n">
-        <v>84</v>
+        <v>76.7</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>204.27</v>
+        <v>163.81</v>
       </c>
       <c r="K63" t="n">
-        <v>73.75</v>
+        <v>74.72</v>
       </c>
       <c r="L63" t="n">
-        <v>217.18</v>
+        <v>180.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:33:11</t>
+          <t>10:39:29</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.58</v>
+        <v>4.47</v>
       </c>
       <c r="F64" t="n">
-        <v>10.35</v>
+        <v>10.54</v>
       </c>
       <c r="G64" t="n">
-        <v>332.1</v>
+        <v>324.1</v>
       </c>
       <c r="H64" t="n">
-        <v>84</v>
+        <v>84.7</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>6.67</v>
+        <v>-177.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-12.45</v>
+        <v>19.38</v>
       </c>
       <c r="L64" t="n">
-        <v>14.13</v>
+        <v>178.36</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:37:05</t>
+          <t>10:44:03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.42</v>
+        <v>4.99</v>
       </c>
       <c r="F65" t="n">
-        <v>11.25</v>
+        <v>10.38</v>
       </c>
       <c r="G65" t="n">
-        <v>338.3</v>
+        <v>337.8</v>
       </c>
       <c r="H65" t="n">
-        <v>80.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>88.66</v>
+        <v>-136.74</v>
       </c>
       <c r="K65" t="n">
-        <v>122.48</v>
+        <v>-111.91</v>
       </c>
       <c r="L65" t="n">
-        <v>151.21</v>
+        <v>176.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:39:28</t>
+          <t>10:46:01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.84</v>
+        <v>5.08</v>
       </c>
       <c r="F66" t="n">
-        <v>10.93</v>
+        <v>10.64</v>
       </c>
       <c r="G66" t="n">
-        <v>332.9</v>
+        <v>339.7</v>
       </c>
       <c r="H66" t="n">
-        <v>75</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-145.73</v>
+        <v>561.65</v>
       </c>
       <c r="K66" t="n">
-        <v>-375.59</v>
+        <v>30.11</v>
       </c>
       <c r="L66" t="n">
-        <v>402.88</v>
+        <v>562.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:40:50</t>
+          <t>10:47:52</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.59</v>
+        <v>3.8</v>
       </c>
       <c r="F67" t="n">
-        <v>10.69</v>
+        <v>9.68</v>
       </c>
       <c r="G67" t="n">
-        <v>342.3</v>
+        <v>345</v>
       </c>
       <c r="H67" t="n">
-        <v>81</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>177.79</v>
+        <v>-76.98999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-352.24</v>
+        <v>224.25</v>
       </c>
       <c r="L67" t="n">
-        <v>394.57</v>
+        <v>237.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:45:01</t>
+          <t>10:51:39</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.15</v>
+        <v>5.36</v>
       </c>
       <c r="F68" t="n">
-        <v>11.01</v>
+        <v>10.7</v>
       </c>
       <c r="G68" t="n">
-        <v>323.7</v>
+        <v>359.6</v>
       </c>
       <c r="H68" t="n">
-        <v>84.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>395.66</v>
+        <v>-447.38</v>
       </c>
       <c r="K68" t="n">
-        <v>30.77</v>
+        <v>779.05</v>
       </c>
       <c r="L68" t="n">
-        <v>396.85</v>
+        <v>898.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:46:06</t>
+          <t>10:53:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.08</v>
+        <v>4.36</v>
       </c>
       <c r="F69" t="n">
-        <v>11.13</v>
+        <v>10.8</v>
       </c>
       <c r="G69" t="n">
-        <v>349</v>
+        <v>334.1</v>
       </c>
       <c r="H69" t="n">
-        <v>85.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-350.56</v>
+        <v>638.16</v>
       </c>
       <c r="K69" t="n">
-        <v>-31.31</v>
+        <v>-8.75</v>
       </c>
       <c r="L69" t="n">
-        <v>351.96</v>
+        <v>638.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:47:58</t>
+          <t>10:55:21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.06</v>
+        <v>4.45</v>
       </c>
       <c r="F70" t="n">
-        <v>10.23</v>
+        <v>11.15</v>
       </c>
       <c r="G70" t="n">
-        <v>319.7</v>
+        <v>338.6</v>
       </c>
       <c r="H70" t="n">
-        <v>78.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-134.59</v>
+        <v>715.8</v>
       </c>
       <c r="K70" t="n">
-        <v>-247.04</v>
+        <v>-31.56</v>
       </c>
       <c r="L70" t="n">
-        <v>281.32</v>
+        <v>716.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:53:35</t>
+          <t>10:59:48</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="F71" t="n">
-        <v>10.77</v>
+        <v>10.91</v>
       </c>
       <c r="G71" t="n">
-        <v>323.6</v>
+        <v>349.9</v>
       </c>
       <c r="H71" t="n">
-        <v>77.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-427.54</v>
+        <v>84.94</v>
       </c>
       <c r="K71" t="n">
-        <v>496.95</v>
+        <v>447.97</v>
       </c>
       <c r="L71" t="n">
-        <v>655.5599999999999</v>
+        <v>455.96</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:55:03</t>
+          <t>11:01:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.48</v>
+        <v>4.8</v>
       </c>
       <c r="F72" t="n">
-        <v>9.76</v>
+        <v>10.81</v>
       </c>
       <c r="G72" t="n">
-        <v>345</v>
+        <v>334.5</v>
       </c>
       <c r="H72" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>462.72</v>
+        <v>162.67</v>
       </c>
       <c r="K72" t="n">
-        <v>-306.06</v>
+        <v>299.47</v>
       </c>
       <c r="L72" t="n">
-        <v>554.78</v>
+        <v>340.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:56:45</t>
+          <t>11:01:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.28</v>
+        <v>4.69</v>
       </c>
       <c r="F73" t="n">
-        <v>10.76</v>
+        <v>10.65</v>
       </c>
       <c r="G73" t="n">
-        <v>338.5</v>
+        <v>324.2</v>
       </c>
       <c r="H73" t="n">
-        <v>76.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-63.8</v>
+        <v>-16.6</v>
       </c>
       <c r="K73" t="n">
-        <v>-114.11</v>
+        <v>-248.57</v>
       </c>
       <c r="L73" t="n">
-        <v>130.73</v>
+        <v>249.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:05:17</t>
+          <t>11:13:32</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.55</v>
+        <v>3.95</v>
       </c>
       <c r="F74" t="n">
-        <v>10.65</v>
+        <v>10.49</v>
       </c>
       <c r="G74" t="n">
-        <v>330.1</v>
+        <v>349.2</v>
       </c>
       <c r="H74" t="n">
-        <v>81.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-169.36</v>
+        <v>-156.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-299.6</v>
+        <v>27.6</v>
       </c>
       <c r="L74" t="n">
-        <v>344.15</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:07:23</t>
+          <t>11:15:36</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.43</v>
+        <v>4.28</v>
       </c>
       <c r="F75" t="n">
-        <v>10.97</v>
+        <v>10.69</v>
       </c>
       <c r="G75" t="n">
-        <v>342.1</v>
+        <v>341.2</v>
       </c>
       <c r="H75" t="n">
-        <v>87.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>97.78</v>
+        <v>194.61</v>
       </c>
       <c r="K75" t="n">
-        <v>19.93</v>
+        <v>100.71</v>
       </c>
       <c r="L75" t="n">
-        <v>99.79000000000001</v>
+        <v>219.13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:09:12</t>
+          <t>11:16:53</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.63</v>
+        <v>4.71</v>
       </c>
       <c r="F76" t="n">
-        <v>10.29</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>338.9</v>
+        <v>334.3</v>
       </c>
       <c r="H76" t="n">
-        <v>86.5</v>
+        <v>88.3</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.88</v>
+        <v>-161.15</v>
       </c>
       <c r="K76" t="n">
-        <v>-107.7</v>
+        <v>-132.06</v>
       </c>
       <c r="L76" t="n">
-        <v>107.74</v>
+        <v>208.35</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:12:48</t>
+          <t>11:22:05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.68</v>
+        <v>4.9</v>
       </c>
       <c r="F77" t="n">
-        <v>11.32</v>
+        <v>10.91</v>
       </c>
       <c r="G77" t="n">
-        <v>345.5</v>
+        <v>345.6</v>
       </c>
       <c r="H77" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>79.53</v>
+        <v>161.77</v>
       </c>
       <c r="K77" t="n">
-        <v>14.3</v>
+        <v>-56.62</v>
       </c>
       <c r="L77" t="n">
-        <v>80.81</v>
+        <v>171.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:14:16</t>
+          <t>11:23:28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.52</v>
+        <v>5.12</v>
       </c>
       <c r="F78" t="n">
-        <v>10.38</v>
+        <v>10.65</v>
       </c>
       <c r="G78" t="n">
-        <v>350.3</v>
+        <v>343.4</v>
       </c>
       <c r="H78" t="n">
-        <v>79.7</v>
+        <v>83.8</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-40.58</v>
+        <v>-32.37</v>
       </c>
       <c r="K78" t="n">
-        <v>207.14</v>
+        <v>-171.77</v>
       </c>
       <c r="L78" t="n">
-        <v>211.08</v>
+        <v>174.79</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:16:08</t>
+          <t>11:24:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3358,31 +3358,31 @@
         <v>3.94</v>
       </c>
       <c r="F79" t="n">
-        <v>10.51</v>
+        <v>10.59</v>
       </c>
       <c r="G79" t="n">
-        <v>330.1</v>
+        <v>344</v>
       </c>
       <c r="H79" t="n">
-        <v>77.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I79" t="n">
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>15.77</v>
+        <v>-33.38</v>
       </c>
       <c r="K79" t="n">
-        <v>146.48</v>
+        <v>-160.39</v>
       </c>
       <c r="L79" t="n">
-        <v>147.33</v>
+        <v>163.82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:20:19</t>
+          <t>11:30:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.19</v>
+        <v>3.96</v>
       </c>
       <c r="F80" t="n">
-        <v>11.27</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>345.4</v>
+        <v>352.5</v>
       </c>
       <c r="H80" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>144.63</v>
+        <v>-329.22</v>
       </c>
       <c r="K80" t="n">
-        <v>292.2</v>
+        <v>-15.1</v>
       </c>
       <c r="L80" t="n">
-        <v>326.03</v>
+        <v>329.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:21:07</t>
+          <t>11:32:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="F81" t="n">
-        <v>10.64</v>
+        <v>10.54</v>
       </c>
       <c r="G81" t="n">
-        <v>336.7</v>
+        <v>353.1</v>
       </c>
       <c r="H81" t="n">
-        <v>82.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>12.2</v>
+        <v>-534.35</v>
       </c>
       <c r="K81" t="n">
-        <v>1.56</v>
+        <v>-172.98</v>
       </c>
       <c r="L81" t="n">
-        <v>12.3</v>
+        <v>561.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:22:44</t>
+          <t>11:34:17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.51</v>
+        <v>4.76</v>
       </c>
       <c r="F82" t="n">
-        <v>10.63</v>
+        <v>11.58</v>
       </c>
       <c r="G82" t="n">
-        <v>340.2</v>
+        <v>333.6</v>
       </c>
       <c r="H82" t="n">
-        <v>81.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>96.27</v>
+        <v>-262.82</v>
       </c>
       <c r="K82" t="n">
-        <v>59.75</v>
+        <v>440.48</v>
       </c>
       <c r="L82" t="n">
-        <v>113.3</v>
+        <v>512.92</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:28:32</t>
+          <t>11:39:03</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.32</v>
+        <v>4.99</v>
       </c>
       <c r="F83" t="n">
-        <v>11.07</v>
+        <v>10.09</v>
       </c>
       <c r="G83" t="n">
-        <v>336.4</v>
+        <v>338.3</v>
       </c>
       <c r="H83" t="n">
-        <v>87.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>166.56</v>
+        <v>208.48</v>
       </c>
       <c r="K83" t="n">
-        <v>-488.13</v>
+        <v>444.05</v>
       </c>
       <c r="L83" t="n">
-        <v>515.77</v>
+        <v>490.56</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:30:29</t>
+          <t>11:39:45</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="F84" t="n">
-        <v>11.45</v>
+        <v>10.97</v>
       </c>
       <c r="G84" t="n">
-        <v>351.6</v>
+        <v>345.3</v>
       </c>
       <c r="H84" t="n">
-        <v>85.7</v>
+        <v>77</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-317.61</v>
+        <v>180.62</v>
       </c>
       <c r="K84" t="n">
-        <v>779.95</v>
+        <v>466.39</v>
       </c>
       <c r="L84" t="n">
-        <v>842.14</v>
+        <v>500.14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:32:12</t>
+          <t>11:40:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.63</v>
+        <v>4.73</v>
       </c>
       <c r="F85" t="n">
-        <v>10.73</v>
+        <v>10.3</v>
       </c>
       <c r="G85" t="n">
-        <v>319.9</v>
+        <v>331</v>
       </c>
       <c r="H85" t="n">
-        <v>76.2</v>
+        <v>82.8</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>171.95</v>
+        <v>226.7</v>
       </c>
       <c r="K85" t="n">
-        <v>282.29</v>
+        <v>706.67</v>
       </c>
       <c r="L85" t="n">
-        <v>330.54</v>
+        <v>742.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:38:11</t>
+          <t>11:45:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.2</v>
+        <v>4.93</v>
       </c>
       <c r="F86" t="n">
-        <v>11.11</v>
+        <v>9.9</v>
       </c>
       <c r="G86" t="n">
-        <v>341.7</v>
+        <v>346</v>
       </c>
       <c r="H86" t="n">
-        <v>79</v>
+        <v>88.8</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>344.89</v>
+        <v>-249.82</v>
       </c>
       <c r="K86" t="n">
-        <v>-572.17</v>
+        <v>487.4</v>
       </c>
       <c r="L86" t="n">
-        <v>668.0700000000001</v>
+        <v>547.6900000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:40:09</t>
+          <t>11:47:58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.29</v>
+        <v>3.9</v>
       </c>
       <c r="F87" t="n">
-        <v>10.68</v>
+        <v>11.05</v>
       </c>
       <c r="G87" t="n">
-        <v>338.3</v>
+        <v>343.6</v>
       </c>
       <c r="H87" t="n">
-        <v>79.3</v>
+        <v>69.3</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-122.09</v>
+        <v>-438.73</v>
       </c>
       <c r="K87" t="n">
-        <v>-18.39</v>
+        <v>-246.38</v>
       </c>
       <c r="L87" t="n">
-        <v>123.47</v>
+        <v>503.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:42:18</t>
+          <t>11:49:26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.69</v>
+        <v>3.8</v>
       </c>
       <c r="F88" t="n">
-        <v>10.27</v>
+        <v>11.09</v>
       </c>
       <c r="G88" t="n">
-        <v>330.2</v>
+        <v>327.8</v>
       </c>
       <c r="H88" t="n">
-        <v>74.8</v>
+        <v>81.5</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>361.62</v>
+        <v>80.94</v>
       </c>
       <c r="K88" t="n">
-        <v>137.85</v>
+        <v>-123.03</v>
       </c>
       <c r="L88" t="n">
-        <v>387</v>
+        <v>147.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-245.52</v>
+        <v>-216.43</v>
       </c>
       <c r="K14" t="n">
-        <v>104.1</v>
+        <v>91.77</v>
       </c>
       <c r="L14" t="n">
-        <v>266.68</v>
+        <v>235.08</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-239.69</v>
+        <v>-255.93</v>
       </c>
       <c r="K15" t="n">
-        <v>-63.85</v>
+        <v>-68.17</v>
       </c>
       <c r="L15" t="n">
-        <v>248.05</v>
+        <v>264.85</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>59.75</v>
+        <v>99.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-70.28</v>
+        <v>-116.75</v>
       </c>
       <c r="L16" t="n">
-        <v>92.25</v>
+        <v>153.23</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>280.89</v>
+        <v>314.25</v>
       </c>
       <c r="K17" t="n">
-        <v>-133.59</v>
+        <v>-149.46</v>
       </c>
       <c r="L17" t="n">
-        <v>311.04</v>
+        <v>347.98</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>307.74</v>
+        <v>280.07</v>
       </c>
       <c r="K18" t="n">
-        <v>247.76</v>
+        <v>225.48</v>
       </c>
       <c r="L18" t="n">
-        <v>395.08</v>
+        <v>359.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>104.94</v>
+        <v>112.69</v>
       </c>
       <c r="K19" t="n">
-        <v>266.41</v>
+        <v>286.06</v>
       </c>
       <c r="L19" t="n">
-        <v>286.33</v>
+        <v>307.46</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>24.62</v>
+        <v>28.47</v>
       </c>
       <c r="K20" t="n">
-        <v>206.34</v>
+        <v>238.69</v>
       </c>
       <c r="L20" t="n">
-        <v>207.8</v>
+        <v>240.39</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>326.37</v>
+        <v>400.94</v>
       </c>
       <c r="K21" t="n">
-        <v>86.5</v>
+        <v>106.26</v>
       </c>
       <c r="L21" t="n">
-        <v>337.64</v>
+        <v>414.78</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>103.6</v>
+        <v>126.21</v>
       </c>
       <c r="K22" t="n">
-        <v>217.92</v>
+        <v>265.48</v>
       </c>
       <c r="L22" t="n">
-        <v>241.3</v>
+        <v>293.95</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-435.13</v>
+        <v>-489.74</v>
       </c>
       <c r="K23" t="n">
-        <v>258.8</v>
+        <v>291.28</v>
       </c>
       <c r="L23" t="n">
-        <v>506.28</v>
+        <v>569.8200000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-412.28</v>
+        <v>-475.26</v>
       </c>
       <c r="K24" t="n">
-        <v>-114.64</v>
+        <v>-132.15</v>
       </c>
       <c r="L24" t="n">
-        <v>427.92</v>
+        <v>493.29</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-338.7</v>
+        <v>-420.46</v>
       </c>
       <c r="K25" t="n">
-        <v>42.5</v>
+        <v>52.76</v>
       </c>
       <c r="L25" t="n">
-        <v>341.35</v>
+        <v>423.76</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>423.39</v>
+        <v>578.9299999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>510.66</v>
+        <v>698.26</v>
       </c>
       <c r="L26" t="n">
-        <v>663.35</v>
+        <v>907.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-326.77</v>
+        <v>-486.37</v>
       </c>
       <c r="K27" t="n">
-        <v>114.74</v>
+        <v>170.79</v>
       </c>
       <c r="L27" t="n">
-        <v>346.33</v>
+        <v>515.48</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-30.35</v>
+        <v>-38.46</v>
       </c>
       <c r="K28" t="n">
-        <v>468.89</v>
+        <v>594.14</v>
       </c>
       <c r="L28" t="n">
-        <v>469.87</v>
+        <v>595.39</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>71.52</v>
+        <v>105.89</v>
       </c>
       <c r="K29" t="n">
-        <v>-68.59</v>
+        <v>-101.55</v>
       </c>
       <c r="L29" t="n">
-        <v>99.09</v>
+        <v>146.71</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.24</v>
+        <v>-10.49</v>
       </c>
       <c r="K30" t="n">
-        <v>-235.95</v>
+        <v>-267.96</v>
       </c>
       <c r="L30" t="n">
-        <v>236.13</v>
+        <v>268.17</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>249.23</v>
+        <v>226.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-85.92</v>
+        <v>-77.98</v>
       </c>
       <c r="L31" t="n">
-        <v>263.62</v>
+        <v>239.27</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-11.98</v>
+        <v>-13.47</v>
       </c>
       <c r="K32" t="n">
-        <v>-248.95</v>
+        <v>-279.95</v>
       </c>
       <c r="L32" t="n">
-        <v>249.24</v>
+        <v>280.28</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.13</v>
+        <v>-63.88</v>
       </c>
       <c r="K33" t="n">
-        <v>123.83</v>
+        <v>187.78</v>
       </c>
       <c r="L33" t="n">
-        <v>130.8</v>
+        <v>198.35</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>190.67</v>
+        <v>215.37</v>
       </c>
       <c r="K34" t="n">
-        <v>-86.66</v>
+        <v>-97.89</v>
       </c>
       <c r="L34" t="n">
-        <v>209.44</v>
+        <v>236.57</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-122.6</v>
+        <v>-143.66</v>
       </c>
       <c r="K35" t="n">
-        <v>-347.07</v>
+        <v>-406.67</v>
       </c>
       <c r="L35" t="n">
-        <v>368.09</v>
+        <v>431.3</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-333.62</v>
+        <v>-420.74</v>
       </c>
       <c r="K36" t="n">
-        <v>102.56</v>
+        <v>129.34</v>
       </c>
       <c r="L36" t="n">
-        <v>349.02</v>
+        <v>440.17</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-149.98</v>
+        <v>-190.26</v>
       </c>
       <c r="K37" t="n">
-        <v>269.94</v>
+        <v>342.43</v>
       </c>
       <c r="L37" t="n">
-        <v>308.8</v>
+        <v>391.74</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-68.09999999999999</v>
+        <v>-121.88</v>
       </c>
       <c r="K38" t="n">
-        <v>-149.22</v>
+        <v>-267.06</v>
       </c>
       <c r="L38" t="n">
-        <v>164.02</v>
+        <v>293.56</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-148.11</v>
+        <v>-281.19</v>
       </c>
       <c r="K39" t="n">
-        <v>-60.94</v>
+        <v>-115.69</v>
       </c>
       <c r="L39" t="n">
-        <v>160.16</v>
+        <v>304.06</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-320.63</v>
+        <v>-450.89</v>
       </c>
       <c r="K40" t="n">
-        <v>351.67</v>
+        <v>494.54</v>
       </c>
       <c r="L40" t="n">
-        <v>475.89</v>
+        <v>669.23</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>162.08</v>
+        <v>236.83</v>
       </c>
       <c r="K41" t="n">
-        <v>695.96</v>
+        <v>1016.95</v>
       </c>
       <c r="L41" t="n">
-        <v>714.58</v>
+        <v>1044.16</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-509.42</v>
+        <v>-618.46</v>
       </c>
       <c r="K42" t="n">
-        <v>402.35</v>
+        <v>488.47</v>
       </c>
       <c r="L42" t="n">
-        <v>649.15</v>
+        <v>788.1</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>932.3099999999999</v>
+        <v>967.76</v>
       </c>
       <c r="K43" t="n">
-        <v>138.92</v>
+        <v>144.21</v>
       </c>
       <c r="L43" t="n">
-        <v>942.61</v>
+        <v>978.45</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>66.95</v>
+        <v>66.3</v>
       </c>
       <c r="K44" t="n">
-        <v>-238.11</v>
+        <v>-235.78</v>
       </c>
       <c r="L44" t="n">
-        <v>247.34</v>
+        <v>244.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-108.55</v>
+        <v>-138.17</v>
       </c>
       <c r="K45" t="n">
-        <v>136.33</v>
+        <v>173.53</v>
       </c>
       <c r="L45" t="n">
-        <v>174.27</v>
+        <v>221.82</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-47.29</v>
+        <v>-69.70999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>95.86</v>
+        <v>141.29</v>
       </c>
       <c r="L46" t="n">
-        <v>106.89</v>
+        <v>157.55</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>9.130000000000001</v>
+        <v>11.01</v>
       </c>
       <c r="K47" t="n">
-        <v>-240.1</v>
+        <v>-289.33</v>
       </c>
       <c r="L47" t="n">
-        <v>240.28</v>
+        <v>289.54</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-17.78</v>
+        <v>-22.72</v>
       </c>
       <c r="K48" t="n">
-        <v>158.64</v>
+        <v>202.79</v>
       </c>
       <c r="L48" t="n">
-        <v>159.63</v>
+        <v>204.05</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>270.77</v>
+        <v>292.31</v>
       </c>
       <c r="K49" t="n">
-        <v>37.25</v>
+        <v>40.21</v>
       </c>
       <c r="L49" t="n">
-        <v>273.32</v>
+        <v>295.06</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>444.47</v>
+        <v>517.04</v>
       </c>
       <c r="K50" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="L50" t="n">
-        <v>444.48</v>
+        <v>517.05</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-153.91</v>
+        <v>-192.49</v>
       </c>
       <c r="K51" t="n">
-        <v>-290.84</v>
+        <v>-363.77</v>
       </c>
       <c r="L51" t="n">
-        <v>329.05</v>
+        <v>411.56</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>425.71</v>
+        <v>453.27</v>
       </c>
       <c r="K52" t="n">
-        <v>-129.96</v>
+        <v>-138.38</v>
       </c>
       <c r="L52" t="n">
-        <v>445.1</v>
+        <v>473.93</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>633.21</v>
+        <v>822.51</v>
       </c>
       <c r="K53" t="n">
-        <v>-82.87</v>
+        <v>-107.65</v>
       </c>
       <c r="L53" t="n">
-        <v>638.61</v>
+        <v>829.53</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-489.51</v>
+        <v>-590.67</v>
       </c>
       <c r="K54" t="n">
-        <v>25.93</v>
+        <v>31.29</v>
       </c>
       <c r="L54" t="n">
-        <v>490.2</v>
+        <v>591.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>272.78</v>
+        <v>352.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-301.48</v>
+        <v>-389.8</v>
       </c>
       <c r="L55" t="n">
-        <v>406.57</v>
+        <v>525.6799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>257.72</v>
+        <v>278.02</v>
       </c>
       <c r="K56" t="n">
-        <v>885.92</v>
+        <v>955.6900000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>922.65</v>
+        <v>995.3099999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-81.58</v>
+        <v>-117.95</v>
       </c>
       <c r="K57" t="n">
-        <v>427.57</v>
+        <v>618.2</v>
       </c>
       <c r="L57" t="n">
-        <v>435.28</v>
+        <v>629.36</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>945.72</v>
+        <v>1110.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-223.29</v>
+        <v>-262.09</v>
       </c>
       <c r="L58" t="n">
-        <v>971.72</v>
+        <v>1140.56</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>137.26</v>
+        <v>134.17</v>
       </c>
       <c r="K59" t="n">
-        <v>200.52</v>
+        <v>196</v>
       </c>
       <c r="L59" t="n">
-        <v>243</v>
+        <v>237.53</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>101.32</v>
+        <v>109.5</v>
       </c>
       <c r="K60" t="n">
-        <v>155.87</v>
+        <v>168.45</v>
       </c>
       <c r="L60" t="n">
-        <v>185.9</v>
+        <v>200.91</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-118.08</v>
+        <v>-117.51</v>
       </c>
       <c r="K61" t="n">
-        <v>-250.4</v>
+        <v>-249.18</v>
       </c>
       <c r="L61" t="n">
-        <v>276.84</v>
+        <v>275.49</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>49.37</v>
+        <v>99.81</v>
       </c>
       <c r="K62" t="n">
-        <v>-17.55</v>
+        <v>-35.49</v>
       </c>
       <c r="L62" t="n">
-        <v>52.4</v>
+        <v>105.93</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>163.81</v>
+        <v>198.83</v>
       </c>
       <c r="K63" t="n">
-        <v>74.72</v>
+        <v>90.7</v>
       </c>
       <c r="L63" t="n">
-        <v>180.04</v>
+        <v>218.54</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-177.3</v>
+        <v>-219.82</v>
       </c>
       <c r="K64" t="n">
-        <v>19.38</v>
+        <v>24.03</v>
       </c>
       <c r="L64" t="n">
-        <v>178.36</v>
+        <v>221.13</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-136.74</v>
+        <v>-239.54</v>
       </c>
       <c r="K65" t="n">
-        <v>-111.91</v>
+        <v>-196.05</v>
       </c>
       <c r="L65" t="n">
-        <v>176.7</v>
+        <v>309.54</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>561.65</v>
+        <v>683.41</v>
       </c>
       <c r="K66" t="n">
-        <v>30.11</v>
+        <v>36.63</v>
       </c>
       <c r="L66" t="n">
-        <v>562.45</v>
+        <v>684.39</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-76.98999999999999</v>
+        <v>-106.4</v>
       </c>
       <c r="K67" t="n">
-        <v>224.25</v>
+        <v>309.89</v>
       </c>
       <c r="L67" t="n">
-        <v>237.1</v>
+        <v>327.65</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-447.38</v>
+        <v>-528.58</v>
       </c>
       <c r="K68" t="n">
-        <v>779.05</v>
+        <v>920.45</v>
       </c>
       <c r="L68" t="n">
-        <v>898.37</v>
+        <v>1061.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>638.16</v>
+        <v>699.79</v>
       </c>
       <c r="K69" t="n">
-        <v>-8.75</v>
+        <v>-9.6</v>
       </c>
       <c r="L69" t="n">
-        <v>638.22</v>
+        <v>699.85</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>715.8</v>
+        <v>897.5700000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-31.56</v>
+        <v>-39.57</v>
       </c>
       <c r="L70" t="n">
-        <v>716.5</v>
+        <v>898.4400000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>84.94</v>
+        <v>117.28</v>
       </c>
       <c r="K71" t="n">
-        <v>447.97</v>
+        <v>618.53</v>
       </c>
       <c r="L71" t="n">
-        <v>455.96</v>
+        <v>629.55</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>162.67</v>
+        <v>285.97</v>
       </c>
       <c r="K72" t="n">
-        <v>299.47</v>
+        <v>526.47</v>
       </c>
       <c r="L72" t="n">
-        <v>340.8</v>
+        <v>599.12</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-16.6</v>
+        <v>-29.59</v>
       </c>
       <c r="K73" t="n">
-        <v>-248.57</v>
+        <v>-443.13</v>
       </c>
       <c r="L73" t="n">
-        <v>249.12</v>
+        <v>444.12</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-156.01</v>
+        <v>-169.83</v>
       </c>
       <c r="K74" t="n">
-        <v>27.6</v>
+        <v>30.04</v>
       </c>
       <c r="L74" t="n">
-        <v>158.43</v>
+        <v>172.47</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>194.61</v>
+        <v>207.2</v>
       </c>
       <c r="K75" t="n">
-        <v>100.71</v>
+        <v>107.23</v>
       </c>
       <c r="L75" t="n">
-        <v>219.13</v>
+        <v>233.31</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-161.15</v>
+        <v>-179.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-132.06</v>
+        <v>-146.7</v>
       </c>
       <c r="L76" t="n">
-        <v>208.35</v>
+        <v>231.45</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>161.77</v>
+        <v>207.23</v>
       </c>
       <c r="K77" t="n">
-        <v>-56.62</v>
+        <v>-72.53</v>
       </c>
       <c r="L77" t="n">
-        <v>171.4</v>
+        <v>219.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.37</v>
+        <v>-45.49</v>
       </c>
       <c r="K78" t="n">
-        <v>-171.77</v>
+        <v>-241.36</v>
       </c>
       <c r="L78" t="n">
-        <v>174.79</v>
+        <v>245.61</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-33.38</v>
+        <v>-43.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-160.39</v>
+        <v>-208.39</v>
       </c>
       <c r="L79" t="n">
-        <v>163.82</v>
+        <v>212.85</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-329.22</v>
+        <v>-402.62</v>
       </c>
       <c r="K80" t="n">
-        <v>-15.1</v>
+        <v>-18.47</v>
       </c>
       <c r="L80" t="n">
-        <v>329.57</v>
+        <v>403.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-534.35</v>
+        <v>-623.34</v>
       </c>
       <c r="K81" t="n">
-        <v>-172.98</v>
+        <v>-201.78</v>
       </c>
       <c r="L81" t="n">
-        <v>561.65</v>
+        <v>655.1900000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-262.82</v>
+        <v>-291.79</v>
       </c>
       <c r="K82" t="n">
-        <v>440.48</v>
+        <v>489.03</v>
       </c>
       <c r="L82" t="n">
-        <v>512.92</v>
+        <v>569.46</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>208.48</v>
+        <v>272.97</v>
       </c>
       <c r="K83" t="n">
-        <v>444.05</v>
+        <v>581.41</v>
       </c>
       <c r="L83" t="n">
-        <v>490.56</v>
+        <v>642.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>180.62</v>
+        <v>257.88</v>
       </c>
       <c r="K84" t="n">
-        <v>466.39</v>
+        <v>665.9</v>
       </c>
       <c r="L84" t="n">
-        <v>500.14</v>
+        <v>714.09</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>226.7</v>
+        <v>239.82</v>
       </c>
       <c r="K85" t="n">
-        <v>706.67</v>
+        <v>747.5700000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>742.15</v>
+        <v>785.1</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-249.82</v>
+        <v>-356.54</v>
       </c>
       <c r="K86" t="n">
-        <v>487.4</v>
+        <v>695.62</v>
       </c>
       <c r="L86" t="n">
-        <v>547.6900000000001</v>
+        <v>781.67</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-438.73</v>
+        <v>-522.28</v>
       </c>
       <c r="K87" t="n">
-        <v>-246.38</v>
+        <v>-293.3</v>
       </c>
       <c r="L87" t="n">
-        <v>503.18</v>
+        <v>599</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>80.94</v>
+        <v>170.89</v>
       </c>
       <c r="K88" t="n">
-        <v>-123.03</v>
+        <v>-259.75</v>
       </c>
       <c r="L88" t="n">
-        <v>147.26</v>
+        <v>310.92</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-216.43</v>
+        <v>-184.75</v>
       </c>
       <c r="K14" t="n">
-        <v>91.77</v>
+        <v>78.34</v>
       </c>
       <c r="L14" t="n">
-        <v>235.08</v>
+        <v>200.67</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-255.93</v>
+        <v>-181.65</v>
       </c>
       <c r="K15" t="n">
-        <v>-68.17</v>
+        <v>-48.38</v>
       </c>
       <c r="L15" t="n">
-        <v>264.85</v>
+        <v>187.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>99.25</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-116.75</v>
+        <v>-80.2</v>
       </c>
       <c r="L16" t="n">
-        <v>153.23</v>
+        <v>105.27</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>314.25</v>
+        <v>210.12</v>
       </c>
       <c r="K17" t="n">
-        <v>-149.46</v>
+        <v>-99.93000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>347.98</v>
+        <v>232.67</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>280.07</v>
+        <v>205.94</v>
       </c>
       <c r="K18" t="n">
-        <v>225.48</v>
+        <v>165.8</v>
       </c>
       <c r="L18" t="n">
-        <v>359.56</v>
+        <v>264.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>112.69</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>286.06</v>
+        <v>190.92</v>
       </c>
       <c r="L19" t="n">
-        <v>307.46</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>28.47</v>
+        <v>20.63</v>
       </c>
       <c r="K20" t="n">
-        <v>238.69</v>
+        <v>172.95</v>
       </c>
       <c r="L20" t="n">
-        <v>240.39</v>
+        <v>174.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>400.94</v>
+        <v>233.03</v>
       </c>
       <c r="K21" t="n">
-        <v>106.26</v>
+        <v>61.76</v>
       </c>
       <c r="L21" t="n">
-        <v>414.78</v>
+        <v>241.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>126.21</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>265.48</v>
+        <v>180.92</v>
       </c>
       <c r="L22" t="n">
-        <v>293.95</v>
+        <v>200.33</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-489.74</v>
+        <v>-273.56</v>
       </c>
       <c r="K23" t="n">
-        <v>291.28</v>
+        <v>162.7</v>
       </c>
       <c r="L23" t="n">
-        <v>569.8200000000001</v>
+        <v>318.28</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-475.26</v>
+        <v>-267.59</v>
       </c>
       <c r="K24" t="n">
-        <v>-132.15</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>493.29</v>
+        <v>277.74</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-420.46</v>
+        <v>-236.58</v>
       </c>
       <c r="K25" t="n">
-        <v>52.76</v>
+        <v>29.69</v>
       </c>
       <c r="L25" t="n">
-        <v>423.76</v>
+        <v>238.44</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>578.9299999999999</v>
+        <v>271.07</v>
       </c>
       <c r="K26" t="n">
-        <v>698.26</v>
+        <v>326.94</v>
       </c>
       <c r="L26" t="n">
-        <v>907.05</v>
+        <v>424.7</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-486.37</v>
+        <v>-261.65</v>
       </c>
       <c r="K27" t="n">
-        <v>170.79</v>
+        <v>91.88</v>
       </c>
       <c r="L27" t="n">
-        <v>515.48</v>
+        <v>277.31</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-38.46</v>
+        <v>-20.94</v>
       </c>
       <c r="K28" t="n">
-        <v>594.14</v>
+        <v>323.5</v>
       </c>
       <c r="L28" t="n">
-        <v>595.39</v>
+        <v>324.18</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>105.89</v>
+        <v>73.86</v>
       </c>
       <c r="K29" t="n">
-        <v>-101.55</v>
+        <v>-70.83</v>
       </c>
       <c r="L29" t="n">
-        <v>146.71</v>
+        <v>102.34</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.49</v>
+        <v>-7.18</v>
       </c>
       <c r="K30" t="n">
-        <v>-267.96</v>
+        <v>-183.31</v>
       </c>
       <c r="L30" t="n">
-        <v>268.17</v>
+        <v>183.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>226.2</v>
+        <v>180.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-77.98</v>
+        <v>-62.33</v>
       </c>
       <c r="L31" t="n">
-        <v>239.27</v>
+        <v>191.25</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-13.47</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>-279.95</v>
+        <v>-194.74</v>
       </c>
       <c r="L32" t="n">
-        <v>280.28</v>
+        <v>194.97</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-63.88</v>
+        <v>-43.95</v>
       </c>
       <c r="K33" t="n">
-        <v>187.78</v>
+        <v>129.2</v>
       </c>
       <c r="L33" t="n">
-        <v>198.35</v>
+        <v>136.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>215.37</v>
+        <v>171.17</v>
       </c>
       <c r="K34" t="n">
-        <v>-97.89</v>
+        <v>-77.8</v>
       </c>
       <c r="L34" t="n">
-        <v>236.57</v>
+        <v>188.02</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-143.66</v>
+        <v>-87.68000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-406.67</v>
+        <v>-248.19</v>
       </c>
       <c r="L35" t="n">
-        <v>431.3</v>
+        <v>263.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-420.74</v>
+        <v>-246.68</v>
       </c>
       <c r="K36" t="n">
-        <v>129.34</v>
+        <v>75.83</v>
       </c>
       <c r="L36" t="n">
-        <v>440.17</v>
+        <v>258.07</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-190.26</v>
+        <v>-110.3</v>
       </c>
       <c r="K37" t="n">
-        <v>342.43</v>
+        <v>198.51</v>
       </c>
       <c r="L37" t="n">
-        <v>391.74</v>
+        <v>227.1</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-121.88</v>
+        <v>-67.47</v>
       </c>
       <c r="K38" t="n">
-        <v>-267.06</v>
+        <v>-147.84</v>
       </c>
       <c r="L38" t="n">
-        <v>293.56</v>
+        <v>162.51</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-281.19</v>
+        <v>-150.38</v>
       </c>
       <c r="K39" t="n">
-        <v>-115.69</v>
+        <v>-61.87</v>
       </c>
       <c r="L39" t="n">
-        <v>304.06</v>
+        <v>162.61</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-450.89</v>
+        <v>-232.04</v>
       </c>
       <c r="K40" t="n">
-        <v>494.54</v>
+        <v>254.51</v>
       </c>
       <c r="L40" t="n">
-        <v>669.23</v>
+        <v>344.41</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>236.83</v>
+        <v>106.97</v>
       </c>
       <c r="K41" t="n">
-        <v>1016.95</v>
+        <v>459.31</v>
       </c>
       <c r="L41" t="n">
-        <v>1044.16</v>
+        <v>471.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-618.46</v>
+        <v>-321.9</v>
       </c>
       <c r="K42" t="n">
-        <v>488.47</v>
+        <v>254.24</v>
       </c>
       <c r="L42" t="n">
-        <v>788.1</v>
+        <v>410.19</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>967.76</v>
+        <v>559.02</v>
       </c>
       <c r="K43" t="n">
-        <v>144.21</v>
+        <v>83.3</v>
       </c>
       <c r="L43" t="n">
-        <v>978.45</v>
+        <v>565.2</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>66.3</v>
+        <v>55</v>
       </c>
       <c r="K44" t="n">
-        <v>-235.78</v>
+        <v>-195.6</v>
       </c>
       <c r="L44" t="n">
-        <v>244.92</v>
+        <v>203.19</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-138.17</v>
+        <v>-98.95</v>
       </c>
       <c r="K45" t="n">
-        <v>173.53</v>
+        <v>124.28</v>
       </c>
       <c r="L45" t="n">
-        <v>221.82</v>
+        <v>158.86</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-69.70999999999999</v>
+        <v>-49.57</v>
       </c>
       <c r="K46" t="n">
-        <v>141.29</v>
+        <v>100.47</v>
       </c>
       <c r="L46" t="n">
-        <v>157.55</v>
+        <v>112.03</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>11.01</v>
+        <v>7.38</v>
       </c>
       <c r="K47" t="n">
-        <v>-289.33</v>
+        <v>-193.94</v>
       </c>
       <c r="L47" t="n">
-        <v>289.54</v>
+        <v>194.08</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.72</v>
+        <v>-16.4</v>
       </c>
       <c r="K48" t="n">
-        <v>202.79</v>
+        <v>146.33</v>
       </c>
       <c r="L48" t="n">
-        <v>204.05</v>
+        <v>147.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>292.31</v>
+        <v>215.73</v>
       </c>
       <c r="K49" t="n">
-        <v>40.21</v>
+        <v>29.68</v>
       </c>
       <c r="L49" t="n">
-        <v>295.06</v>
+        <v>217.76</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>517.04</v>
+        <v>298.13</v>
       </c>
       <c r="K50" t="n">
-        <v>2.41</v>
+        <v>1.39</v>
       </c>
       <c r="L50" t="n">
-        <v>517.05</v>
+        <v>298.14</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-192.49</v>
+        <v>-119.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-363.77</v>
+        <v>-226.04</v>
       </c>
       <c r="L51" t="n">
-        <v>411.56</v>
+        <v>255.74</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>453.27</v>
+        <v>295.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-138.38</v>
+        <v>-90.12</v>
       </c>
       <c r="L52" t="n">
-        <v>473.93</v>
+        <v>308.65</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>822.51</v>
+        <v>412.22</v>
       </c>
       <c r="K53" t="n">
-        <v>-107.65</v>
+        <v>-53.95</v>
       </c>
       <c r="L53" t="n">
-        <v>829.53</v>
+        <v>415.74</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-590.67</v>
+        <v>-350.79</v>
       </c>
       <c r="K54" t="n">
-        <v>31.29</v>
+        <v>18.59</v>
       </c>
       <c r="L54" t="n">
-        <v>591.5</v>
+        <v>351.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>352.7</v>
+        <v>216.35</v>
       </c>
       <c r="K55" t="n">
-        <v>-389.8</v>
+        <v>-239.12</v>
       </c>
       <c r="L55" t="n">
-        <v>525.6799999999999</v>
+        <v>322.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>278.02</v>
+        <v>158.33</v>
       </c>
       <c r="K56" t="n">
-        <v>955.6900000000001</v>
+        <v>544.25</v>
       </c>
       <c r="L56" t="n">
-        <v>995.3099999999999</v>
+        <v>566.8200000000001</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-117.95</v>
+        <v>-62.48</v>
       </c>
       <c r="K57" t="n">
-        <v>618.2</v>
+        <v>327.48</v>
       </c>
       <c r="L57" t="n">
-        <v>629.36</v>
+        <v>333.39</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>1110.04</v>
+        <v>539.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-262.09</v>
+        <v>-127.46</v>
       </c>
       <c r="L58" t="n">
-        <v>1140.56</v>
+        <v>554.6900000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>134.17</v>
+        <v>108.47</v>
       </c>
       <c r="K59" t="n">
-        <v>196</v>
+        <v>158.46</v>
       </c>
       <c r="L59" t="n">
-        <v>237.53</v>
+        <v>192.03</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>109.5</v>
+        <v>83.39</v>
       </c>
       <c r="K60" t="n">
-        <v>168.45</v>
+        <v>128.28</v>
       </c>
       <c r="L60" t="n">
-        <v>200.91</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-117.51</v>
+        <v>-93.48999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-249.18</v>
+        <v>-198.24</v>
       </c>
       <c r="L61" t="n">
-        <v>275.49</v>
+        <v>219.18</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>99.81</v>
+        <v>81.03</v>
       </c>
       <c r="K62" t="n">
-        <v>-35.49</v>
+        <v>-28.81</v>
       </c>
       <c r="L62" t="n">
-        <v>105.93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>198.83</v>
+        <v>143.41</v>
       </c>
       <c r="K63" t="n">
-        <v>90.7</v>
+        <v>65.42</v>
       </c>
       <c r="L63" t="n">
-        <v>218.54</v>
+        <v>157.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-219.82</v>
+        <v>-162.23</v>
       </c>
       <c r="K64" t="n">
-        <v>24.03</v>
+        <v>17.74</v>
       </c>
       <c r="L64" t="n">
-        <v>221.13</v>
+        <v>163.2</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-239.54</v>
+        <v>-142.34</v>
       </c>
       <c r="K65" t="n">
-        <v>-196.05</v>
+        <v>-116.49</v>
       </c>
       <c r="L65" t="n">
-        <v>309.54</v>
+        <v>183.93</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>683.41</v>
+        <v>380.81</v>
       </c>
       <c r="K66" t="n">
-        <v>36.63</v>
+        <v>20.41</v>
       </c>
       <c r="L66" t="n">
-        <v>684.39</v>
+        <v>381.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-106.4</v>
+        <v>-62.01</v>
       </c>
       <c r="K67" t="n">
-        <v>309.89</v>
+        <v>180.59</v>
       </c>
       <c r="L67" t="n">
-        <v>327.65</v>
+        <v>190.94</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-528.58</v>
+        <v>-285.76</v>
       </c>
       <c r="K68" t="n">
-        <v>920.45</v>
+        <v>497.62</v>
       </c>
       <c r="L68" t="n">
-        <v>1061.43</v>
+        <v>573.83</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>699.79</v>
+        <v>417.59</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.6</v>
+        <v>-5.73</v>
       </c>
       <c r="L69" t="n">
-        <v>699.85</v>
+        <v>417.63</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>897.5700000000001</v>
+        <v>450.13</v>
       </c>
       <c r="K70" t="n">
-        <v>-39.57</v>
+        <v>-19.85</v>
       </c>
       <c r="L70" t="n">
-        <v>898.4400000000001</v>
+        <v>450.57</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>117.28</v>
+        <v>62.5</v>
       </c>
       <c r="K71" t="n">
-        <v>618.53</v>
+        <v>329.62</v>
       </c>
       <c r="L71" t="n">
-        <v>629.55</v>
+        <v>335.49</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>285.97</v>
+        <v>142.52</v>
       </c>
       <c r="K72" t="n">
-        <v>526.47</v>
+        <v>262.37</v>
       </c>
       <c r="L72" t="n">
-        <v>599.12</v>
+        <v>298.58</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-29.59</v>
+        <v>-16.67</v>
       </c>
       <c r="K73" t="n">
-        <v>-443.13</v>
+        <v>-249.62</v>
       </c>
       <c r="L73" t="n">
-        <v>444.12</v>
+        <v>250.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-169.83</v>
+        <v>-134.75</v>
       </c>
       <c r="K74" t="n">
-        <v>30.04</v>
+        <v>23.84</v>
       </c>
       <c r="L74" t="n">
-        <v>172.47</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>207.2</v>
+        <v>156.18</v>
       </c>
       <c r="K75" t="n">
-        <v>107.23</v>
+        <v>80.83</v>
       </c>
       <c r="L75" t="n">
-        <v>233.31</v>
+        <v>175.86</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-179.02</v>
+        <v>-137.57</v>
       </c>
       <c r="K76" t="n">
-        <v>-146.7</v>
+        <v>-112.73</v>
       </c>
       <c r="L76" t="n">
-        <v>231.45</v>
+        <v>177.86</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>207.23</v>
+        <v>158.23</v>
       </c>
       <c r="K77" t="n">
-        <v>-72.53</v>
+        <v>-55.38</v>
       </c>
       <c r="L77" t="n">
-        <v>219.55</v>
+        <v>167.64</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-45.49</v>
+        <v>-32.03</v>
       </c>
       <c r="K78" t="n">
-        <v>-241.36</v>
+        <v>-169.93</v>
       </c>
       <c r="L78" t="n">
-        <v>245.61</v>
+        <v>172.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-43.37</v>
+        <v>-29.6</v>
       </c>
       <c r="K79" t="n">
-        <v>-208.39</v>
+        <v>-142.21</v>
       </c>
       <c r="L79" t="n">
-        <v>212.85</v>
+        <v>145.26</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-402.62</v>
+        <v>-240.11</v>
       </c>
       <c r="K80" t="n">
-        <v>-18.47</v>
+        <v>-11.02</v>
       </c>
       <c r="L80" t="n">
-        <v>403.05</v>
+        <v>240.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-623.34</v>
+        <v>-359.68</v>
       </c>
       <c r="K81" t="n">
-        <v>-201.78</v>
+        <v>-116.43</v>
       </c>
       <c r="L81" t="n">
-        <v>655.1900000000001</v>
+        <v>378.06</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-291.79</v>
+        <v>-180.54</v>
       </c>
       <c r="K82" t="n">
-        <v>489.03</v>
+        <v>302.59</v>
       </c>
       <c r="L82" t="n">
-        <v>569.46</v>
+        <v>352.36</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>272.97</v>
+        <v>154.44</v>
       </c>
       <c r="K83" t="n">
-        <v>581.41</v>
+        <v>328.96</v>
       </c>
       <c r="L83" t="n">
-        <v>642.3</v>
+        <v>363.41</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>257.88</v>
+        <v>128.88</v>
       </c>
       <c r="K84" t="n">
-        <v>665.9</v>
+        <v>332.8</v>
       </c>
       <c r="L84" t="n">
-        <v>714.09</v>
+        <v>356.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>239.82</v>
+        <v>148.07</v>
       </c>
       <c r="K85" t="n">
-        <v>747.5700000000001</v>
+        <v>461.57</v>
       </c>
       <c r="L85" t="n">
-        <v>785.1</v>
+        <v>484.74</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-356.54</v>
+        <v>-183.53</v>
       </c>
       <c r="K86" t="n">
-        <v>695.62</v>
+        <v>358.08</v>
       </c>
       <c r="L86" t="n">
-        <v>781.67</v>
+        <v>402.37</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-522.28</v>
+        <v>-304.99</v>
       </c>
       <c r="K87" t="n">
-        <v>-293.3</v>
+        <v>-171.27</v>
       </c>
       <c r="L87" t="n">
-        <v>599</v>
+        <v>349.79</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>170.89</v>
+        <v>100.15</v>
       </c>
       <c r="K88" t="n">
-        <v>-259.75</v>
+        <v>-152.22</v>
       </c>
       <c r="L88" t="n">
-        <v>310.92</v>
+        <v>182.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-184.75</v>
+        <v>-190.85</v>
       </c>
       <c r="K14" t="n">
-        <v>78.34</v>
+        <v>80.92</v>
       </c>
       <c r="L14" t="n">
-        <v>200.67</v>
+        <v>207.29</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-181.65</v>
+        <v>-193.13</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.38</v>
+        <v>-51.44</v>
       </c>
       <c r="L15" t="n">
-        <v>187.98</v>
+        <v>199.86</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>68.18000000000001</v>
+        <v>72.78</v>
       </c>
       <c r="K16" t="n">
-        <v>-80.2</v>
+        <v>-85.62</v>
       </c>
       <c r="L16" t="n">
-        <v>105.27</v>
+        <v>112.37</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>210.12</v>
+        <v>227.77</v>
       </c>
       <c r="K17" t="n">
-        <v>-99.93000000000001</v>
+        <v>-108.33</v>
       </c>
       <c r="L17" t="n">
-        <v>232.67</v>
+        <v>252.22</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>205.94</v>
+        <v>218.59</v>
       </c>
       <c r="K18" t="n">
-        <v>165.8</v>
+        <v>175.99</v>
       </c>
       <c r="L18" t="n">
-        <v>264.39</v>
+        <v>280.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>75.20999999999999</v>
+        <v>81</v>
       </c>
       <c r="K19" t="n">
-        <v>190.92</v>
+        <v>205.63</v>
       </c>
       <c r="L19" t="n">
-        <v>205.2</v>
+        <v>221.01</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>20.63</v>
+        <v>22.39</v>
       </c>
       <c r="K20" t="n">
-        <v>172.95</v>
+        <v>187.68</v>
       </c>
       <c r="L20" t="n">
-        <v>174.18</v>
+        <v>189.01</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>233.03</v>
+        <v>259.66</v>
       </c>
       <c r="K21" t="n">
-        <v>61.76</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>241.08</v>
+        <v>268.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>86.01000000000001</v>
+        <v>93.72</v>
       </c>
       <c r="K22" t="n">
-        <v>180.92</v>
+        <v>197.14</v>
       </c>
       <c r="L22" t="n">
-        <v>200.33</v>
+        <v>218.29</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-273.56</v>
+        <v>-311.11</v>
       </c>
       <c r="K23" t="n">
-        <v>162.7</v>
+        <v>185.03</v>
       </c>
       <c r="L23" t="n">
-        <v>318.28</v>
+        <v>361.98</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-267.59</v>
+        <v>-301.07</v>
       </c>
       <c r="K24" t="n">
-        <v>-74.40000000000001</v>
+        <v>-83.72</v>
       </c>
       <c r="L24" t="n">
-        <v>277.74</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-236.58</v>
+        <v>-269.22</v>
       </c>
       <c r="K25" t="n">
-        <v>29.69</v>
+        <v>33.78</v>
       </c>
       <c r="L25" t="n">
-        <v>238.44</v>
+        <v>271.33</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>271.07</v>
+        <v>317.57</v>
       </c>
       <c r="K26" t="n">
-        <v>326.94</v>
+        <v>383.03</v>
       </c>
       <c r="L26" t="n">
-        <v>424.7</v>
+        <v>497.56</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-261.65</v>
+        <v>-304.19</v>
       </c>
       <c r="K27" t="n">
-        <v>91.88</v>
+        <v>106.82</v>
       </c>
       <c r="L27" t="n">
-        <v>277.31</v>
+        <v>322.4</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-20.94</v>
+        <v>-24.2</v>
       </c>
       <c r="K28" t="n">
-        <v>323.5</v>
+        <v>373.84</v>
       </c>
       <c r="L28" t="n">
-        <v>324.18</v>
+        <v>374.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>73.86</v>
+        <v>78.03</v>
       </c>
       <c r="K29" t="n">
-        <v>-70.83</v>
+        <v>-74.84</v>
       </c>
       <c r="L29" t="n">
-        <v>102.34</v>
+        <v>108.12</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.18</v>
+        <v>-7.66</v>
       </c>
       <c r="K30" t="n">
-        <v>-183.31</v>
+        <v>-195.59</v>
       </c>
       <c r="L30" t="n">
-        <v>183.45</v>
+        <v>195.74</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>180.8</v>
+        <v>185.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-62.33</v>
+        <v>-63.85</v>
       </c>
       <c r="L31" t="n">
-        <v>191.25</v>
+        <v>195.9</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.369999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-194.74</v>
+        <v>-209.3</v>
       </c>
       <c r="L32" t="n">
-        <v>194.97</v>
+        <v>209.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-43.95</v>
+        <v>-47.08</v>
       </c>
       <c r="K33" t="n">
-        <v>129.2</v>
+        <v>138.4</v>
       </c>
       <c r="L33" t="n">
-        <v>136.48</v>
+        <v>146.19</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>171.17</v>
+        <v>178.76</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.8</v>
+        <v>-81.25</v>
       </c>
       <c r="L34" t="n">
-        <v>188.02</v>
+        <v>196.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-87.68000000000001</v>
+        <v>-96.86</v>
       </c>
       <c r="K35" t="n">
-        <v>-248.19</v>
+        <v>-274.21</v>
       </c>
       <c r="L35" t="n">
-        <v>263.23</v>
+        <v>290.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-246.68</v>
+        <v>-273.72</v>
       </c>
       <c r="K36" t="n">
-        <v>75.83</v>
+        <v>84.14</v>
       </c>
       <c r="L36" t="n">
-        <v>258.07</v>
+        <v>286.37</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-110.3</v>
+        <v>-124.39</v>
       </c>
       <c r="K37" t="n">
-        <v>198.51</v>
+        <v>223.87</v>
       </c>
       <c r="L37" t="n">
-        <v>227.1</v>
+        <v>256.11</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-67.47</v>
+        <v>-75.98</v>
       </c>
       <c r="K38" t="n">
-        <v>-147.84</v>
+        <v>-166.49</v>
       </c>
       <c r="L38" t="n">
-        <v>162.51</v>
+        <v>183.01</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-150.38</v>
+        <v>-172.59</v>
       </c>
       <c r="K39" t="n">
-        <v>-61.87</v>
+        <v>-71.01000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>162.61</v>
+        <v>186.63</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-232.04</v>
+        <v>-264.55</v>
       </c>
       <c r="K40" t="n">
-        <v>254.51</v>
+        <v>290.16</v>
       </c>
       <c r="L40" t="n">
-        <v>344.41</v>
+        <v>392.66</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>106.97</v>
+        <v>127.46</v>
       </c>
       <c r="K41" t="n">
-        <v>459.31</v>
+        <v>547.29</v>
       </c>
       <c r="L41" t="n">
-        <v>471.6</v>
+        <v>561.9400000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-321.9</v>
+        <v>-370.22</v>
       </c>
       <c r="K42" t="n">
-        <v>254.24</v>
+        <v>292.41</v>
       </c>
       <c r="L42" t="n">
-        <v>410.19</v>
+        <v>471.77</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>559.02</v>
+        <v>640.1799999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>83.3</v>
+        <v>95.39</v>
       </c>
       <c r="L43" t="n">
-        <v>565.2</v>
+        <v>647.25</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>55</v>
+        <v>57.65</v>
       </c>
       <c r="K44" t="n">
-        <v>-195.6</v>
+        <v>-205.01</v>
       </c>
       <c r="L44" t="n">
-        <v>203.19</v>
+        <v>212.96</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-98.95</v>
+        <v>-104.82</v>
       </c>
       <c r="K45" t="n">
-        <v>124.28</v>
+        <v>131.65</v>
       </c>
       <c r="L45" t="n">
-        <v>158.86</v>
+        <v>168.29</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-49.57</v>
+        <v>-52.45</v>
       </c>
       <c r="K46" t="n">
-        <v>100.47</v>
+        <v>106.31</v>
       </c>
       <c r="L46" t="n">
-        <v>112.03</v>
+        <v>118.55</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>7.38</v>
+        <v>7.89</v>
       </c>
       <c r="K47" t="n">
-        <v>-193.94</v>
+        <v>-207.45</v>
       </c>
       <c r="L47" t="n">
-        <v>194.08</v>
+        <v>207.6</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-16.4</v>
+        <v>-17.57</v>
       </c>
       <c r="K48" t="n">
-        <v>146.33</v>
+        <v>156.77</v>
       </c>
       <c r="L48" t="n">
-        <v>147.25</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>215.73</v>
+        <v>227.3</v>
       </c>
       <c r="K49" t="n">
-        <v>29.68</v>
+        <v>31.27</v>
       </c>
       <c r="L49" t="n">
-        <v>217.76</v>
+        <v>229.44</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>298.13</v>
+        <v>336.8</v>
       </c>
       <c r="K50" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="L50" t="n">
-        <v>298.14</v>
+        <v>336.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-119.61</v>
+        <v>-132</v>
       </c>
       <c r="K51" t="n">
-        <v>-226.04</v>
+        <v>-249.44</v>
       </c>
       <c r="L51" t="n">
-        <v>255.74</v>
+        <v>282.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>295.2</v>
+        <v>323.15</v>
       </c>
       <c r="K52" t="n">
-        <v>-90.12</v>
+        <v>-98.65000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>308.65</v>
+        <v>337.88</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>412.22</v>
+        <v>477.24</v>
       </c>
       <c r="K53" t="n">
-        <v>-53.95</v>
+        <v>-62.46</v>
       </c>
       <c r="L53" t="n">
-        <v>415.74</v>
+        <v>481.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-350.79</v>
+        <v>-392.97</v>
       </c>
       <c r="K54" t="n">
-        <v>18.59</v>
+        <v>20.82</v>
       </c>
       <c r="L54" t="n">
-        <v>351.28</v>
+        <v>393.52</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>216.35</v>
+        <v>237.97</v>
       </c>
       <c r="K55" t="n">
-        <v>-239.12</v>
+        <v>-263</v>
       </c>
       <c r="L55" t="n">
-        <v>322.47</v>
+        <v>354.68</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>158.33</v>
+        <v>183.48</v>
       </c>
       <c r="K56" t="n">
-        <v>544.25</v>
+        <v>630.71</v>
       </c>
       <c r="L56" t="n">
-        <v>566.8200000000001</v>
+        <v>656.86</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-62.48</v>
+        <v>-72.7</v>
       </c>
       <c r="K57" t="n">
-        <v>327.48</v>
+        <v>381.05</v>
       </c>
       <c r="L57" t="n">
-        <v>333.39</v>
+        <v>387.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>539.85</v>
+        <v>628.2</v>
       </c>
       <c r="K58" t="n">
-        <v>-127.46</v>
+        <v>-148.32</v>
       </c>
       <c r="L58" t="n">
-        <v>554.6900000000001</v>
+        <v>645.48</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>108.47</v>
+        <v>113.72</v>
       </c>
       <c r="K59" t="n">
-        <v>158.46</v>
+        <v>166.12</v>
       </c>
       <c r="L59" t="n">
-        <v>192.03</v>
+        <v>201.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>83.39</v>
+        <v>86.02</v>
       </c>
       <c r="K60" t="n">
-        <v>128.28</v>
+        <v>132.32</v>
       </c>
       <c r="L60" t="n">
-        <v>153</v>
+        <v>157.82</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-93.48999999999999</v>
+        <v>-97.97</v>
       </c>
       <c r="K61" t="n">
-        <v>-198.24</v>
+        <v>-207.75</v>
       </c>
       <c r="L61" t="n">
-        <v>219.18</v>
+        <v>229.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>81.03</v>
+        <v>85.36</v>
       </c>
       <c r="K62" t="n">
-        <v>-28.81</v>
+        <v>-30.35</v>
       </c>
       <c r="L62" t="n">
-        <v>86</v>
+        <v>90.59</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>143.41</v>
+        <v>151.96</v>
       </c>
       <c r="K63" t="n">
-        <v>65.42</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>157.63</v>
+        <v>167.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-162.23</v>
+        <v>-172.5</v>
       </c>
       <c r="K64" t="n">
-        <v>17.74</v>
+        <v>18.86</v>
       </c>
       <c r="L64" t="n">
-        <v>163.2</v>
+        <v>173.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-142.34</v>
+        <v>-158.78</v>
       </c>
       <c r="K65" t="n">
-        <v>-116.49</v>
+        <v>-129.95</v>
       </c>
       <c r="L65" t="n">
-        <v>183.93</v>
+        <v>205.17</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>380.81</v>
+        <v>430.94</v>
       </c>
       <c r="K66" t="n">
-        <v>20.41</v>
+        <v>23.1</v>
       </c>
       <c r="L66" t="n">
-        <v>381.36</v>
+        <v>431.56</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-62.01</v>
+        <v>-69.19</v>
       </c>
       <c r="K67" t="n">
-        <v>180.59</v>
+        <v>201.53</v>
       </c>
       <c r="L67" t="n">
-        <v>190.94</v>
+        <v>213.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-285.76</v>
+        <v>-325.35</v>
       </c>
       <c r="K68" t="n">
-        <v>497.62</v>
+        <v>566.55</v>
       </c>
       <c r="L68" t="n">
-        <v>573.83</v>
+        <v>653.3200000000001</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>417.59</v>
+        <v>470.34</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.73</v>
+        <v>-6.45</v>
       </c>
       <c r="L69" t="n">
-        <v>417.63</v>
+        <v>470.39</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>450.13</v>
+        <v>527.13</v>
       </c>
       <c r="K70" t="n">
-        <v>-19.85</v>
+        <v>-23.24</v>
       </c>
       <c r="L70" t="n">
-        <v>450.57</v>
+        <v>527.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>62.5</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>329.62</v>
+        <v>382.43</v>
       </c>
       <c r="L71" t="n">
-        <v>335.49</v>
+        <v>389.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>142.52</v>
+        <v>166.77</v>
       </c>
       <c r="K72" t="n">
-        <v>262.37</v>
+        <v>307.02</v>
       </c>
       <c r="L72" t="n">
-        <v>298.58</v>
+        <v>349.39</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-16.67</v>
+        <v>-19.19</v>
       </c>
       <c r="K73" t="n">
-        <v>-249.62</v>
+        <v>-287.36</v>
       </c>
       <c r="L73" t="n">
-        <v>250.17</v>
+        <v>288</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-134.75</v>
+        <v>-139.9</v>
       </c>
       <c r="K74" t="n">
-        <v>23.84</v>
+        <v>24.75</v>
       </c>
       <c r="L74" t="n">
-        <v>136.85</v>
+        <v>142.07</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>156.18</v>
+        <v>164.86</v>
       </c>
       <c r="K75" t="n">
-        <v>80.83</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>175.86</v>
+        <v>185.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-137.57</v>
+        <v>-146.25</v>
       </c>
       <c r="K76" t="n">
-        <v>-112.73</v>
+        <v>-119.84</v>
       </c>
       <c r="L76" t="n">
-        <v>177.86</v>
+        <v>189.08</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>158.23</v>
+        <v>165.8</v>
       </c>
       <c r="K77" t="n">
-        <v>-55.38</v>
+        <v>-58.03</v>
       </c>
       <c r="L77" t="n">
-        <v>167.64</v>
+        <v>175.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-32.03</v>
+        <v>-34.26</v>
       </c>
       <c r="K78" t="n">
-        <v>-169.93</v>
+        <v>-181.77</v>
       </c>
       <c r="L78" t="n">
-        <v>172.92</v>
+        <v>184.97</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-29.6</v>
+        <v>-32.07</v>
       </c>
       <c r="K79" t="n">
-        <v>-142.21</v>
+        <v>-154.06</v>
       </c>
       <c r="L79" t="n">
-        <v>145.26</v>
+        <v>157.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-240.11</v>
+        <v>-270</v>
       </c>
       <c r="K80" t="n">
-        <v>-11.02</v>
+        <v>-12.39</v>
       </c>
       <c r="L80" t="n">
-        <v>240.36</v>
+        <v>270.29</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-359.68</v>
+        <v>-404.09</v>
       </c>
       <c r="K81" t="n">
-        <v>-116.43</v>
+        <v>-130.81</v>
       </c>
       <c r="L81" t="n">
-        <v>378.06</v>
+        <v>424.74</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-180.54</v>
+        <v>-199.42</v>
       </c>
       <c r="K82" t="n">
-        <v>302.59</v>
+        <v>334.23</v>
       </c>
       <c r="L82" t="n">
-        <v>352.36</v>
+        <v>389.2</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>154.44</v>
+        <v>173.64</v>
       </c>
       <c r="K83" t="n">
-        <v>328.96</v>
+        <v>369.85</v>
       </c>
       <c r="L83" t="n">
-        <v>363.41</v>
+        <v>408.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>128.88</v>
+        <v>148.29</v>
       </c>
       <c r="K84" t="n">
-        <v>332.8</v>
+        <v>382.91</v>
       </c>
       <c r="L84" t="n">
-        <v>356.89</v>
+        <v>410.63</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>148.07</v>
+        <v>166.66</v>
       </c>
       <c r="K85" t="n">
-        <v>461.57</v>
+        <v>519.51</v>
       </c>
       <c r="L85" t="n">
-        <v>484.74</v>
+        <v>545.59</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-183.53</v>
+        <v>-215.87</v>
       </c>
       <c r="K86" t="n">
-        <v>358.08</v>
+        <v>421.16</v>
       </c>
       <c r="L86" t="n">
-        <v>402.37</v>
+        <v>473.26</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-304.99</v>
+        <v>-341.95</v>
       </c>
       <c r="K87" t="n">
-        <v>-171.27</v>
+        <v>-192.03</v>
       </c>
       <c r="L87" t="n">
-        <v>349.79</v>
+        <v>392.19</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>100.15</v>
+        <v>113.93</v>
       </c>
       <c r="K88" t="n">
-        <v>-152.22</v>
+        <v>-173.17</v>
       </c>
       <c r="L88" t="n">
-        <v>182.21</v>
+        <v>207.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-190.85</v>
+        <v>-85.15000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>80.92</v>
+        <v>36.11</v>
       </c>
       <c r="L14" t="n">
-        <v>207.29</v>
+        <v>92.48999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-193.13</v>
+        <v>-85.31999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-51.44</v>
+        <v>-22.73</v>
       </c>
       <c r="L15" t="n">
-        <v>199.86</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>72.78</v>
+        <v>31.78</v>
       </c>
       <c r="K16" t="n">
-        <v>-85.62</v>
+        <v>-37.39</v>
       </c>
       <c r="L16" t="n">
-        <v>112.37</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>227.77</v>
+        <v>99.47</v>
       </c>
       <c r="K17" t="n">
-        <v>-108.33</v>
+        <v>-47.31</v>
       </c>
       <c r="L17" t="n">
-        <v>252.22</v>
+        <v>110.15</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>218.59</v>
+        <v>105.59</v>
       </c>
       <c r="K18" t="n">
-        <v>175.99</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>280.63</v>
+        <v>135.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>81</v>
+        <v>38.98</v>
       </c>
       <c r="K19" t="n">
-        <v>205.63</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>221.01</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>22.39</v>
+        <v>11.24</v>
       </c>
       <c r="K20" t="n">
-        <v>187.68</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>189.01</v>
+        <v>94.88</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>259.66</v>
+        <v>129.06</v>
       </c>
       <c r="K21" t="n">
-        <v>68.81999999999999</v>
+        <v>34.21</v>
       </c>
       <c r="L21" t="n">
-        <v>268.63</v>
+        <v>133.51</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>93.72</v>
+        <v>45.93</v>
       </c>
       <c r="K22" t="n">
-        <v>197.14</v>
+        <v>96.61</v>
       </c>
       <c r="L22" t="n">
-        <v>218.29</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-311.11</v>
+        <v>-172.33</v>
       </c>
       <c r="K23" t="n">
-        <v>185.03</v>
+        <v>102.5</v>
       </c>
       <c r="L23" t="n">
-        <v>361.98</v>
+        <v>200.51</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-301.07</v>
+        <v>-171.76</v>
       </c>
       <c r="K24" t="n">
-        <v>-83.72</v>
+        <v>-47.76</v>
       </c>
       <c r="L24" t="n">
-        <v>312.5</v>
+        <v>178.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-269.22</v>
+        <v>-153.24</v>
       </c>
       <c r="K25" t="n">
-        <v>33.78</v>
+        <v>19.23</v>
       </c>
       <c r="L25" t="n">
-        <v>271.33</v>
+        <v>154.44</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>317.57</v>
+        <v>171.72</v>
       </c>
       <c r="K26" t="n">
-        <v>383.03</v>
+        <v>207.12</v>
       </c>
       <c r="L26" t="n">
-        <v>497.56</v>
+        <v>269.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-304.19</v>
+        <v>-166.1</v>
       </c>
       <c r="K27" t="n">
-        <v>106.82</v>
+        <v>58.33</v>
       </c>
       <c r="L27" t="n">
-        <v>322.4</v>
+        <v>176.04</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-24.2</v>
+        <v>-13.44</v>
       </c>
       <c r="K28" t="n">
-        <v>373.84</v>
+        <v>207.57</v>
       </c>
       <c r="L28" t="n">
-        <v>374.62</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>78.03</v>
+        <v>36.37</v>
       </c>
       <c r="K29" t="n">
-        <v>-74.84</v>
+        <v>-34.88</v>
       </c>
       <c r="L29" t="n">
-        <v>108.12</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.66</v>
+        <v>-3.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-195.59</v>
+        <v>-83.8</v>
       </c>
       <c r="L30" t="n">
-        <v>195.74</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>185.2</v>
+        <v>87.84</v>
       </c>
       <c r="K31" t="n">
-        <v>-63.85</v>
+        <v>-30.28</v>
       </c>
       <c r="L31" t="n">
-        <v>195.9</v>
+        <v>92.92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-10.07</v>
+        <v>-4.52</v>
       </c>
       <c r="K32" t="n">
-        <v>-209.3</v>
+        <v>-93.98999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>209.54</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-47.08</v>
+        <v>-20.17</v>
       </c>
       <c r="K33" t="n">
-        <v>138.4</v>
+        <v>59.3</v>
       </c>
       <c r="L33" t="n">
-        <v>146.19</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>178.76</v>
+        <v>74.77</v>
       </c>
       <c r="K34" t="n">
-        <v>-81.25</v>
+        <v>-33.98</v>
       </c>
       <c r="L34" t="n">
-        <v>196.36</v>
+        <v>82.13</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-96.86</v>
+        <v>-47.38</v>
       </c>
       <c r="K35" t="n">
-        <v>-274.21</v>
+        <v>-134.11</v>
       </c>
       <c r="L35" t="n">
-        <v>290.81</v>
+        <v>142.24</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-273.72</v>
+        <v>-132.49</v>
       </c>
       <c r="K36" t="n">
-        <v>84.14</v>
+        <v>40.73</v>
       </c>
       <c r="L36" t="n">
-        <v>286.37</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-124.39</v>
+        <v>-61.63</v>
       </c>
       <c r="K37" t="n">
-        <v>223.87</v>
+        <v>110.92</v>
       </c>
       <c r="L37" t="n">
-        <v>256.11</v>
+        <v>126.89</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-75.98</v>
+        <v>-40.66</v>
       </c>
       <c r="K38" t="n">
-        <v>-166.49</v>
+        <v>-89.08</v>
       </c>
       <c r="L38" t="n">
-        <v>183.01</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-172.59</v>
+        <v>-91.39</v>
       </c>
       <c r="K39" t="n">
-        <v>-71.01000000000001</v>
+        <v>-37.6</v>
       </c>
       <c r="L39" t="n">
-        <v>186.63</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-264.55</v>
+        <v>-115.62</v>
       </c>
       <c r="K40" t="n">
-        <v>290.16</v>
+        <v>126.81</v>
       </c>
       <c r="L40" t="n">
-        <v>392.66</v>
+        <v>171.6</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>127.46</v>
+        <v>67.61</v>
       </c>
       <c r="K41" t="n">
-        <v>547.29</v>
+        <v>290.3</v>
       </c>
       <c r="L41" t="n">
-        <v>561.9400000000001</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-370.22</v>
+        <v>-203.04</v>
       </c>
       <c r="K42" t="n">
-        <v>292.41</v>
+        <v>160.37</v>
       </c>
       <c r="L42" t="n">
-        <v>471.77</v>
+        <v>258.73</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>640.1799999999999</v>
+        <v>345.1</v>
       </c>
       <c r="K43" t="n">
-        <v>95.39</v>
+        <v>51.42</v>
       </c>
       <c r="L43" t="n">
-        <v>647.25</v>
+        <v>348.91</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>57.65</v>
+        <v>22.93</v>
       </c>
       <c r="K44" t="n">
-        <v>-205.01</v>
+        <v>-81.55</v>
       </c>
       <c r="L44" t="n">
-        <v>212.96</v>
+        <v>84.70999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-104.82</v>
+        <v>-41.82</v>
       </c>
       <c r="K45" t="n">
-        <v>131.65</v>
+        <v>52.53</v>
       </c>
       <c r="L45" t="n">
-        <v>168.29</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-52.45</v>
+        <v>-23.36</v>
       </c>
       <c r="K46" t="n">
-        <v>106.31</v>
+        <v>47.34</v>
       </c>
       <c r="L46" t="n">
-        <v>118.55</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>7.89</v>
+        <v>3.48</v>
       </c>
       <c r="K47" t="n">
-        <v>-207.45</v>
+        <v>-91.43000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>207.6</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-17.57</v>
+        <v>-7.97</v>
       </c>
       <c r="K48" t="n">
-        <v>156.77</v>
+        <v>71.09</v>
       </c>
       <c r="L48" t="n">
-        <v>157.75</v>
+        <v>71.54000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>227.3</v>
+        <v>97.11</v>
       </c>
       <c r="K49" t="n">
-        <v>31.27</v>
+        <v>13.36</v>
       </c>
       <c r="L49" t="n">
-        <v>229.44</v>
+        <v>98.02</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>336.8</v>
+        <v>165.77</v>
       </c>
       <c r="K50" t="n">
-        <v>1.57</v>
+        <v>0.77</v>
       </c>
       <c r="L50" t="n">
-        <v>336.8</v>
+        <v>165.77</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-132</v>
+        <v>-63.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-249.44</v>
+        <v>-119.62</v>
       </c>
       <c r="L51" t="n">
-        <v>282.21</v>
+        <v>135.34</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>323.15</v>
+        <v>157.04</v>
       </c>
       <c r="K52" t="n">
-        <v>-98.65000000000001</v>
+        <v>-47.94</v>
       </c>
       <c r="L52" t="n">
-        <v>337.88</v>
+        <v>164.19</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>477.24</v>
+        <v>216.73</v>
       </c>
       <c r="K53" t="n">
-        <v>-62.46</v>
+        <v>-28.36</v>
       </c>
       <c r="L53" t="n">
-        <v>481.31</v>
+        <v>218.58</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-392.97</v>
+        <v>-176.71</v>
       </c>
       <c r="K54" t="n">
-        <v>20.82</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>393.52</v>
+        <v>176.96</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>237.97</v>
+        <v>104.98</v>
       </c>
       <c r="K55" t="n">
-        <v>-263</v>
+        <v>-116.02</v>
       </c>
       <c r="L55" t="n">
-        <v>354.68</v>
+        <v>156.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>183.48</v>
+        <v>97.59</v>
       </c>
       <c r="K56" t="n">
-        <v>630.71</v>
+        <v>335.47</v>
       </c>
       <c r="L56" t="n">
-        <v>656.86</v>
+        <v>349.37</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-72.7</v>
+        <v>-38.84</v>
       </c>
       <c r="K57" t="n">
-        <v>381.05</v>
+        <v>203.58</v>
       </c>
       <c r="L57" t="n">
-        <v>387.92</v>
+        <v>207.25</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>628.2</v>
+        <v>343.52</v>
       </c>
       <c r="K58" t="n">
-        <v>-148.32</v>
+        <v>-81.11</v>
       </c>
       <c r="L58" t="n">
-        <v>645.48</v>
+        <v>352.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>113.72</v>
+        <v>47.93</v>
       </c>
       <c r="K59" t="n">
-        <v>166.12</v>
+        <v>70.02</v>
       </c>
       <c r="L59" t="n">
-        <v>201.32</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>86.02</v>
+        <v>38.77</v>
       </c>
       <c r="K60" t="n">
-        <v>132.32</v>
+        <v>59.64</v>
       </c>
       <c r="L60" t="n">
-        <v>157.82</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-97.97</v>
+        <v>-38.98</v>
       </c>
       <c r="K61" t="n">
-        <v>-207.75</v>
+        <v>-82.66</v>
       </c>
       <c r="L61" t="n">
-        <v>229.69</v>
+        <v>91.39</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>85.36</v>
+        <v>34.59</v>
       </c>
       <c r="K62" t="n">
-        <v>-30.35</v>
+        <v>-12.3</v>
       </c>
       <c r="L62" t="n">
-        <v>90.59</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>151.96</v>
+        <v>68.8</v>
       </c>
       <c r="K63" t="n">
-        <v>69.31999999999999</v>
+        <v>31.38</v>
       </c>
       <c r="L63" t="n">
-        <v>167.02</v>
+        <v>75.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-172.5</v>
+        <v>-74.34</v>
       </c>
       <c r="K64" t="n">
-        <v>18.86</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>173.53</v>
+        <v>74.78</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-158.78</v>
+        <v>-75.83</v>
       </c>
       <c r="K65" t="n">
-        <v>-129.95</v>
+        <v>-62.06</v>
       </c>
       <c r="L65" t="n">
-        <v>205.17</v>
+        <v>97.98999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>430.94</v>
+        <v>205.87</v>
       </c>
       <c r="K66" t="n">
-        <v>23.1</v>
+        <v>11.04</v>
       </c>
       <c r="L66" t="n">
-        <v>431.56</v>
+        <v>206.17</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-69.19</v>
+        <v>-34.5</v>
       </c>
       <c r="K67" t="n">
-        <v>201.53</v>
+        <v>100.49</v>
       </c>
       <c r="L67" t="n">
-        <v>213.08</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-325.35</v>
+        <v>-146.74</v>
       </c>
       <c r="K68" t="n">
-        <v>566.55</v>
+        <v>255.52</v>
       </c>
       <c r="L68" t="n">
-        <v>653.3200000000001</v>
+        <v>294.66</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>470.34</v>
+        <v>217.93</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.45</v>
+        <v>-2.99</v>
       </c>
       <c r="L69" t="n">
-        <v>470.39</v>
+        <v>217.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>527.13</v>
+        <v>240.57</v>
       </c>
       <c r="K70" t="n">
-        <v>-23.24</v>
+        <v>-10.61</v>
       </c>
       <c r="L70" t="n">
-        <v>527.64</v>
+        <v>240.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>72.51000000000001</v>
+        <v>39.07</v>
       </c>
       <c r="K71" t="n">
-        <v>382.43</v>
+        <v>206.06</v>
       </c>
       <c r="L71" t="n">
-        <v>389.24</v>
+        <v>209.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>166.77</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>307.02</v>
+        <v>162.33</v>
       </c>
       <c r="L72" t="n">
-        <v>349.39</v>
+        <v>184.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-19.19</v>
+        <v>-10.15</v>
       </c>
       <c r="K73" t="n">
-        <v>-287.36</v>
+        <v>-152.01</v>
       </c>
       <c r="L73" t="n">
-        <v>288</v>
+        <v>152.35</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-139.9</v>
+        <v>-64.37</v>
       </c>
       <c r="K74" t="n">
-        <v>24.75</v>
+        <v>11.39</v>
       </c>
       <c r="L74" t="n">
-        <v>142.07</v>
+        <v>65.37</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>164.86</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>85.31999999999999</v>
+        <v>36.76</v>
       </c>
       <c r="L75" t="n">
-        <v>185.63</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-146.25</v>
+        <v>-58.45</v>
       </c>
       <c r="K76" t="n">
-        <v>-119.84</v>
+        <v>-47.9</v>
       </c>
       <c r="L76" t="n">
-        <v>189.08</v>
+        <v>75.56999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>165.8</v>
+        <v>69.2</v>
       </c>
       <c r="K77" t="n">
-        <v>-58.03</v>
+        <v>-24.22</v>
       </c>
       <c r="L77" t="n">
-        <v>175.66</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-34.26</v>
+        <v>-14.43</v>
       </c>
       <c r="K78" t="n">
-        <v>-181.77</v>
+        <v>-76.56999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>184.97</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-32.07</v>
+        <v>-15.05</v>
       </c>
       <c r="K79" t="n">
-        <v>-154.06</v>
+        <v>-72.28</v>
       </c>
       <c r="L79" t="n">
-        <v>157.37</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-270</v>
+        <v>-133.5</v>
       </c>
       <c r="K80" t="n">
-        <v>-12.39</v>
+        <v>-6.12</v>
       </c>
       <c r="L80" t="n">
-        <v>270.29</v>
+        <v>133.64</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-404.09</v>
+        <v>-192.95</v>
       </c>
       <c r="K81" t="n">
-        <v>-130.81</v>
+        <v>-62.46</v>
       </c>
       <c r="L81" t="n">
-        <v>424.74</v>
+        <v>202.81</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-199.42</v>
+        <v>-95.18000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>334.23</v>
+        <v>159.52</v>
       </c>
       <c r="L82" t="n">
-        <v>389.2</v>
+        <v>185.76</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>173.64</v>
+        <v>76.7</v>
       </c>
       <c r="K83" t="n">
-        <v>369.85</v>
+        <v>163.36</v>
       </c>
       <c r="L83" t="n">
-        <v>408.59</v>
+        <v>180.47</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>148.29</v>
+        <v>65.31</v>
       </c>
       <c r="K84" t="n">
-        <v>382.91</v>
+        <v>168.65</v>
       </c>
       <c r="L84" t="n">
-        <v>410.63</v>
+        <v>180.86</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>166.66</v>
+        <v>72.72</v>
       </c>
       <c r="K85" t="n">
-        <v>519.51</v>
+        <v>226.69</v>
       </c>
       <c r="L85" t="n">
-        <v>545.59</v>
+        <v>238.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-215.87</v>
+        <v>-114.66</v>
       </c>
       <c r="K86" t="n">
-        <v>421.16</v>
+        <v>223.7</v>
       </c>
       <c r="L86" t="n">
-        <v>473.26</v>
+        <v>251.37</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-341.95</v>
+        <v>-187.17</v>
       </c>
       <c r="K87" t="n">
-        <v>-192.03</v>
+        <v>-105.11</v>
       </c>
       <c r="L87" t="n">
-        <v>392.19</v>
+        <v>214.66</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>113.93</v>
+        <v>62.67</v>
       </c>
       <c r="K88" t="n">
-        <v>-173.17</v>
+        <v>-95.25</v>
       </c>
       <c r="L88" t="n">
-        <v>207.28</v>
+        <v>114.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-85.15000000000001</v>
+        <v>-79.87</v>
       </c>
       <c r="K14" t="n">
-        <v>36.11</v>
+        <v>33.86</v>
       </c>
       <c r="L14" t="n">
-        <v>92.48999999999999</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.31999999999999</v>
+        <v>-81.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.73</v>
+        <v>-21.6</v>
       </c>
       <c r="L15" t="n">
-        <v>88.3</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>31.78</v>
+        <v>32.76</v>
       </c>
       <c r="K16" t="n">
-        <v>-37.39</v>
+        <v>-38.53</v>
       </c>
       <c r="L16" t="n">
-        <v>49.07</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>99.47</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-47.31</v>
+        <v>-44.59</v>
       </c>
       <c r="L17" t="n">
-        <v>110.15</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>105.59</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>85.01000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="L18" t="n">
-        <v>135.56</v>
+        <v>126.4</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>38.98</v>
+        <v>37.3</v>
       </c>
       <c r="K19" t="n">
-        <v>98.95999999999999</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>106.36</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>11.24</v>
+        <v>11.33</v>
       </c>
       <c r="K20" t="n">
-        <v>94.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>94.88</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>129.06</v>
+        <v>126.74</v>
       </c>
       <c r="K21" t="n">
-        <v>34.21</v>
+        <v>33.59</v>
       </c>
       <c r="L21" t="n">
-        <v>133.51</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>45.93</v>
+        <v>45.92</v>
       </c>
       <c r="K22" t="n">
-        <v>96.61</v>
+        <v>96.58</v>
       </c>
       <c r="L22" t="n">
-        <v>106.97</v>
+        <v>106.94</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-172.33</v>
+        <v>-167.46</v>
       </c>
       <c r="K23" t="n">
-        <v>102.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>200.51</v>
+        <v>194.85</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-171.76</v>
+        <v>-168.4</v>
       </c>
       <c r="K24" t="n">
-        <v>-47.76</v>
+        <v>-46.83</v>
       </c>
       <c r="L24" t="n">
-        <v>178.28</v>
+        <v>174.79</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-153.24</v>
+        <v>-152.9</v>
       </c>
       <c r="K25" t="n">
-        <v>19.23</v>
+        <v>19.19</v>
       </c>
       <c r="L25" t="n">
-        <v>154.44</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>171.72</v>
+        <v>177.31</v>
       </c>
       <c r="K26" t="n">
-        <v>207.12</v>
+        <v>213.85</v>
       </c>
       <c r="L26" t="n">
-        <v>269.05</v>
+        <v>277.8</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-166.1</v>
+        <v>-177.08</v>
       </c>
       <c r="K27" t="n">
-        <v>58.33</v>
+        <v>62.18</v>
       </c>
       <c r="L27" t="n">
-        <v>176.04</v>
+        <v>187.68</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-13.44</v>
+        <v>-13.68</v>
       </c>
       <c r="K28" t="n">
-        <v>207.57</v>
+        <v>211.4</v>
       </c>
       <c r="L28" t="n">
-        <v>208</v>
+        <v>211.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>36.37</v>
+        <v>37.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-34.88</v>
+        <v>-35.73</v>
       </c>
       <c r="L29" t="n">
-        <v>50.39</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.28</v>
+        <v>-3.12</v>
       </c>
       <c r="K30" t="n">
-        <v>-83.8</v>
+        <v>-79.62</v>
       </c>
       <c r="L30" t="n">
-        <v>83.87</v>
+        <v>79.68000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>87.84</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-30.28</v>
+        <v>-28.56</v>
       </c>
       <c r="L31" t="n">
-        <v>92.92</v>
+        <v>87.64</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.52</v>
+        <v>-4.32</v>
       </c>
       <c r="K32" t="n">
-        <v>-93.98999999999999</v>
+        <v>-89.77</v>
       </c>
       <c r="L32" t="n">
-        <v>94.09999999999999</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-20.17</v>
+        <v>-20.23</v>
       </c>
       <c r="K33" t="n">
-        <v>59.3</v>
+        <v>59.48</v>
       </c>
       <c r="L33" t="n">
-        <v>62.64</v>
+        <v>62.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>74.77</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-33.98</v>
+        <v>-31.36</v>
       </c>
       <c r="L34" t="n">
-        <v>82.13</v>
+        <v>75.79000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-47.38</v>
+        <v>-45.94</v>
       </c>
       <c r="K35" t="n">
-        <v>-134.11</v>
+        <v>-130.04</v>
       </c>
       <c r="L35" t="n">
-        <v>142.24</v>
+        <v>137.92</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-132.49</v>
+        <v>-129.31</v>
       </c>
       <c r="K36" t="n">
-        <v>40.73</v>
+        <v>39.75</v>
       </c>
       <c r="L36" t="n">
-        <v>138.6</v>
+        <v>135.28</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-61.63</v>
+        <v>-60.73</v>
       </c>
       <c r="K37" t="n">
-        <v>110.92</v>
+        <v>109.3</v>
       </c>
       <c r="L37" t="n">
-        <v>126.89</v>
+        <v>125.04</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-40.66</v>
+        <v>-43.25</v>
       </c>
       <c r="K38" t="n">
-        <v>-89.08</v>
+        <v>-94.76000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>97.92</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-91.39</v>
+        <v>-97.72</v>
       </c>
       <c r="K39" t="n">
-        <v>-37.6</v>
+        <v>-40.2</v>
       </c>
       <c r="L39" t="n">
-        <v>98.81999999999999</v>
+        <v>105.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-115.62</v>
+        <v>-120.7</v>
       </c>
       <c r="K40" t="n">
-        <v>126.81</v>
+        <v>132.39</v>
       </c>
       <c r="L40" t="n">
-        <v>171.6</v>
+        <v>179.15</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>67.61</v>
+        <v>75.55</v>
       </c>
       <c r="K41" t="n">
-        <v>290.3</v>
+        <v>324.4</v>
       </c>
       <c r="L41" t="n">
-        <v>298.06</v>
+        <v>333.08</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-203.04</v>
+        <v>-204.52</v>
       </c>
       <c r="K42" t="n">
-        <v>160.37</v>
+        <v>161.54</v>
       </c>
       <c r="L42" t="n">
-        <v>258.73</v>
+        <v>260.62</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>345.1</v>
+        <v>344.5</v>
       </c>
       <c r="K43" t="n">
-        <v>51.42</v>
+        <v>51.33</v>
       </c>
       <c r="L43" t="n">
-        <v>348.91</v>
+        <v>348.3</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>22.93</v>
+        <v>21.16</v>
       </c>
       <c r="K44" t="n">
-        <v>-81.55</v>
+        <v>-75.25</v>
       </c>
       <c r="L44" t="n">
-        <v>84.70999999999999</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.82</v>
+        <v>-40.57</v>
       </c>
       <c r="K45" t="n">
-        <v>52.53</v>
+        <v>50.96</v>
       </c>
       <c r="L45" t="n">
-        <v>67.15000000000001</v>
+        <v>65.14</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.36</v>
+        <v>-23.82</v>
       </c>
       <c r="K46" t="n">
-        <v>47.34</v>
+        <v>48.27</v>
       </c>
       <c r="L46" t="n">
-        <v>52.79</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="K47" t="n">
-        <v>-91.43000000000001</v>
+        <v>-88.12</v>
       </c>
       <c r="L47" t="n">
-        <v>91.5</v>
+        <v>88.18000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-7.97</v>
+        <v>-7.92</v>
       </c>
       <c r="K48" t="n">
-        <v>71.09</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>71.54000000000001</v>
+        <v>71.12</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>97.11</v>
+        <v>91.92</v>
       </c>
       <c r="K49" t="n">
-        <v>13.36</v>
+        <v>12.65</v>
       </c>
       <c r="L49" t="n">
-        <v>98.02</v>
+        <v>92.79000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>165.77</v>
+        <v>159.9</v>
       </c>
       <c r="K50" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="L50" t="n">
-        <v>165.77</v>
+        <v>159.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.3</v>
+        <v>-62.24</v>
       </c>
       <c r="K51" t="n">
-        <v>-119.62</v>
+        <v>-117.62</v>
       </c>
       <c r="L51" t="n">
-        <v>135.34</v>
+        <v>133.07</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>157.04</v>
+        <v>150.52</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.94</v>
+        <v>-45.95</v>
       </c>
       <c r="L52" t="n">
-        <v>164.19</v>
+        <v>157.38</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>216.73</v>
+        <v>213.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-28.36</v>
+        <v>-27.9</v>
       </c>
       <c r="L53" t="n">
-        <v>218.58</v>
+        <v>215.03</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-176.71</v>
+        <v>-175.98</v>
       </c>
       <c r="K54" t="n">
-        <v>9.359999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="L54" t="n">
-        <v>176.96</v>
+        <v>176.22</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>104.98</v>
+        <v>112.19</v>
       </c>
       <c r="K55" t="n">
-        <v>-116.02</v>
+        <v>-124</v>
       </c>
       <c r="L55" t="n">
-        <v>156.47</v>
+        <v>167.22</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>97.59</v>
+        <v>102.38</v>
       </c>
       <c r="K56" t="n">
-        <v>335.47</v>
+        <v>351.93</v>
       </c>
       <c r="L56" t="n">
-        <v>349.37</v>
+        <v>366.52</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-38.84</v>
+        <v>-42.49</v>
       </c>
       <c r="K57" t="n">
-        <v>203.58</v>
+        <v>222.67</v>
       </c>
       <c r="L57" t="n">
-        <v>207.25</v>
+        <v>226.69</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>343.52</v>
+        <v>340.68</v>
       </c>
       <c r="K58" t="n">
-        <v>-81.11</v>
+        <v>-80.44</v>
       </c>
       <c r="L58" t="n">
-        <v>352.96</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>47.93</v>
+        <v>45.12</v>
       </c>
       <c r="K59" t="n">
-        <v>70.02</v>
+        <v>65.92</v>
       </c>
       <c r="L59" t="n">
-        <v>84.84999999999999</v>
+        <v>79.88</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>38.77</v>
+        <v>37.56</v>
       </c>
       <c r="K60" t="n">
-        <v>59.64</v>
+        <v>57.79</v>
       </c>
       <c r="L60" t="n">
-        <v>71.13</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-38.98</v>
+        <v>-35.6</v>
       </c>
       <c r="K61" t="n">
-        <v>-82.66</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>91.39</v>
+        <v>83.47</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>34.59</v>
+        <v>32.86</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.3</v>
+        <v>-11.68</v>
       </c>
       <c r="L62" t="n">
-        <v>36.72</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>68.8</v>
+        <v>67.56</v>
       </c>
       <c r="K63" t="n">
-        <v>31.38</v>
+        <v>30.82</v>
       </c>
       <c r="L63" t="n">
-        <v>75.62</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-74.34</v>
+        <v>-72.67</v>
       </c>
       <c r="K64" t="n">
-        <v>8.130000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="L64" t="n">
-        <v>74.78</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-75.83</v>
+        <v>-78.18000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-62.06</v>
+        <v>-63.99</v>
       </c>
       <c r="L65" t="n">
-        <v>97.98999999999999</v>
+        <v>101.03</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>205.87</v>
+        <v>194.44</v>
       </c>
       <c r="K66" t="n">
-        <v>11.04</v>
+        <v>10.42</v>
       </c>
       <c r="L66" t="n">
-        <v>206.17</v>
+        <v>194.72</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-34.5</v>
+        <v>-34.84</v>
       </c>
       <c r="K67" t="n">
-        <v>100.49</v>
+        <v>101.46</v>
       </c>
       <c r="L67" t="n">
-        <v>106.25</v>
+        <v>107.28</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-146.74</v>
+        <v>-150.39</v>
       </c>
       <c r="K68" t="n">
-        <v>255.52</v>
+        <v>261.89</v>
       </c>
       <c r="L68" t="n">
-        <v>294.66</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>217.93</v>
+        <v>211.61</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.99</v>
+        <v>-2.9</v>
       </c>
       <c r="L69" t="n">
-        <v>217.95</v>
+        <v>211.63</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>240.57</v>
+        <v>234.15</v>
       </c>
       <c r="K70" t="n">
-        <v>-10.61</v>
+        <v>-10.32</v>
       </c>
       <c r="L70" t="n">
-        <v>240.81</v>
+        <v>234.38</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>39.07</v>
+        <v>41.41</v>
       </c>
       <c r="K71" t="n">
-        <v>206.06</v>
+        <v>218.37</v>
       </c>
       <c r="L71" t="n">
-        <v>209.73</v>
+        <v>222.26</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>88.18000000000001</v>
+        <v>103.82</v>
       </c>
       <c r="K72" t="n">
-        <v>162.33</v>
+        <v>191.13</v>
       </c>
       <c r="L72" t="n">
-        <v>184.74</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-10.15</v>
+        <v>-12.04</v>
       </c>
       <c r="K73" t="n">
-        <v>-152.01</v>
+        <v>-180.24</v>
       </c>
       <c r="L73" t="n">
-        <v>152.35</v>
+        <v>180.64</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-64.37</v>
+        <v>-63.24</v>
       </c>
       <c r="K74" t="n">
-        <v>11.39</v>
+        <v>11.19</v>
       </c>
       <c r="L74" t="n">
-        <v>65.37</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>71.04000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="K75" t="n">
-        <v>36.76</v>
+        <v>35.13</v>
       </c>
       <c r="L75" t="n">
-        <v>79.98</v>
+        <v>76.43000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-58.45</v>
+        <v>-55.65</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.9</v>
+        <v>-45.6</v>
       </c>
       <c r="L76" t="n">
-        <v>75.56999999999999</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>69.2</v>
+        <v>65.95</v>
       </c>
       <c r="K77" t="n">
-        <v>-24.22</v>
+        <v>-23.08</v>
       </c>
       <c r="L77" t="n">
-        <v>73.31</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-14.43</v>
+        <v>-13.31</v>
       </c>
       <c r="K78" t="n">
-        <v>-76.56999999999999</v>
+        <v>-70.64</v>
       </c>
       <c r="L78" t="n">
-        <v>77.92</v>
+        <v>71.88</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.05</v>
+        <v>-15.01</v>
       </c>
       <c r="K79" t="n">
-        <v>-72.28</v>
+        <v>-72.11</v>
       </c>
       <c r="L79" t="n">
-        <v>73.83</v>
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-133.5</v>
+        <v>-131.36</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.12</v>
+        <v>-6.03</v>
       </c>
       <c r="L80" t="n">
-        <v>133.64</v>
+        <v>131.49</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-192.95</v>
+        <v>-182.2</v>
       </c>
       <c r="K81" t="n">
-        <v>-62.46</v>
+        <v>-58.98</v>
       </c>
       <c r="L81" t="n">
-        <v>202.81</v>
+        <v>191.51</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-95.18000000000001</v>
+        <v>-90.52</v>
       </c>
       <c r="K82" t="n">
-        <v>159.52</v>
+        <v>151.71</v>
       </c>
       <c r="L82" t="n">
-        <v>185.76</v>
+        <v>176.66</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>76.7</v>
+        <v>81.11</v>
       </c>
       <c r="K83" t="n">
-        <v>163.36</v>
+        <v>172.76</v>
       </c>
       <c r="L83" t="n">
-        <v>180.47</v>
+        <v>190.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>65.31</v>
+        <v>67.61</v>
       </c>
       <c r="K84" t="n">
-        <v>168.65</v>
+        <v>174.59</v>
       </c>
       <c r="L84" t="n">
-        <v>180.86</v>
+        <v>187.23</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>72.72</v>
+        <v>73.41</v>
       </c>
       <c r="K85" t="n">
-        <v>226.69</v>
+        <v>228.82</v>
       </c>
       <c r="L85" t="n">
-        <v>238.07</v>
+        <v>240.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-114.66</v>
+        <v>-130.82</v>
       </c>
       <c r="K86" t="n">
-        <v>223.7</v>
+        <v>255.22</v>
       </c>
       <c r="L86" t="n">
-        <v>251.37</v>
+        <v>286.8</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-187.17</v>
+        <v>-192.5</v>
       </c>
       <c r="K87" t="n">
-        <v>-105.11</v>
+        <v>-108.1</v>
       </c>
       <c r="L87" t="n">
-        <v>214.66</v>
+        <v>220.78</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>62.67</v>
+        <v>70.75</v>
       </c>
       <c r="K88" t="n">
-        <v>-95.25</v>
+        <v>-107.54</v>
       </c>
       <c r="L88" t="n">
-        <v>114.02</v>
+        <v>128.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-79.87</v>
+        <v>-76.19</v>
       </c>
       <c r="K14" t="n">
-        <v>33.86</v>
+        <v>32.31</v>
       </c>
       <c r="L14" t="n">
-        <v>86.75</v>
+        <v>82.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-81.09</v>
+        <v>-78.76000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.6</v>
+        <v>-20.98</v>
       </c>
       <c r="L15" t="n">
-        <v>83.92</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>32.76</v>
+        <v>34.84</v>
       </c>
       <c r="K16" t="n">
-        <v>-38.53</v>
+        <v>-40.98</v>
       </c>
       <c r="L16" t="n">
-        <v>50.57</v>
+        <v>53.79</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>93.76000000000001</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-44.59</v>
+        <v>-43.18</v>
       </c>
       <c r="L17" t="n">
-        <v>103.82</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>98.45999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="K18" t="n">
-        <v>79.27</v>
+        <v>74.23</v>
       </c>
       <c r="L18" t="n">
-        <v>126.4</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>37.3</v>
+        <v>36.09</v>
       </c>
       <c r="K19" t="n">
-        <v>94.68000000000001</v>
+        <v>91.61</v>
       </c>
       <c r="L19" t="n">
-        <v>101.76</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>11.33</v>
+        <v>11.49</v>
       </c>
       <c r="K20" t="n">
-        <v>94.95999999999999</v>
+        <v>96.31</v>
       </c>
       <c r="L20" t="n">
-        <v>95.63</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>126.74</v>
+        <v>125.04</v>
       </c>
       <c r="K21" t="n">
-        <v>33.59</v>
+        <v>33.14</v>
       </c>
       <c r="L21" t="n">
-        <v>131.12</v>
+        <v>129.36</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>45.92</v>
+        <v>46.37</v>
       </c>
       <c r="K22" t="n">
-        <v>96.58</v>
+        <v>97.55</v>
       </c>
       <c r="L22" t="n">
-        <v>106.94</v>
+        <v>108.01</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-167.46</v>
+        <v>-161.62</v>
       </c>
       <c r="K23" t="n">
-        <v>99.59999999999999</v>
+        <v>96.13</v>
       </c>
       <c r="L23" t="n">
-        <v>194.85</v>
+        <v>188.05</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-168.4</v>
+        <v>-164.47</v>
       </c>
       <c r="K24" t="n">
-        <v>-46.83</v>
+        <v>-45.73</v>
       </c>
       <c r="L24" t="n">
-        <v>174.79</v>
+        <v>170.71</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-152.9</v>
+        <v>-152.43</v>
       </c>
       <c r="K25" t="n">
-        <v>19.19</v>
+        <v>19.13</v>
       </c>
       <c r="L25" t="n">
-        <v>154.1</v>
+        <v>153.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>177.31</v>
+        <v>175.03</v>
       </c>
       <c r="K26" t="n">
-        <v>213.85</v>
+        <v>211.11</v>
       </c>
       <c r="L26" t="n">
-        <v>277.8</v>
+        <v>274.23</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-177.08</v>
+        <v>-183.06</v>
       </c>
       <c r="K27" t="n">
-        <v>62.18</v>
+        <v>64.28</v>
       </c>
       <c r="L27" t="n">
-        <v>187.68</v>
+        <v>194.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-13.68</v>
+        <v>-13.67</v>
       </c>
       <c r="K28" t="n">
-        <v>211.4</v>
+        <v>211.22</v>
       </c>
       <c r="L28" t="n">
-        <v>211.85</v>
+        <v>211.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>37.26</v>
+        <v>39.04</v>
       </c>
       <c r="K29" t="n">
-        <v>-35.73</v>
+        <v>-37.44</v>
       </c>
       <c r="L29" t="n">
-        <v>51.62</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.12</v>
+        <v>-3.04</v>
       </c>
       <c r="K30" t="n">
-        <v>-79.62</v>
+        <v>-77.69</v>
       </c>
       <c r="L30" t="n">
-        <v>79.68000000000001</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>82.84999999999999</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.56</v>
+        <v>-27.16</v>
       </c>
       <c r="L31" t="n">
-        <v>87.64</v>
+        <v>83.34</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.32</v>
+        <v>-4.23</v>
       </c>
       <c r="K32" t="n">
-        <v>-89.77</v>
+        <v>-87.81999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>89.88</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-20.23</v>
+        <v>-21.09</v>
       </c>
       <c r="K33" t="n">
-        <v>59.48</v>
+        <v>61.99</v>
       </c>
       <c r="L33" t="n">
-        <v>62.83</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>68.98999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="K34" t="n">
-        <v>-31.36</v>
+        <v>-31.25</v>
       </c>
       <c r="L34" t="n">
-        <v>75.79000000000001</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-45.94</v>
+        <v>-44.8</v>
       </c>
       <c r="K35" t="n">
-        <v>-130.04</v>
+        <v>-126.82</v>
       </c>
       <c r="L35" t="n">
-        <v>137.92</v>
+        <v>134.51</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-129.31</v>
+        <v>-127.38</v>
       </c>
       <c r="K36" t="n">
-        <v>39.75</v>
+        <v>39.16</v>
       </c>
       <c r="L36" t="n">
-        <v>135.28</v>
+        <v>133.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-60.73</v>
+        <v>-60.19</v>
       </c>
       <c r="K37" t="n">
-        <v>109.3</v>
+        <v>108.34</v>
       </c>
       <c r="L37" t="n">
-        <v>125.04</v>
+        <v>123.93</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-43.25</v>
+        <v>-46.09</v>
       </c>
       <c r="K38" t="n">
-        <v>-94.76000000000001</v>
+        <v>-100.98</v>
       </c>
       <c r="L38" t="n">
-        <v>104.16</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-97.72</v>
+        <v>-104.65</v>
       </c>
       <c r="K39" t="n">
-        <v>-40.2</v>
+        <v>-43.06</v>
       </c>
       <c r="L39" t="n">
-        <v>105.66</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-120.7</v>
+        <v>-120.31</v>
       </c>
       <c r="K40" t="n">
-        <v>132.39</v>
+        <v>131.96</v>
       </c>
       <c r="L40" t="n">
-        <v>179.15</v>
+        <v>178.57</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>75.55</v>
+        <v>75.03</v>
       </c>
       <c r="K41" t="n">
-        <v>324.4</v>
+        <v>322.16</v>
       </c>
       <c r="L41" t="n">
-        <v>333.08</v>
+        <v>330.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-204.52</v>
+        <v>-199.06</v>
       </c>
       <c r="K42" t="n">
-        <v>161.54</v>
+        <v>157.22</v>
       </c>
       <c r="L42" t="n">
-        <v>260.62</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>344.5</v>
+        <v>325.11</v>
       </c>
       <c r="K43" t="n">
-        <v>51.33</v>
+        <v>48.44</v>
       </c>
       <c r="L43" t="n">
-        <v>348.3</v>
+        <v>328.7</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>21.16</v>
+        <v>20.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-75.25</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>78.17</v>
+        <v>76.02</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-40.57</v>
+        <v>-41.05</v>
       </c>
       <c r="K45" t="n">
-        <v>50.96</v>
+        <v>51.55</v>
       </c>
       <c r="L45" t="n">
-        <v>65.14</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.82</v>
+        <v>-24.99</v>
       </c>
       <c r="K46" t="n">
-        <v>48.27</v>
+        <v>50.65</v>
       </c>
       <c r="L46" t="n">
-        <v>53.83</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="K47" t="n">
-        <v>-88.12</v>
+        <v>-87.43000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>88.18000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-7.92</v>
+        <v>-8.09</v>
       </c>
       <c r="K48" t="n">
-        <v>70.68000000000001</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>71.12</v>
+        <v>72.69</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>91.92</v>
+        <v>89.87</v>
       </c>
       <c r="K49" t="n">
-        <v>12.65</v>
+        <v>12.36</v>
       </c>
       <c r="L49" t="n">
-        <v>92.79000000000001</v>
+        <v>90.72</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>159.9</v>
+        <v>154.76</v>
       </c>
       <c r="K50" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="L50" t="n">
-        <v>159.9</v>
+        <v>154.76</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-62.24</v>
+        <v>-61.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.62</v>
+        <v>-117.1</v>
       </c>
       <c r="L51" t="n">
-        <v>133.07</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>150.52</v>
+        <v>144.97</v>
       </c>
       <c r="K52" t="n">
-        <v>-45.95</v>
+        <v>-44.26</v>
       </c>
       <c r="L52" t="n">
-        <v>157.38</v>
+        <v>151.57</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>213.21</v>
+        <v>207.05</v>
       </c>
       <c r="K53" t="n">
-        <v>-27.9</v>
+        <v>-27.1</v>
       </c>
       <c r="L53" t="n">
-        <v>215.03</v>
+        <v>208.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-175.98</v>
+        <v>-173.92</v>
       </c>
       <c r="K54" t="n">
-        <v>9.32</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>176.22</v>
+        <v>174.16</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>112.19</v>
+        <v>113.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-124</v>
+        <v>-125.36</v>
       </c>
       <c r="L55" t="n">
-        <v>167.22</v>
+        <v>169.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>102.38</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>351.93</v>
+        <v>337.76</v>
       </c>
       <c r="L56" t="n">
-        <v>366.52</v>
+        <v>351.76</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-42.49</v>
+        <v>-43.68</v>
       </c>
       <c r="K57" t="n">
-        <v>222.67</v>
+        <v>228.95</v>
       </c>
       <c r="L57" t="n">
-        <v>226.69</v>
+        <v>233.08</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>340.68</v>
+        <v>324.2</v>
       </c>
       <c r="K58" t="n">
-        <v>-80.44</v>
+        <v>-76.55</v>
       </c>
       <c r="L58" t="n">
-        <v>350.05</v>
+        <v>333.12</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>45.12</v>
+        <v>43.68</v>
       </c>
       <c r="K59" t="n">
-        <v>65.92</v>
+        <v>63.8</v>
       </c>
       <c r="L59" t="n">
-        <v>79.88</v>
+        <v>77.31999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>37.56</v>
+        <v>37.2</v>
       </c>
       <c r="K60" t="n">
-        <v>57.79</v>
+        <v>57.23</v>
       </c>
       <c r="L60" t="n">
-        <v>68.92</v>
+        <v>68.26000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-35.6</v>
+        <v>-34.28</v>
       </c>
       <c r="K61" t="n">
-        <v>-75.48999999999999</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>83.47</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>32.86</v>
+        <v>35.95</v>
       </c>
       <c r="K62" t="n">
-        <v>-11.68</v>
+        <v>-12.78</v>
       </c>
       <c r="L62" t="n">
-        <v>34.88</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>67.56</v>
+        <v>68.13</v>
       </c>
       <c r="K63" t="n">
-        <v>30.82</v>
+        <v>31.08</v>
       </c>
       <c r="L63" t="n">
-        <v>74.25</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-72.67</v>
+        <v>-73.58</v>
       </c>
       <c r="K64" t="n">
-        <v>7.94</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>73.09999999999999</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-78.18000000000001</v>
+        <v>-82.59</v>
       </c>
       <c r="K65" t="n">
-        <v>-63.99</v>
+        <v>-67.59</v>
       </c>
       <c r="L65" t="n">
-        <v>101.03</v>
+        <v>106.72</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>194.44</v>
+        <v>186.29</v>
       </c>
       <c r="K66" t="n">
-        <v>10.42</v>
+        <v>9.99</v>
       </c>
       <c r="L66" t="n">
-        <v>194.72</v>
+        <v>186.56</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-34.84</v>
+        <v>-35.45</v>
       </c>
       <c r="K67" t="n">
-        <v>101.46</v>
+        <v>103.25</v>
       </c>
       <c r="L67" t="n">
-        <v>107.28</v>
+        <v>109.17</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-150.39</v>
+        <v>-143.41</v>
       </c>
       <c r="K68" t="n">
-        <v>261.89</v>
+        <v>249.73</v>
       </c>
       <c r="L68" t="n">
-        <v>302</v>
+        <v>287.98</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>211.61</v>
+        <v>202.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.9</v>
+        <v>-2.78</v>
       </c>
       <c r="L69" t="n">
-        <v>211.63</v>
+        <v>202.44</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>234.15</v>
+        <v>224.48</v>
       </c>
       <c r="K70" t="n">
-        <v>-10.32</v>
+        <v>-9.9</v>
       </c>
       <c r="L70" t="n">
-        <v>234.38</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>41.41</v>
+        <v>41.96</v>
       </c>
       <c r="K71" t="n">
-        <v>218.37</v>
+        <v>221.31</v>
       </c>
       <c r="L71" t="n">
-        <v>222.26</v>
+        <v>225.25</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>103.82</v>
+        <v>109.78</v>
       </c>
       <c r="K72" t="n">
-        <v>191.13</v>
+        <v>202.1</v>
       </c>
       <c r="L72" t="n">
-        <v>217.5</v>
+        <v>229.99</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-12.04</v>
+        <v>-12.96</v>
       </c>
       <c r="K73" t="n">
-        <v>-180.24</v>
+        <v>-194.09</v>
       </c>
       <c r="L73" t="n">
-        <v>180.64</v>
+        <v>194.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-63.24</v>
+        <v>-63.42</v>
       </c>
       <c r="K74" t="n">
-        <v>11.19</v>
+        <v>11.22</v>
       </c>
       <c r="L74" t="n">
-        <v>64.22</v>
+        <v>64.41</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>67.88</v>
+        <v>66.62</v>
       </c>
       <c r="K75" t="n">
-        <v>35.13</v>
+        <v>34.48</v>
       </c>
       <c r="L75" t="n">
-        <v>76.43000000000001</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.65</v>
+        <v>-55.1</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.6</v>
+        <v>-45.15</v>
       </c>
       <c r="L76" t="n">
-        <v>71.95</v>
+        <v>71.23</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>65.95</v>
+        <v>67.45</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.08</v>
+        <v>-23.61</v>
       </c>
       <c r="L77" t="n">
-        <v>69.87</v>
+        <v>71.47</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-13.31</v>
+        <v>-13.7</v>
       </c>
       <c r="K78" t="n">
-        <v>-70.64</v>
+        <v>-72.68000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>71.88</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.01</v>
+        <v>-15.31</v>
       </c>
       <c r="K79" t="n">
-        <v>-72.11</v>
+        <v>-73.54000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>73.65000000000001</v>
+        <v>75.12</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-131.36</v>
+        <v>-130.03</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.03</v>
+        <v>-5.97</v>
       </c>
       <c r="L80" t="n">
-        <v>131.49</v>
+        <v>130.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-182.2</v>
+        <v>-174.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-58.98</v>
+        <v>-56.4</v>
       </c>
       <c r="L81" t="n">
-        <v>191.51</v>
+        <v>183.12</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.52</v>
+        <v>-86.76000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>151.71</v>
+        <v>145.4</v>
       </c>
       <c r="L82" t="n">
-        <v>176.66</v>
+        <v>169.32</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>81.11</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>172.76</v>
+        <v>172.5</v>
       </c>
       <c r="L83" t="n">
-        <v>190.86</v>
+        <v>190.57</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>67.61</v>
+        <v>67.58</v>
       </c>
       <c r="K84" t="n">
-        <v>174.59</v>
+        <v>174.51</v>
       </c>
       <c r="L84" t="n">
-        <v>187.23</v>
+        <v>187.14</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>73.41</v>
+        <v>70.06</v>
       </c>
       <c r="K85" t="n">
-        <v>228.82</v>
+        <v>218.4</v>
       </c>
       <c r="L85" t="n">
-        <v>240.31</v>
+        <v>229.37</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-130.82</v>
+        <v>-132.8</v>
       </c>
       <c r="K86" t="n">
-        <v>255.22</v>
+        <v>259.1</v>
       </c>
       <c r="L86" t="n">
-        <v>286.8</v>
+        <v>291.16</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-192.5</v>
+        <v>-191.62</v>
       </c>
       <c r="K87" t="n">
-        <v>-108.1</v>
+        <v>-107.61</v>
       </c>
       <c r="L87" t="n">
-        <v>220.78</v>
+        <v>219.77</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>70.75</v>
+        <v>78.03</v>
       </c>
       <c r="K88" t="n">
-        <v>-107.54</v>
+        <v>-118.6</v>
       </c>
       <c r="L88" t="n">
-        <v>128.73</v>
+        <v>141.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -628,25 +628,25 @@
         <v>4.1</v>
       </c>
       <c r="F14" t="n">
-        <v>10.98</v>
+        <v>10.58</v>
       </c>
       <c r="G14" t="n">
-        <v>330.7</v>
+        <v>343.3</v>
       </c>
       <c r="H14" t="n">
-        <v>81.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-76.19</v>
+        <v>-81.34</v>
       </c>
       <c r="K14" t="n">
-        <v>32.31</v>
+        <v>35.46</v>
       </c>
       <c r="L14" t="n">
-        <v>82.76000000000001</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>4.15</v>
       </c>
       <c r="F15" t="n">
-        <v>11.14</v>
+        <v>12.3</v>
       </c>
       <c r="G15" t="n">
-        <v>341.7</v>
+        <v>346.3</v>
       </c>
       <c r="H15" t="n">
-        <v>83.7</v>
+        <v>82.7</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-78.76000000000001</v>
+        <v>-85.48</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.98</v>
+        <v>-21.57</v>
       </c>
       <c r="L15" t="n">
-        <v>81.5</v>
+        <v>88.16</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>4.21</v>
       </c>
       <c r="F16" t="n">
-        <v>10.8</v>
+        <v>11.08</v>
       </c>
       <c r="G16" t="n">
-        <v>342.2</v>
+        <v>339.6</v>
       </c>
       <c r="H16" t="n">
-        <v>82.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>34.84</v>
+        <v>38.31</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.98</v>
+        <v>-43.87</v>
       </c>
       <c r="L16" t="n">
-        <v>53.79</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>4.38</v>
       </c>
       <c r="F17" t="n">
-        <v>10.03</v>
+        <v>10.22</v>
       </c>
       <c r="G17" t="n">
-        <v>340.3</v>
+        <v>324.2</v>
       </c>
       <c r="H17" t="n">
-        <v>87.7</v>
+        <v>82</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>90.79000000000001</v>
+        <v>91.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-43.18</v>
+        <v>-42.41</v>
       </c>
       <c r="L17" t="n">
-        <v>100.54</v>
+        <v>100.55</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.78</v>
       </c>
       <c r="F18" t="n">
-        <v>10.21</v>
+        <v>7.48</v>
       </c>
       <c r="G18" t="n">
-        <v>330.9</v>
+        <v>327.8</v>
       </c>
       <c r="H18" t="n">
-        <v>75.8</v>
+        <v>77.3</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>92.2</v>
+        <v>89.77</v>
       </c>
       <c r="K18" t="n">
-        <v>74.23</v>
+        <v>74.81</v>
       </c>
       <c r="L18" t="n">
-        <v>118.37</v>
+        <v>116.85</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.8</v>
       </c>
       <c r="F19" t="n">
-        <v>11.01</v>
+        <v>11.13</v>
       </c>
       <c r="G19" t="n">
-        <v>330.9</v>
+        <v>343.7</v>
       </c>
       <c r="H19" t="n">
-        <v>76.2</v>
+        <v>77.3</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>36.09</v>
+        <v>36.74</v>
       </c>
       <c r="K19" t="n">
-        <v>91.61</v>
+        <v>96.55</v>
       </c>
       <c r="L19" t="n">
-        <v>98.47</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>3.68</v>
       </c>
       <c r="F20" t="n">
-        <v>10.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>332.7</v>
+        <v>333.7</v>
       </c>
       <c r="H20" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>11.49</v>
+        <v>6.61</v>
       </c>
       <c r="K20" t="n">
-        <v>96.31</v>
+        <v>118.39</v>
       </c>
       <c r="L20" t="n">
-        <v>97</v>
+        <v>118.57</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>3.86</v>
       </c>
       <c r="F21" t="n">
-        <v>10.88</v>
+        <v>8.73</v>
       </c>
       <c r="G21" t="n">
-        <v>335.2</v>
+        <v>341.3</v>
       </c>
       <c r="H21" t="n">
-        <v>75.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>125.04</v>
+        <v>118.02</v>
       </c>
       <c r="K21" t="n">
-        <v>33.14</v>
+        <v>43.93</v>
       </c>
       <c r="L21" t="n">
-        <v>129.36</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>4.14</v>
       </c>
       <c r="F22" t="n">
-        <v>11.81</v>
+        <v>9.16</v>
       </c>
       <c r="G22" t="n">
-        <v>335.9</v>
+        <v>359.8</v>
       </c>
       <c r="H22" t="n">
-        <v>77.5</v>
+        <v>79.8</v>
       </c>
       <c r="I22" t="n">
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>46.37</v>
+        <v>49.82</v>
       </c>
       <c r="K22" t="n">
-        <v>97.55</v>
+        <v>112.23</v>
       </c>
       <c r="L22" t="n">
-        <v>108.01</v>
+        <v>122.79</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.44</v>
       </c>
       <c r="F23" t="n">
-        <v>10.74</v>
+        <v>7.07</v>
       </c>
       <c r="G23" t="n">
-        <v>334.6</v>
+        <v>338.4</v>
       </c>
       <c r="H23" t="n">
-        <v>82.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-161.62</v>
+        <v>-159.39</v>
       </c>
       <c r="K23" t="n">
-        <v>96.13</v>
+        <v>110.44</v>
       </c>
       <c r="L23" t="n">
-        <v>188.05</v>
+        <v>193.92</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>3.31</v>
       </c>
       <c r="F24" t="n">
-        <v>10.78</v>
+        <v>6.29</v>
       </c>
       <c r="G24" t="n">
-        <v>330.6</v>
+        <v>339.2</v>
       </c>
       <c r="H24" t="n">
-        <v>75.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-164.47</v>
+        <v>-167.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-45.73</v>
+        <v>-23.36</v>
       </c>
       <c r="L24" t="n">
-        <v>170.71</v>
+        <v>169.2</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>3.32</v>
       </c>
       <c r="F25" t="n">
-        <v>10.92</v>
+        <v>8.49</v>
       </c>
       <c r="G25" t="n">
-        <v>320.7</v>
+        <v>342</v>
       </c>
       <c r="H25" t="n">
-        <v>83.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-152.43</v>
+        <v>-169.88</v>
       </c>
       <c r="K25" t="n">
-        <v>19.13</v>
+        <v>50.93</v>
       </c>
       <c r="L25" t="n">
-        <v>153.62</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>4.16</v>
       </c>
       <c r="F26" t="n">
-        <v>10.41</v>
+        <v>8.84</v>
       </c>
       <c r="G26" t="n">
-        <v>336.8</v>
+        <v>331.8</v>
       </c>
       <c r="H26" t="n">
-        <v>76.2</v>
+        <v>80.2</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>175.03</v>
+        <v>145.6</v>
       </c>
       <c r="K26" t="n">
-        <v>211.11</v>
+        <v>224.07</v>
       </c>
       <c r="L26" t="n">
-        <v>274.23</v>
+        <v>267.22</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>3.95</v>
       </c>
       <c r="F27" t="n">
-        <v>9.890000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G27" t="n">
-        <v>329.4</v>
+        <v>321.4</v>
       </c>
       <c r="H27" t="n">
-        <v>87.7</v>
+        <v>76.5</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-183.06</v>
+        <v>-192.99</v>
       </c>
       <c r="K27" t="n">
-        <v>64.28</v>
+        <v>86.34</v>
       </c>
       <c r="L27" t="n">
-        <v>194.02</v>
+        <v>211.43</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.62</v>
       </c>
       <c r="F28" t="n">
-        <v>10.74</v>
+        <v>12.05</v>
       </c>
       <c r="G28" t="n">
-        <v>350</v>
+        <v>338.3</v>
       </c>
       <c r="H28" t="n">
-        <v>87.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-13.67</v>
+        <v>-34.55</v>
       </c>
       <c r="K28" t="n">
-        <v>211.22</v>
+        <v>256.86</v>
       </c>
       <c r="L28" t="n">
-        <v>211.66</v>
+        <v>259.17</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.89</v>
       </c>
       <c r="F29" t="n">
-        <v>10.78</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>333.9</v>
+        <v>339.1</v>
       </c>
       <c r="H29" t="n">
-        <v>79.2</v>
+        <v>78.7</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>39.04</v>
+        <v>43.35</v>
       </c>
       <c r="K29" t="n">
-        <v>-37.44</v>
+        <v>-40.1</v>
       </c>
       <c r="L29" t="n">
-        <v>54.09</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>4.31</v>
       </c>
       <c r="F30" t="n">
-        <v>11.15</v>
+        <v>11.21</v>
       </c>
       <c r="G30" t="n">
-        <v>355.3</v>
+        <v>346.6</v>
       </c>
       <c r="H30" t="n">
-        <v>80.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.04</v>
+        <v>-3.87</v>
       </c>
       <c r="K30" t="n">
-        <v>-77.69</v>
+        <v>-83.94</v>
       </c>
       <c r="L30" t="n">
-        <v>77.75</v>
+        <v>84.03</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>3.81</v>
       </c>
       <c r="F31" t="n">
-        <v>9.960000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="G31" t="n">
-        <v>345.8</v>
+        <v>322.7</v>
       </c>
       <c r="H31" t="n">
-        <v>71.8</v>
+        <v>84.7</v>
       </c>
       <c r="I31" t="n">
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>78.79000000000001</v>
+        <v>82.58</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.16</v>
+        <v>-28.32</v>
       </c>
       <c r="L31" t="n">
-        <v>83.34</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>4.2</v>
       </c>
       <c r="F32" t="n">
-        <v>10.65</v>
+        <v>12.16</v>
       </c>
       <c r="G32" t="n">
-        <v>328</v>
+        <v>336.5</v>
       </c>
       <c r="H32" t="n">
-        <v>83.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.23</v>
+        <v>-5.6</v>
       </c>
       <c r="K32" t="n">
-        <v>-87.81999999999999</v>
+        <v>-94.51000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>87.92</v>
+        <v>94.67</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>4.51</v>
       </c>
       <c r="F33" t="n">
-        <v>11.71</v>
+        <v>11.82</v>
       </c>
       <c r="G33" t="n">
-        <v>338.6</v>
+        <v>357.9</v>
       </c>
       <c r="H33" t="n">
-        <v>82.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.09</v>
+        <v>-21.92</v>
       </c>
       <c r="K33" t="n">
-        <v>61.99</v>
+        <v>75.94</v>
       </c>
       <c r="L33" t="n">
-        <v>65.48</v>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.95</v>
       </c>
       <c r="F34" t="n">
-        <v>10.5</v>
+        <v>12.19</v>
       </c>
       <c r="G34" t="n">
-        <v>339.3</v>
+        <v>333.6</v>
       </c>
       <c r="H34" t="n">
-        <v>78.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>68.75</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-31.25</v>
+        <v>-35</v>
       </c>
       <c r="L34" t="n">
-        <v>75.52</v>
+        <v>90.58</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>4.18</v>
       </c>
       <c r="F35" t="n">
-        <v>11.18</v>
+        <v>9.77</v>
       </c>
       <c r="G35" t="n">
-        <v>345.2</v>
+        <v>347.1</v>
       </c>
       <c r="H35" t="n">
-        <v>76.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-44.8</v>
+        <v>-50.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-126.82</v>
+        <v>-121.97</v>
       </c>
       <c r="L35" t="n">
-        <v>134.51</v>
+        <v>131.91</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>4.41</v>
       </c>
       <c r="F36" t="n">
-        <v>10.57</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>337.8</v>
+        <v>334.9</v>
       </c>
       <c r="H36" t="n">
-        <v>76.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-127.38</v>
+        <v>-126.57</v>
       </c>
       <c r="K36" t="n">
-        <v>39.16</v>
+        <v>49.27</v>
       </c>
       <c r="L36" t="n">
-        <v>133.27</v>
+        <v>135.82</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.92</v>
       </c>
       <c r="F37" t="n">
-        <v>10.79</v>
+        <v>10.5</v>
       </c>
       <c r="G37" t="n">
-        <v>330.9</v>
+        <v>339.5</v>
       </c>
       <c r="H37" t="n">
-        <v>84.8</v>
+        <v>77.3</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-60.19</v>
+        <v>-58.55</v>
       </c>
       <c r="K37" t="n">
-        <v>108.34</v>
+        <v>111.47</v>
       </c>
       <c r="L37" t="n">
-        <v>123.93</v>
+        <v>125.91</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.6</v>
       </c>
       <c r="F38" t="n">
-        <v>10.64</v>
+        <v>6.81</v>
       </c>
       <c r="G38" t="n">
-        <v>331.7</v>
+        <v>336.4</v>
       </c>
       <c r="H38" t="n">
-        <v>73.8</v>
+        <v>77.7</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-46.09</v>
+        <v>-83.22</v>
       </c>
       <c r="K38" t="n">
-        <v>-100.98</v>
+        <v>-68.5</v>
       </c>
       <c r="L38" t="n">
-        <v>111</v>
+        <v>107.78</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>3.65</v>
       </c>
       <c r="F39" t="n">
-        <v>11.18</v>
+        <v>10.1</v>
       </c>
       <c r="G39" t="n">
-        <v>334.2</v>
+        <v>347.3</v>
       </c>
       <c r="H39" t="n">
-        <v>84.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-104.65</v>
+        <v>-132.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-43.06</v>
+        <v>18.21</v>
       </c>
       <c r="L39" t="n">
-        <v>113.16</v>
+        <v>134.01</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>4.72</v>
       </c>
       <c r="F40" t="n">
-        <v>11.44</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>345.2</v>
+        <v>352.4</v>
       </c>
       <c r="H40" t="n">
-        <v>73.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-120.31</v>
+        <v>-122.51</v>
       </c>
       <c r="K40" t="n">
-        <v>131.96</v>
+        <v>162.59</v>
       </c>
       <c r="L40" t="n">
-        <v>178.57</v>
+        <v>203.58</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>4.89</v>
       </c>
       <c r="F41" t="n">
-        <v>10.32</v>
+        <v>10.42</v>
       </c>
       <c r="G41" t="n">
-        <v>340.8</v>
+        <v>330</v>
       </c>
       <c r="H41" t="n">
-        <v>83.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="I41" t="n">
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>75.03</v>
+        <v>50.51</v>
       </c>
       <c r="K41" t="n">
-        <v>322.16</v>
+        <v>352.07</v>
       </c>
       <c r="L41" t="n">
-        <v>330.78</v>
+        <v>355.68</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.86</v>
       </c>
       <c r="F42" t="n">
-        <v>11.29</v>
+        <v>8.83</v>
       </c>
       <c r="G42" t="n">
-        <v>339.6</v>
+        <v>349.4</v>
       </c>
       <c r="H42" t="n">
-        <v>77</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-199.06</v>
+        <v>-212.7</v>
       </c>
       <c r="K42" t="n">
-        <v>157.22</v>
+        <v>198.85</v>
       </c>
       <c r="L42" t="n">
-        <v>253.66</v>
+        <v>291.17</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>4.23</v>
       </c>
       <c r="F43" t="n">
-        <v>10.78</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>343.1</v>
+        <v>339.3</v>
       </c>
       <c r="H43" t="n">
-        <v>80.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>325.11</v>
+        <v>346.54</v>
       </c>
       <c r="K43" t="n">
-        <v>48.44</v>
+        <v>75.8</v>
       </c>
       <c r="L43" t="n">
-        <v>328.7</v>
+        <v>354.74</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>4.82</v>
       </c>
       <c r="F44" t="n">
-        <v>10.61</v>
+        <v>12.3</v>
       </c>
       <c r="G44" t="n">
-        <v>345</v>
+        <v>335.9</v>
       </c>
       <c r="H44" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>20.58</v>
+        <v>22.26</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.18000000000001</v>
+        <v>-80.94</v>
       </c>
       <c r="L44" t="n">
-        <v>76.02</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.72</v>
       </c>
       <c r="F45" t="n">
-        <v>10.38</v>
+        <v>12.3</v>
       </c>
       <c r="G45" t="n">
-        <v>333.7</v>
+        <v>331.2</v>
       </c>
       <c r="H45" t="n">
-        <v>78</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.05</v>
+        <v>-42.66</v>
       </c>
       <c r="K45" t="n">
-        <v>51.55</v>
+        <v>53.89</v>
       </c>
       <c r="L45" t="n">
-        <v>65.90000000000001</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>4.11</v>
       </c>
       <c r="F46" t="n">
-        <v>10.33</v>
+        <v>11.11</v>
       </c>
       <c r="G46" t="n">
-        <v>338.8</v>
+        <v>330.2</v>
       </c>
       <c r="H46" t="n">
-        <v>80.7</v>
+        <v>81.2</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.99</v>
+        <v>-29.07</v>
       </c>
       <c r="K46" t="n">
-        <v>50.65</v>
+        <v>57.61</v>
       </c>
       <c r="L46" t="n">
-        <v>56.47</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4.32</v>
       </c>
       <c r="F47" t="n">
-        <v>10.5</v>
+        <v>11.01</v>
       </c>
       <c r="G47" t="n">
-        <v>341</v>
+        <v>333.7</v>
       </c>
       <c r="H47" t="n">
-        <v>77.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I47" t="n">
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>3.33</v>
+        <v>1.49</v>
       </c>
       <c r="K47" t="n">
-        <v>-87.43000000000001</v>
+        <v>-95.7</v>
       </c>
       <c r="L47" t="n">
-        <v>87.5</v>
+        <v>95.70999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>4.14</v>
       </c>
       <c r="F48" t="n">
-        <v>10.68</v>
+        <v>12.3</v>
       </c>
       <c r="G48" t="n">
-        <v>343.8</v>
+        <v>337.1</v>
       </c>
       <c r="H48" t="n">
-        <v>84.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.09</v>
+        <v>-11.17</v>
       </c>
       <c r="K48" t="n">
-        <v>72.23999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="L48" t="n">
-        <v>72.69</v>
+        <v>84.16</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>4.53</v>
       </c>
       <c r="F49" t="n">
-        <v>11.32</v>
+        <v>11.95</v>
       </c>
       <c r="G49" t="n">
-        <v>342.9</v>
+        <v>350</v>
       </c>
       <c r="H49" t="n">
-        <v>78.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>89.87</v>
+        <v>103.25</v>
       </c>
       <c r="K49" t="n">
-        <v>12.36</v>
+        <v>18.08</v>
       </c>
       <c r="L49" t="n">
-        <v>90.72</v>
+        <v>104.82</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>4.05</v>
       </c>
       <c r="F50" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="G50" t="n">
-        <v>322.7</v>
+        <v>349.6</v>
       </c>
       <c r="H50" t="n">
-        <v>86.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>154.76</v>
+        <v>155.96</v>
       </c>
       <c r="K50" t="n">
-        <v>0.72</v>
+        <v>14.49</v>
       </c>
       <c r="L50" t="n">
-        <v>154.76</v>
+        <v>156.63</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>4.63</v>
       </c>
       <c r="F51" t="n">
-        <v>10.3</v>
+        <v>12.08</v>
       </c>
       <c r="G51" t="n">
-        <v>332</v>
+        <v>329.6</v>
       </c>
       <c r="H51" t="n">
-        <v>79.2</v>
+        <v>77.8</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-61.97</v>
+        <v>-78.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.1</v>
+        <v>-112.96</v>
       </c>
       <c r="L51" t="n">
-        <v>132.49</v>
+        <v>137.62</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>4.32</v>
       </c>
       <c r="F52" t="n">
-        <v>11.26</v>
+        <v>10.36</v>
       </c>
       <c r="G52" t="n">
-        <v>336.3</v>
+        <v>348.9</v>
       </c>
       <c r="H52" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I52" t="n">
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>144.97</v>
+        <v>156.32</v>
       </c>
       <c r="K52" t="n">
-        <v>-44.26</v>
+        <v>-34.34</v>
       </c>
       <c r="L52" t="n">
-        <v>151.57</v>
+        <v>160.05</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>4.48</v>
       </c>
       <c r="F53" t="n">
-        <v>10.39</v>
+        <v>12.3</v>
       </c>
       <c r="G53" t="n">
-        <v>332</v>
+        <v>331.3</v>
       </c>
       <c r="H53" t="n">
-        <v>82.5</v>
+        <v>77.8</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>207.05</v>
+        <v>196.29</v>
       </c>
       <c r="K53" t="n">
-        <v>-27.1</v>
+        <v>-3.73</v>
       </c>
       <c r="L53" t="n">
-        <v>208.82</v>
+        <v>196.32</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>4.54</v>
       </c>
       <c r="F54" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="G54" t="n">
-        <v>337.8</v>
+        <v>335</v>
       </c>
       <c r="H54" t="n">
-        <v>76</v>
+        <v>80.7</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-173.92</v>
+        <v>-187.62</v>
       </c>
       <c r="K54" t="n">
-        <v>9.210000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="L54" t="n">
-        <v>174.16</v>
+        <v>190.49</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>4.97</v>
       </c>
       <c r="F55" t="n">
-        <v>9.94</v>
+        <v>12.3</v>
       </c>
       <c r="G55" t="n">
         <v>331.2</v>
       </c>
       <c r="H55" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>113.43</v>
+        <v>155.92</v>
       </c>
       <c r="K55" t="n">
-        <v>-125.36</v>
+        <v>183.68</v>
       </c>
       <c r="L55" t="n">
-        <v>169.06</v>
+        <v>240.93</v>
       </c>
     </row>
     <row r="56">
@@ -2389,10 +2389,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="F56" t="n">
-        <v>9.82</v>
+        <v>12.3</v>
       </c>
       <c r="G56" t="n">
         <v>334.4</v>
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>98.26000000000001</v>
+        <v>-194.6</v>
       </c>
       <c r="K56" t="n">
-        <v>337.76</v>
+        <v>204.69</v>
       </c>
       <c r="L56" t="n">
-        <v>351.76</v>
+        <v>282.43</v>
       </c>
     </row>
     <row r="57">
@@ -2431,10 +2431,10 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.44</v>
+        <v>5.18</v>
       </c>
       <c r="F57" t="n">
-        <v>10.65</v>
+        <v>12.3</v>
       </c>
       <c r="G57" t="n">
         <v>327.8</v>
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-43.68</v>
+        <v>284.03</v>
       </c>
       <c r="K57" t="n">
-        <v>228.95</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>233.08</v>
+        <v>300.07</v>
       </c>
     </row>
     <row r="58">
@@ -2473,10 +2473,10 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.92</v>
+        <v>4.74</v>
       </c>
       <c r="F58" t="n">
-        <v>10.83</v>
+        <v>10.81</v>
       </c>
       <c r="G58" t="n">
         <v>335.3</v>
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>324.2</v>
+        <v>76.77</v>
       </c>
       <c r="K58" t="n">
-        <v>-76.55</v>
+        <v>462.53</v>
       </c>
       <c r="L58" t="n">
-        <v>333.12</v>
+        <v>468.86</v>
       </c>
     </row>
     <row r="59">
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.4</v>
+        <v>4.26</v>
       </c>
       <c r="F59" t="n">
-        <v>11.53</v>
+        <v>10.7</v>
       </c>
       <c r="G59" t="n">
         <v>334</v>
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>43.68</v>
+        <v>-40.81</v>
       </c>
       <c r="K59" t="n">
-        <v>63.8</v>
+        <v>60.09</v>
       </c>
       <c r="L59" t="n">
-        <v>77.31999999999999</v>
+        <v>72.64</v>
       </c>
     </row>
     <row r="60">
@@ -2557,10 +2557,10 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.05</v>
+        <v>5.02</v>
       </c>
       <c r="F60" t="n">
-        <v>10.26</v>
+        <v>12.3</v>
       </c>
       <c r="G60" t="n">
         <v>344.2</v>
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>37.2</v>
+        <v>38.59</v>
       </c>
       <c r="K60" t="n">
-        <v>57.23</v>
+        <v>57.34</v>
       </c>
       <c r="L60" t="n">
-        <v>68.26000000000001</v>
+        <v>69.11</v>
       </c>
     </row>
     <row r="61">
@@ -2599,10 +2599,10 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.83</v>
+        <v>4.91</v>
       </c>
       <c r="F61" t="n">
-        <v>10.62</v>
+        <v>12.3</v>
       </c>
       <c r="G61" t="n">
         <v>328.7</v>
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.28</v>
+        <v>-25.55</v>
       </c>
       <c r="K61" t="n">
-        <v>-72.68000000000001</v>
+        <v>-58</v>
       </c>
       <c r="L61" t="n">
-        <v>80.36</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
       <c r="F62" t="n">
-        <v>10.84</v>
+        <v>6.09</v>
       </c>
       <c r="G62" t="n">
-        <v>335.1</v>
+        <v>340.5</v>
       </c>
       <c r="H62" t="n">
-        <v>83.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I62" t="n">
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>35.95</v>
+        <v>33.56</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.78</v>
+        <v>-4.85</v>
       </c>
       <c r="L62" t="n">
-        <v>38.16</v>
+        <v>33.91</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>4.15</v>
       </c>
       <c r="F63" t="n">
-        <v>10.84</v>
+        <v>12.3</v>
       </c>
       <c r="G63" t="n">
-        <v>338.2</v>
+        <v>340.4</v>
       </c>
       <c r="H63" t="n">
-        <v>76.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>68.13</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>31.08</v>
+        <v>37.52</v>
       </c>
       <c r="L63" t="n">
-        <v>74.88</v>
+        <v>81.91</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>4.47</v>
       </c>
       <c r="F64" t="n">
-        <v>10.54</v>
+        <v>12.3</v>
       </c>
       <c r="G64" t="n">
-        <v>324.1</v>
+        <v>334.5</v>
       </c>
       <c r="H64" t="n">
-        <v>84.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-73.58</v>
+        <v>-84.12</v>
       </c>
       <c r="K64" t="n">
-        <v>8.039999999999999</v>
+        <v>13.65</v>
       </c>
       <c r="L64" t="n">
-        <v>74.01000000000001</v>
+        <v>85.23</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.99</v>
       </c>
       <c r="F65" t="n">
-        <v>10.38</v>
+        <v>12.3</v>
       </c>
       <c r="G65" t="n">
-        <v>337.8</v>
+        <v>331.3</v>
       </c>
       <c r="H65" t="n">
-        <v>83.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-82.59</v>
+        <v>-110.71</v>
       </c>
       <c r="K65" t="n">
-        <v>-67.59</v>
+        <v>-42.65</v>
       </c>
       <c r="L65" t="n">
-        <v>106.72</v>
+        <v>118.64</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>5.08</v>
       </c>
       <c r="F66" t="n">
-        <v>10.64</v>
+        <v>12.3</v>
       </c>
       <c r="G66" t="n">
-        <v>339.7</v>
+        <v>336.3</v>
       </c>
       <c r="H66" t="n">
-        <v>87.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>186.29</v>
+        <v>177.51</v>
       </c>
       <c r="K66" t="n">
-        <v>9.99</v>
+        <v>24.95</v>
       </c>
       <c r="L66" t="n">
-        <v>186.56</v>
+        <v>179.26</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>3.8</v>
       </c>
       <c r="F67" t="n">
-        <v>9.68</v>
+        <v>10.57</v>
       </c>
       <c r="G67" t="n">
-        <v>345</v>
+        <v>317.2</v>
       </c>
       <c r="H67" t="n">
-        <v>76.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-35.45</v>
+        <v>-48.4</v>
       </c>
       <c r="K67" t="n">
-        <v>103.25</v>
+        <v>108.12</v>
       </c>
       <c r="L67" t="n">
-        <v>109.17</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>5.36</v>
       </c>
       <c r="F68" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="G68" t="n">
-        <v>359.6</v>
+        <v>337.6</v>
       </c>
       <c r="H68" t="n">
-        <v>82.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-143.41</v>
+        <v>-173</v>
       </c>
       <c r="K68" t="n">
-        <v>249.73</v>
+        <v>289.91</v>
       </c>
       <c r="L68" t="n">
-        <v>287.98</v>
+        <v>337.61</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>4.36</v>
       </c>
       <c r="F69" t="n">
-        <v>10.8</v>
+        <v>12.3</v>
       </c>
       <c r="G69" t="n">
-        <v>334.1</v>
+        <v>339.5</v>
       </c>
       <c r="H69" t="n">
-        <v>80.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>202.42</v>
+        <v>231.53</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.78</v>
+        <v>21.58</v>
       </c>
       <c r="L69" t="n">
-        <v>202.44</v>
+        <v>232.54</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>4.45</v>
       </c>
       <c r="F70" t="n">
-        <v>11.15</v>
+        <v>12.3</v>
       </c>
       <c r="G70" t="n">
-        <v>338.6</v>
+        <v>346.5</v>
       </c>
       <c r="H70" t="n">
-        <v>91.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I70" t="n">
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>224.48</v>
+        <v>240.54</v>
       </c>
       <c r="K70" t="n">
-        <v>-9.9</v>
+        <v>16.06</v>
       </c>
       <c r="L70" t="n">
-        <v>224.7</v>
+        <v>241.08</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>4.24</v>
       </c>
       <c r="F71" t="n">
-        <v>10.91</v>
+        <v>12.3</v>
       </c>
       <c r="G71" t="n">
-        <v>349.9</v>
+        <v>341.7</v>
       </c>
       <c r="H71" t="n">
-        <v>82.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="I71" t="n">
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>41.96</v>
+        <v>25.6</v>
       </c>
       <c r="K71" t="n">
-        <v>221.31</v>
+        <v>271.19</v>
       </c>
       <c r="L71" t="n">
-        <v>225.25</v>
+        <v>272.4</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>4.8</v>
       </c>
       <c r="F72" t="n">
-        <v>10.81</v>
+        <v>12.3</v>
       </c>
       <c r="G72" t="n">
-        <v>334.5</v>
+        <v>339.7</v>
       </c>
       <c r="H72" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>109.78</v>
+        <v>103.42</v>
       </c>
       <c r="K72" t="n">
-        <v>202.1</v>
+        <v>270.47</v>
       </c>
       <c r="L72" t="n">
-        <v>229.99</v>
+        <v>289.57</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>4.69</v>
       </c>
       <c r="F73" t="n">
-        <v>10.65</v>
+        <v>12.3</v>
       </c>
       <c r="G73" t="n">
-        <v>324.2</v>
+        <v>336.6</v>
       </c>
       <c r="H73" t="n">
-        <v>79.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-12.96</v>
+        <v>-39.32</v>
       </c>
       <c r="K73" t="n">
-        <v>-194.09</v>
+        <v>-231.46</v>
       </c>
       <c r="L73" t="n">
-        <v>194.52</v>
+        <v>234.78</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>3.95</v>
       </c>
       <c r="F74" t="n">
-        <v>10.49</v>
+        <v>10.83</v>
       </c>
       <c r="G74" t="n">
-        <v>349.2</v>
+        <v>333.4</v>
       </c>
       <c r="H74" t="n">
-        <v>79.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-63.42</v>
+        <v>-69.5</v>
       </c>
       <c r="K74" t="n">
-        <v>11.22</v>
+        <v>13.11</v>
       </c>
       <c r="L74" t="n">
-        <v>64.41</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>4.28</v>
       </c>
       <c r="F75" t="n">
-        <v>10.69</v>
+        <v>11.74</v>
       </c>
       <c r="G75" t="n">
-        <v>341.2</v>
+        <v>337.4</v>
       </c>
       <c r="H75" t="n">
-        <v>83.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>66.62</v>
+        <v>76.36</v>
       </c>
       <c r="K75" t="n">
-        <v>34.48</v>
+        <v>41.03</v>
       </c>
       <c r="L75" t="n">
-        <v>75.01000000000001</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>4.71</v>
       </c>
       <c r="F76" t="n">
-        <v>9.960000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="G76" t="n">
-        <v>334.3</v>
+        <v>322.8</v>
       </c>
       <c r="H76" t="n">
-        <v>88.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.1</v>
+        <v>-63.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.15</v>
+        <v>-50.22</v>
       </c>
       <c r="L76" t="n">
-        <v>71.23</v>
+        <v>81.22</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>4.9</v>
       </c>
       <c r="F77" t="n">
-        <v>10.91</v>
+        <v>12.3</v>
       </c>
       <c r="G77" t="n">
-        <v>345.6</v>
+        <v>341.9</v>
       </c>
       <c r="H77" t="n">
-        <v>77.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>67.45</v>
+        <v>84.56</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.61</v>
+        <v>-24.38</v>
       </c>
       <c r="L77" t="n">
-        <v>71.47</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>5.12</v>
       </c>
       <c r="F78" t="n">
-        <v>10.65</v>
+        <v>12.3</v>
       </c>
       <c r="G78" t="n">
-        <v>343.4</v>
+        <v>336.6</v>
       </c>
       <c r="H78" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-13.7</v>
+        <v>-19.07</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.68000000000001</v>
+        <v>-76.98</v>
       </c>
       <c r="L78" t="n">
-        <v>73.95999999999999</v>
+        <v>79.31</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>3.94</v>
       </c>
       <c r="F79" t="n">
-        <v>10.59</v>
+        <v>11.51</v>
       </c>
       <c r="G79" t="n">
-        <v>344</v>
+        <v>335.4</v>
       </c>
       <c r="H79" t="n">
-        <v>84.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.31</v>
+        <v>-19.17</v>
       </c>
       <c r="K79" t="n">
-        <v>-73.54000000000001</v>
+        <v>-76.87</v>
       </c>
       <c r="L79" t="n">
-        <v>75.12</v>
+        <v>79.22</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>3.96</v>
       </c>
       <c r="F80" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="G80" t="n">
-        <v>352.5</v>
+        <v>343.6</v>
       </c>
       <c r="H80" t="n">
-        <v>86.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-130.03</v>
+        <v>-149.85</v>
       </c>
       <c r="K80" t="n">
-        <v>-5.97</v>
+        <v>7.45</v>
       </c>
       <c r="L80" t="n">
-        <v>130.17</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>4.9</v>
       </c>
       <c r="F81" t="n">
-        <v>10.54</v>
+        <v>12.3</v>
       </c>
       <c r="G81" t="n">
-        <v>353.1</v>
+        <v>334.4</v>
       </c>
       <c r="H81" t="n">
-        <v>85.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-174.22</v>
+        <v>-176.1</v>
       </c>
       <c r="K81" t="n">
-        <v>-56.4</v>
+        <v>-41.47</v>
       </c>
       <c r="L81" t="n">
-        <v>183.12</v>
+        <v>180.92</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>4.76</v>
       </c>
       <c r="F82" t="n">
-        <v>11.58</v>
+        <v>12.3</v>
       </c>
       <c r="G82" t="n">
-        <v>333.6</v>
+        <v>355.2</v>
       </c>
       <c r="H82" t="n">
-        <v>79.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-86.76000000000001</v>
+        <v>-91.53</v>
       </c>
       <c r="K82" t="n">
-        <v>145.4</v>
+        <v>173.85</v>
       </c>
       <c r="L82" t="n">
-        <v>169.32</v>
+        <v>196.47</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>4.99</v>
       </c>
       <c r="F83" t="n">
-        <v>10.09</v>
+        <v>12.3</v>
       </c>
       <c r="G83" t="n">
-        <v>338.3</v>
+        <v>325.5</v>
       </c>
       <c r="H83" t="n">
-        <v>75.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I83" t="n">
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>80.98999999999999</v>
+        <v>62.51</v>
       </c>
       <c r="K83" t="n">
-        <v>172.5</v>
+        <v>205.76</v>
       </c>
       <c r="L83" t="n">
-        <v>190.57</v>
+        <v>215.04</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>4.67</v>
       </c>
       <c r="F84" t="n">
-        <v>10.97</v>
+        <v>11.91</v>
       </c>
       <c r="G84" t="n">
-        <v>345.3</v>
+        <v>343</v>
       </c>
       <c r="H84" t="n">
-        <v>77</v>
+        <v>84.5</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>67.58</v>
+        <v>58.09</v>
       </c>
       <c r="K84" t="n">
-        <v>174.51</v>
+        <v>206.86</v>
       </c>
       <c r="L84" t="n">
-        <v>187.14</v>
+        <v>214.86</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>4.73</v>
       </c>
       <c r="F85" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="G85" t="n">
-        <v>331</v>
+        <v>329.5</v>
       </c>
       <c r="H85" t="n">
-        <v>82.8</v>
+        <v>77.3</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>70.06</v>
+        <v>63.52</v>
       </c>
       <c r="K85" t="n">
-        <v>218.4</v>
+        <v>255.43</v>
       </c>
       <c r="L85" t="n">
-        <v>229.37</v>
+        <v>263.21</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>4.93</v>
       </c>
       <c r="F86" t="n">
-        <v>9.9</v>
+        <v>12.3</v>
       </c>
       <c r="G86" t="n">
-        <v>346</v>
+        <v>321.6</v>
       </c>
       <c r="H86" t="n">
-        <v>88.8</v>
+        <v>84.8</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-132.8</v>
+        <v>-188.24</v>
       </c>
       <c r="K86" t="n">
-        <v>259.1</v>
+        <v>292.94</v>
       </c>
       <c r="L86" t="n">
-        <v>291.16</v>
+        <v>348.21</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>3.9</v>
       </c>
       <c r="F87" t="n">
-        <v>11.05</v>
+        <v>12.3</v>
       </c>
       <c r="G87" t="n">
-        <v>343.6</v>
+        <v>344.5</v>
       </c>
       <c r="H87" t="n">
-        <v>69.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-191.62</v>
+        <v>-245.49</v>
       </c>
       <c r="K87" t="n">
-        <v>-107.61</v>
+        <v>-92.89</v>
       </c>
       <c r="L87" t="n">
-        <v>219.77</v>
+        <v>262.48</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>3.8</v>
       </c>
       <c r="F88" t="n">
-        <v>11.09</v>
+        <v>11.2</v>
       </c>
       <c r="G88" t="n">
-        <v>327.8</v>
+        <v>345.4</v>
       </c>
       <c r="H88" t="n">
-        <v>81.5</v>
+        <v>75.7</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>78.03</v>
+        <v>78.72</v>
       </c>
       <c r="K88" t="n">
-        <v>-118.6</v>
+        <v>-7.37</v>
       </c>
       <c r="L88" t="n">
-        <v>141.96</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-81.34</v>
+        <v>-75.83</v>
       </c>
       <c r="K14" t="n">
-        <v>35.46</v>
+        <v>33.06</v>
       </c>
       <c r="L14" t="n">
-        <v>88.73</v>
+        <v>82.72</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.48</v>
+        <v>-85.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.57</v>
+        <v>-21.48</v>
       </c>
       <c r="L15" t="n">
-        <v>88.16</v>
+        <v>87.78</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>38.31</v>
+        <v>38.14</v>
       </c>
       <c r="K16" t="n">
-        <v>-43.87</v>
+        <v>-43.67</v>
       </c>
       <c r="L16" t="n">
-        <v>58.24</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>91.16</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-42.41</v>
+        <v>-42.19</v>
       </c>
       <c r="L17" t="n">
-        <v>100.55</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>89.77</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>74.81</v>
+        <v>73.09</v>
       </c>
       <c r="L18" t="n">
-        <v>116.85</v>
+        <v>114.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>36.74</v>
+        <v>35.89</v>
       </c>
       <c r="K19" t="n">
-        <v>96.55</v>
+        <v>94.33</v>
       </c>
       <c r="L19" t="n">
-        <v>103.31</v>
+        <v>100.93</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>6.61</v>
+        <v>6.73</v>
       </c>
       <c r="K20" t="n">
-        <v>118.39</v>
+        <v>120.62</v>
       </c>
       <c r="L20" t="n">
-        <v>118.57</v>
+        <v>120.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>118.02</v>
+        <v>112.98</v>
       </c>
       <c r="K21" t="n">
-        <v>43.93</v>
+        <v>42.06</v>
       </c>
       <c r="L21" t="n">
-        <v>125.93</v>
+        <v>120.55</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>49.82</v>
+        <v>47.67</v>
       </c>
       <c r="K22" t="n">
-        <v>112.23</v>
+        <v>107.39</v>
       </c>
       <c r="L22" t="n">
-        <v>122.79</v>
+        <v>117.5</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-159.39</v>
+        <v>-156.18</v>
       </c>
       <c r="K23" t="n">
-        <v>110.44</v>
+        <v>108.21</v>
       </c>
       <c r="L23" t="n">
-        <v>193.92</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-167.58</v>
+        <v>-164.17</v>
       </c>
       <c r="K24" t="n">
-        <v>-23.36</v>
+        <v>-22.88</v>
       </c>
       <c r="L24" t="n">
-        <v>169.2</v>
+        <v>165.76</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-169.88</v>
+        <v>-179.51</v>
       </c>
       <c r="K25" t="n">
-        <v>50.93</v>
+        <v>53.81</v>
       </c>
       <c r="L25" t="n">
-        <v>177.35</v>
+        <v>187.41</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>145.6</v>
+        <v>140.49</v>
       </c>
       <c r="K26" t="n">
-        <v>224.07</v>
+        <v>216.21</v>
       </c>
       <c r="L26" t="n">
-        <v>267.22</v>
+        <v>257.85</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-192.99</v>
+        <v>-181.67</v>
       </c>
       <c r="K27" t="n">
-        <v>86.34</v>
+        <v>81.27</v>
       </c>
       <c r="L27" t="n">
-        <v>211.43</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-34.55</v>
+        <v>-33.21</v>
       </c>
       <c r="K28" t="n">
-        <v>256.86</v>
+        <v>246.91</v>
       </c>
       <c r="L28" t="n">
-        <v>259.17</v>
+        <v>249.14</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>43.35</v>
+        <v>44.88</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.1</v>
+        <v>-41.51</v>
       </c>
       <c r="L29" t="n">
-        <v>59.05</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.87</v>
+        <v>-3.99</v>
       </c>
       <c r="K30" t="n">
-        <v>-83.94</v>
+        <v>-86.72</v>
       </c>
       <c r="L30" t="n">
-        <v>84.03</v>
+        <v>86.81999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>82.58</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.32</v>
+        <v>-27.67</v>
       </c>
       <c r="L31" t="n">
-        <v>87.31</v>
+        <v>85.29000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.6</v>
+        <v>-5.57</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.51000000000001</v>
+        <v>-94.08</v>
       </c>
       <c r="L32" t="n">
-        <v>94.67</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.92</v>
+        <v>-23.02</v>
       </c>
       <c r="K33" t="n">
-        <v>75.94</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>79.04000000000001</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>83.54000000000001</v>
+        <v>86.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-35</v>
+        <v>-36.07</v>
       </c>
       <c r="L34" t="n">
-        <v>90.58</v>
+        <v>93.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-50.24</v>
+        <v>-48.07</v>
       </c>
       <c r="K35" t="n">
-        <v>-121.97</v>
+        <v>-116.71</v>
       </c>
       <c r="L35" t="n">
-        <v>131.91</v>
+        <v>126.22</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-126.57</v>
+        <v>-121.07</v>
       </c>
       <c r="K36" t="n">
-        <v>49.27</v>
+        <v>47.13</v>
       </c>
       <c r="L36" t="n">
-        <v>135.82</v>
+        <v>129.92</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-58.55</v>
+        <v>-54.75</v>
       </c>
       <c r="K37" t="n">
-        <v>111.47</v>
+        <v>104.24</v>
       </c>
       <c r="L37" t="n">
-        <v>125.91</v>
+        <v>117.74</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-83.22</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-68.5</v>
+        <v>-65.67</v>
       </c>
       <c r="L38" t="n">
-        <v>107.78</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-132.77</v>
+        <v>-140.35</v>
       </c>
       <c r="K39" t="n">
-        <v>18.21</v>
+        <v>19.25</v>
       </c>
       <c r="L39" t="n">
-        <v>134.01</v>
+        <v>141.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-122.51</v>
+        <v>-130.51</v>
       </c>
       <c r="K40" t="n">
-        <v>162.59</v>
+        <v>173.2</v>
       </c>
       <c r="L40" t="n">
-        <v>203.58</v>
+        <v>216.87</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>50.51</v>
+        <v>54.32</v>
       </c>
       <c r="K41" t="n">
-        <v>352.07</v>
+        <v>378.59</v>
       </c>
       <c r="L41" t="n">
-        <v>355.68</v>
+        <v>382.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-212.7</v>
+        <v>-221.95</v>
       </c>
       <c r="K42" t="n">
-        <v>198.85</v>
+        <v>207.5</v>
       </c>
       <c r="L42" t="n">
-        <v>291.17</v>
+        <v>303.84</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>346.54</v>
+        <v>341.95</v>
       </c>
       <c r="K43" t="n">
-        <v>75.8</v>
+        <v>74.8</v>
       </c>
       <c r="L43" t="n">
-        <v>354.74</v>
+        <v>350.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>22.26</v>
+        <v>21.17</v>
       </c>
       <c r="K44" t="n">
-        <v>-80.94</v>
+        <v>-77</v>
       </c>
       <c r="L44" t="n">
-        <v>83.94</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-42.66</v>
+        <v>-39.66</v>
       </c>
       <c r="K45" t="n">
-        <v>53.89</v>
+        <v>50.1</v>
       </c>
       <c r="L45" t="n">
-        <v>68.73</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.07</v>
+        <v>-29.52</v>
       </c>
       <c r="K46" t="n">
-        <v>57.61</v>
+        <v>58.5</v>
       </c>
       <c r="L46" t="n">
-        <v>64.53</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-95.7</v>
+        <v>-98.88</v>
       </c>
       <c r="L47" t="n">
-        <v>95.70999999999999</v>
+        <v>98.89</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-11.17</v>
+        <v>-10.89</v>
       </c>
       <c r="K48" t="n">
-        <v>83.42</v>
+        <v>81.37</v>
       </c>
       <c r="L48" t="n">
-        <v>84.16</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>103.25</v>
+        <v>104.64</v>
       </c>
       <c r="K49" t="n">
-        <v>18.08</v>
+        <v>18.32</v>
       </c>
       <c r="L49" t="n">
-        <v>104.82</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>155.96</v>
+        <v>149.26</v>
       </c>
       <c r="K50" t="n">
-        <v>14.49</v>
+        <v>13.87</v>
       </c>
       <c r="L50" t="n">
-        <v>156.63</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-78.61</v>
+        <v>-75.17</v>
       </c>
       <c r="K51" t="n">
-        <v>-112.96</v>
+        <v>-108.02</v>
       </c>
       <c r="L51" t="n">
-        <v>137.62</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>156.32</v>
+        <v>152.86</v>
       </c>
       <c r="K52" t="n">
-        <v>-34.34</v>
+        <v>-33.58</v>
       </c>
       <c r="L52" t="n">
-        <v>160.05</v>
+        <v>156.51</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>196.29</v>
+        <v>184.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.73</v>
+        <v>-3.5</v>
       </c>
       <c r="L53" t="n">
-        <v>196.32</v>
+        <v>184.05</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-187.62</v>
+        <v>-176.97</v>
       </c>
       <c r="K54" t="n">
-        <v>32.9</v>
+        <v>31.04</v>
       </c>
       <c r="L54" t="n">
-        <v>190.49</v>
+        <v>179.67</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>155.92</v>
+        <v>166.22</v>
       </c>
       <c r="K55" t="n">
-        <v>183.68</v>
+        <v>195.82</v>
       </c>
       <c r="L55" t="n">
-        <v>240.93</v>
+        <v>256.86</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-194.6</v>
+        <v>-183.36</v>
       </c>
       <c r="K56" t="n">
-        <v>204.69</v>
+        <v>192.86</v>
       </c>
       <c r="L56" t="n">
-        <v>282.43</v>
+        <v>266.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>284.03</v>
+        <v>283.63</v>
       </c>
       <c r="K57" t="n">
-        <v>96.79000000000001</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>300.07</v>
+        <v>299.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>76.77</v>
+        <v>81.05</v>
       </c>
       <c r="K58" t="n">
-        <v>462.53</v>
+        <v>488.36</v>
       </c>
       <c r="L58" t="n">
-        <v>468.86</v>
+        <v>495.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-40.81</v>
+        <v>-38.92</v>
       </c>
       <c r="K59" t="n">
-        <v>60.09</v>
+        <v>57.31</v>
       </c>
       <c r="L59" t="n">
-        <v>72.64</v>
+        <v>69.27</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>38.59</v>
+        <v>38.27</v>
       </c>
       <c r="K60" t="n">
-        <v>57.34</v>
+        <v>56.87</v>
       </c>
       <c r="L60" t="n">
-        <v>69.11</v>
+        <v>68.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-25.55</v>
+        <v>-24.3</v>
       </c>
       <c r="K61" t="n">
-        <v>-58</v>
+        <v>-55.15</v>
       </c>
       <c r="L61" t="n">
-        <v>63.38</v>
+        <v>60.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>33.56</v>
+        <v>31.31</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.85</v>
+        <v>-4.52</v>
       </c>
       <c r="L62" t="n">
-        <v>33.91</v>
+        <v>31.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>72.81999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="K63" t="n">
-        <v>37.52</v>
+        <v>34.97</v>
       </c>
       <c r="L63" t="n">
-        <v>81.91</v>
+        <v>76.34999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-84.12</v>
+        <v>-83.64</v>
       </c>
       <c r="K64" t="n">
-        <v>13.65</v>
+        <v>13.57</v>
       </c>
       <c r="L64" t="n">
-        <v>85.23</v>
+        <v>84.73999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-110.71</v>
+        <v>-110.33</v>
       </c>
       <c r="K65" t="n">
-        <v>-42.65</v>
+        <v>-42.51</v>
       </c>
       <c r="L65" t="n">
-        <v>118.64</v>
+        <v>118.24</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>177.51</v>
+        <v>173.28</v>
       </c>
       <c r="K66" t="n">
-        <v>24.95</v>
+        <v>24.35</v>
       </c>
       <c r="L66" t="n">
-        <v>179.26</v>
+        <v>174.99</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-48.4</v>
+        <v>-46.34</v>
       </c>
       <c r="K67" t="n">
-        <v>108.12</v>
+        <v>103.52</v>
       </c>
       <c r="L67" t="n">
-        <v>118.46</v>
+        <v>113.42</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-173</v>
+        <v>-184.63</v>
       </c>
       <c r="K68" t="n">
-        <v>289.91</v>
+        <v>309.4</v>
       </c>
       <c r="L68" t="n">
-        <v>337.61</v>
+        <v>360.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>231.53</v>
+        <v>236.37</v>
       </c>
       <c r="K69" t="n">
-        <v>21.58</v>
+        <v>22.03</v>
       </c>
       <c r="L69" t="n">
-        <v>232.54</v>
+        <v>237.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>240.54</v>
+        <v>254.5</v>
       </c>
       <c r="K70" t="n">
-        <v>16.06</v>
+        <v>17</v>
       </c>
       <c r="L70" t="n">
-        <v>241.08</v>
+        <v>255.07</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>25.6</v>
+        <v>25.26</v>
       </c>
       <c r="K71" t="n">
-        <v>271.19</v>
+        <v>267.61</v>
       </c>
       <c r="L71" t="n">
-        <v>272.4</v>
+        <v>268.8</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>103.42</v>
+        <v>111.15</v>
       </c>
       <c r="K72" t="n">
-        <v>270.47</v>
+        <v>290.68</v>
       </c>
       <c r="L72" t="n">
-        <v>289.57</v>
+        <v>311.21</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-39.32</v>
+        <v>-42.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-231.46</v>
+        <v>-248.58</v>
       </c>
       <c r="L73" t="n">
-        <v>234.78</v>
+        <v>252.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-69.5</v>
+        <v>-64.84</v>
       </c>
       <c r="K74" t="n">
-        <v>13.11</v>
+        <v>12.23</v>
       </c>
       <c r="L74" t="n">
-        <v>70.72</v>
+        <v>65.98</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>76.36</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>41.03</v>
+        <v>42.4</v>
       </c>
       <c r="L75" t="n">
-        <v>86.68000000000001</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-63.83</v>
+        <v>-64.64</v>
       </c>
       <c r="K76" t="n">
-        <v>-50.22</v>
+        <v>-50.86</v>
       </c>
       <c r="L76" t="n">
-        <v>81.22</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>84.56</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-24.38</v>
+        <v>-25.56</v>
       </c>
       <c r="L77" t="n">
-        <v>88</v>
+        <v>92.29000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-19.07</v>
+        <v>-18.52</v>
       </c>
       <c r="K78" t="n">
-        <v>-76.98</v>
+        <v>-74.78</v>
       </c>
       <c r="L78" t="n">
-        <v>79.31</v>
+        <v>77.04000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-19.17</v>
+        <v>-18.31</v>
       </c>
       <c r="K79" t="n">
-        <v>-76.87</v>
+        <v>-73.42</v>
       </c>
       <c r="L79" t="n">
-        <v>79.22</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-149.85</v>
+        <v>-152.6</v>
       </c>
       <c r="K80" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="L80" t="n">
-        <v>150.03</v>
+        <v>152.79</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-176.1</v>
+        <v>-164.33</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.47</v>
+        <v>-38.7</v>
       </c>
       <c r="L81" t="n">
-        <v>180.92</v>
+        <v>168.82</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-91.53</v>
+        <v>-94.83</v>
       </c>
       <c r="K82" t="n">
-        <v>173.85</v>
+        <v>180.12</v>
       </c>
       <c r="L82" t="n">
-        <v>196.47</v>
+        <v>203.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>62.51</v>
+        <v>61.78</v>
       </c>
       <c r="K83" t="n">
-        <v>205.76</v>
+        <v>203.38</v>
       </c>
       <c r="L83" t="n">
-        <v>215.04</v>
+        <v>212.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>58.09</v>
+        <v>60.8</v>
       </c>
       <c r="K84" t="n">
-        <v>206.86</v>
+        <v>216.54</v>
       </c>
       <c r="L84" t="n">
-        <v>214.86</v>
+        <v>224.91</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>63.52</v>
+        <v>62.73</v>
       </c>
       <c r="K85" t="n">
-        <v>255.43</v>
+        <v>252.27</v>
       </c>
       <c r="L85" t="n">
-        <v>263.21</v>
+        <v>259.95</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-188.24</v>
+        <v>-195.38</v>
       </c>
       <c r="K86" t="n">
-        <v>292.94</v>
+        <v>304.04</v>
       </c>
       <c r="L86" t="n">
-        <v>348.21</v>
+        <v>361.41</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-245.49</v>
+        <v>-236.47</v>
       </c>
       <c r="K87" t="n">
-        <v>-92.89</v>
+        <v>-89.48</v>
       </c>
       <c r="L87" t="n">
-        <v>262.48</v>
+        <v>252.84</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>78.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-7.37</v>
+        <v>-7.41</v>
       </c>
       <c r="L88" t="n">
-        <v>79.06999999999999</v>
+        <v>79.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="F14" t="n">
-        <v>10.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>343.3</v>
+        <v>326.8</v>
       </c>
       <c r="H14" t="n">
-        <v>77.09999999999999</v>
+        <v>42.9</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-75.83</v>
+        <v>-76.69</v>
       </c>
       <c r="K14" t="n">
-        <v>33.06</v>
+        <v>-5.75</v>
       </c>
       <c r="L14" t="n">
-        <v>82.72</v>
+        <v>76.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:07:54</t>
+          <t>08:08:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="F15" t="n">
-        <v>12.3</v>
+        <v>8.02</v>
       </c>
       <c r="G15" t="n">
-        <v>346.3</v>
+        <v>335.5</v>
       </c>
       <c r="H15" t="n">
-        <v>82.7</v>
+        <v>39.8</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.11</v>
+        <v>-33.21</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.48</v>
+        <v>68.64</v>
       </c>
       <c r="L15" t="n">
-        <v>87.78</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:08:49</t>
+          <t>08:10:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.21</v>
+        <v>3.24</v>
       </c>
       <c r="F16" t="n">
-        <v>11.08</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>339.6</v>
+        <v>341.3</v>
       </c>
       <c r="H16" t="n">
-        <v>82.90000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>38.14</v>
+        <v>-51.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-43.67</v>
+        <v>23.44</v>
       </c>
       <c r="L16" t="n">
-        <v>57.98</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:13:09</t>
+          <t>08:14:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.38</v>
+        <v>4.17</v>
       </c>
       <c r="F17" t="n">
-        <v>10.22</v>
+        <v>10.15</v>
       </c>
       <c r="G17" t="n">
-        <v>324.2</v>
+        <v>345.9</v>
       </c>
       <c r="H17" t="n">
-        <v>82</v>
+        <v>41.6</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>90.68000000000001</v>
+        <v>18.06</v>
       </c>
       <c r="K17" t="n">
-        <v>-42.19</v>
+        <v>89.88</v>
       </c>
       <c r="L17" t="n">
-        <v>100.01</v>
+        <v>91.68000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:14:39</t>
+          <t>08:17:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.78</v>
+        <v>4.62</v>
       </c>
       <c r="F18" t="n">
-        <v>7.48</v>
+        <v>10.97</v>
       </c>
       <c r="G18" t="n">
-        <v>327.8</v>
+        <v>336.4</v>
       </c>
       <c r="H18" t="n">
-        <v>77.3</v>
+        <v>31.7</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>87.70999999999999</v>
+        <v>-162.51</v>
       </c>
       <c r="K18" t="n">
-        <v>73.09</v>
+        <v>122.32</v>
       </c>
       <c r="L18" t="n">
-        <v>114.17</v>
+        <v>203.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:16:13</t>
+          <t>08:18:23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="F19" t="n">
-        <v>11.13</v>
+        <v>8.99</v>
       </c>
       <c r="G19" t="n">
-        <v>343.7</v>
+        <v>342.6</v>
       </c>
       <c r="H19" t="n">
-        <v>77.3</v>
+        <v>37.4</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>35.89</v>
+        <v>-98.55</v>
       </c>
       <c r="K19" t="n">
-        <v>94.33</v>
+        <v>19.73</v>
       </c>
       <c r="L19" t="n">
-        <v>100.93</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:22:12</t>
+          <t>08:24:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="F20" t="n">
-        <v>8.359999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>333.7</v>
+        <v>328.9</v>
       </c>
       <c r="H20" t="n">
-        <v>78.2</v>
+        <v>37.4</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>6.73</v>
+        <v>-193.83</v>
       </c>
       <c r="K20" t="n">
-        <v>120.62</v>
+        <v>186.47</v>
       </c>
       <c r="L20" t="n">
-        <v>120.81</v>
+        <v>268.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:24:24</t>
+          <t>08:25:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.86</v>
+        <v>4.28</v>
       </c>
       <c r="F21" t="n">
-        <v>8.73</v>
+        <v>12.29</v>
       </c>
       <c r="G21" t="n">
-        <v>341.3</v>
+        <v>338.9</v>
       </c>
       <c r="H21" t="n">
-        <v>79.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J21" t="n">
-        <v>112.98</v>
+        <v>-188.4</v>
       </c>
       <c r="K21" t="n">
-        <v>42.06</v>
+        <v>17.32</v>
       </c>
       <c r="L21" t="n">
-        <v>120.55</v>
+        <v>189.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:26:03</t>
+          <t>08:27:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.14</v>
+        <v>3.49</v>
       </c>
       <c r="F22" t="n">
-        <v>9.16</v>
+        <v>8.16</v>
       </c>
       <c r="G22" t="n">
-        <v>359.8</v>
+        <v>347.6</v>
       </c>
       <c r="H22" t="n">
-        <v>79.8</v>
+        <v>41.6</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>47.67</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>107.39</v>
+        <v>-116.19</v>
       </c>
       <c r="L22" t="n">
-        <v>117.5</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:29:33</t>
+          <t>08:31:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
       <c r="F23" t="n">
-        <v>7.07</v>
+        <v>9.94</v>
       </c>
       <c r="G23" t="n">
-        <v>338.4</v>
+        <v>328.8</v>
       </c>
       <c r="H23" t="n">
-        <v>79.09999999999999</v>
+        <v>45.1</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-156.18</v>
+        <v>-276.79</v>
       </c>
       <c r="K23" t="n">
-        <v>108.21</v>
+        <v>4.74</v>
       </c>
       <c r="L23" t="n">
-        <v>190</v>
+        <v>276.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:31:23</t>
+          <t>08:32:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.31</v>
+        <v>5.14</v>
       </c>
       <c r="F24" t="n">
-        <v>6.29</v>
+        <v>10.76</v>
       </c>
       <c r="G24" t="n">
-        <v>339.2</v>
+        <v>324.9</v>
       </c>
       <c r="H24" t="n">
-        <v>77.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>-164.17</v>
+        <v>-445.72</v>
       </c>
       <c r="K24" t="n">
-        <v>-22.88</v>
+        <v>75.42</v>
       </c>
       <c r="L24" t="n">
-        <v>165.76</v>
+        <v>452.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:32:34</t>
+          <t>08:33:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="F25" t="n">
-        <v>8.49</v>
+        <v>7.9</v>
       </c>
       <c r="G25" t="n">
-        <v>342</v>
+        <v>352.9</v>
       </c>
       <c r="H25" t="n">
-        <v>72.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-179.51</v>
+        <v>-207</v>
       </c>
       <c r="K25" t="n">
-        <v>53.81</v>
+        <v>71.64</v>
       </c>
       <c r="L25" t="n">
-        <v>187.41</v>
+        <v>219.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:36:54</t>
+          <t>08:38:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.16</v>
+        <v>3.09</v>
       </c>
       <c r="F26" t="n">
-        <v>8.84</v>
+        <v>7.66</v>
       </c>
       <c r="G26" t="n">
-        <v>331.8</v>
+        <v>331.9</v>
       </c>
       <c r="H26" t="n">
-        <v>80.2</v>
+        <v>52.8</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>140.49</v>
+        <v>-107.73</v>
       </c>
       <c r="K26" t="n">
-        <v>216.21</v>
+        <v>-227.35</v>
       </c>
       <c r="L26" t="n">
-        <v>257.85</v>
+        <v>251.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:38:56</t>
+          <t>08:39:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.95</v>
+        <v>4.17</v>
       </c>
       <c r="F27" t="n">
-        <v>8.44</v>
+        <v>11.78</v>
       </c>
       <c r="G27" t="n">
-        <v>321.4</v>
+        <v>353.2</v>
       </c>
       <c r="H27" t="n">
-        <v>76.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-181.67</v>
+        <v>-11.13</v>
       </c>
       <c r="K27" t="n">
-        <v>81.27</v>
+        <v>309.59</v>
       </c>
       <c r="L27" t="n">
-        <v>199.02</v>
+        <v>309.79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:40:19</t>
+          <t>08:41:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.62</v>
+        <v>4.28</v>
       </c>
       <c r="F28" t="n">
-        <v>12.05</v>
+        <v>12.3</v>
       </c>
       <c r="G28" t="n">
-        <v>338.3</v>
+        <v>332.3</v>
       </c>
       <c r="H28" t="n">
-        <v>86.8</v>
+        <v>55</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-33.21</v>
+        <v>358.73</v>
       </c>
       <c r="K28" t="n">
-        <v>246.91</v>
+        <v>135.1</v>
       </c>
       <c r="L28" t="n">
-        <v>249.14</v>
+        <v>383.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:50:26</t>
+          <t>08:52:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="F29" t="n">
-        <v>9.279999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="G29" t="n">
-        <v>339.1</v>
+        <v>322.4</v>
       </c>
       <c r="H29" t="n">
-        <v>78.7</v>
+        <v>42.2</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>44.88</v>
+        <v>36.23</v>
       </c>
       <c r="K29" t="n">
-        <v>-41.51</v>
+        <v>60.02</v>
       </c>
       <c r="L29" t="n">
-        <v>61.13</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:51:21</t>
+          <t>08:54:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="F30" t="n">
-        <v>11.21</v>
+        <v>10.86</v>
       </c>
       <c r="G30" t="n">
-        <v>346.6</v>
+        <v>350</v>
       </c>
       <c r="H30" t="n">
-        <v>89.5</v>
+        <v>66</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.99</v>
+        <v>-90.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-86.72</v>
+        <v>-5.94</v>
       </c>
       <c r="L30" t="n">
-        <v>86.81999999999999</v>
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:53:37</t>
+          <t>08:55:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.81</v>
+        <v>4.04</v>
       </c>
       <c r="F31" t="n">
-        <v>8.33</v>
+        <v>9.98</v>
       </c>
       <c r="G31" t="n">
-        <v>322.7</v>
+        <v>326.5</v>
       </c>
       <c r="H31" t="n">
-        <v>84.7</v>
+        <v>38.9</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>80.68000000000001</v>
+        <v>-25.11</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.67</v>
+        <v>-17.49</v>
       </c>
       <c r="L31" t="n">
-        <v>85.29000000000001</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:57:22</t>
+          <t>08:59:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="F32" t="n">
-        <v>12.16</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>336.5</v>
+        <v>321.6</v>
       </c>
       <c r="H32" t="n">
-        <v>75.8</v>
+        <v>35.1</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.57</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-94.08</v>
+        <v>47.45</v>
       </c>
       <c r="L32" t="n">
-        <v>94.25</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:00:02</t>
+          <t>09:01:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.51</v>
+        <v>4.4</v>
       </c>
       <c r="F33" t="n">
-        <v>11.82</v>
+        <v>12.3</v>
       </c>
       <c r="G33" t="n">
-        <v>357.9</v>
+        <v>348.5</v>
       </c>
       <c r="H33" t="n">
-        <v>81.09999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-23.02</v>
+        <v>108.38</v>
       </c>
       <c r="K33" t="n">
-        <v>79.76000000000001</v>
+        <v>-34.98</v>
       </c>
       <c r="L33" t="n">
-        <v>83.02</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:02:28</t>
+          <t>09:03:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.95</v>
+        <v>3.99</v>
       </c>
       <c r="F34" t="n">
-        <v>12.19</v>
+        <v>11.24</v>
       </c>
       <c r="G34" t="n">
-        <v>333.6</v>
+        <v>337.6</v>
       </c>
       <c r="H34" t="n">
-        <v>81.5</v>
+        <v>14.6</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>86.09</v>
+        <v>-66.7</v>
       </c>
       <c r="K34" t="n">
-        <v>-36.07</v>
+        <v>-55.51</v>
       </c>
       <c r="L34" t="n">
-        <v>93.34</v>
+        <v>86.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:07:17</t>
+          <t>09:09:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.18</v>
+        <v>3.78</v>
       </c>
       <c r="F35" t="n">
-        <v>9.77</v>
+        <v>11.38</v>
       </c>
       <c r="G35" t="n">
-        <v>347.1</v>
+        <v>337.4</v>
       </c>
       <c r="H35" t="n">
-        <v>84.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>-48.07</v>
+        <v>-26.74</v>
       </c>
       <c r="K35" t="n">
-        <v>-116.71</v>
+        <v>107.9</v>
       </c>
       <c r="L35" t="n">
-        <v>126.22</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:09:22</t>
+          <t>09:10:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.41</v>
+        <v>4.23</v>
       </c>
       <c r="F36" t="n">
-        <v>9.789999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="G36" t="n">
-        <v>334.9</v>
+        <v>343.7</v>
       </c>
       <c r="H36" t="n">
-        <v>80.7</v>
+        <v>67.3</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-121.07</v>
+        <v>47.53</v>
       </c>
       <c r="K36" t="n">
-        <v>47.13</v>
+        <v>130.5</v>
       </c>
       <c r="L36" t="n">
-        <v>129.92</v>
+        <v>138.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:11:04</t>
+          <t>09:11:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="F37" t="n">
-        <v>10.5</v>
+        <v>8.33</v>
       </c>
       <c r="G37" t="n">
-        <v>339.5</v>
+        <v>338.1</v>
       </c>
       <c r="H37" t="n">
-        <v>77.3</v>
+        <v>25</v>
       </c>
       <c r="I37" t="n">
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>-54.75</v>
+        <v>-21.83</v>
       </c>
       <c r="K37" t="n">
-        <v>104.24</v>
+        <v>165.02</v>
       </c>
       <c r="L37" t="n">
-        <v>117.74</v>
+        <v>166.46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:15:24</t>
+          <t>09:16:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.6</v>
+        <v>4.03</v>
       </c>
       <c r="F38" t="n">
-        <v>6.81</v>
+        <v>12</v>
       </c>
       <c r="G38" t="n">
-        <v>336.4</v>
+        <v>329.1</v>
       </c>
       <c r="H38" t="n">
-        <v>77.7</v>
+        <v>31.1</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-79.79000000000001</v>
+        <v>-126.42</v>
       </c>
       <c r="K38" t="n">
-        <v>-65.67</v>
+        <v>152.68</v>
       </c>
       <c r="L38" t="n">
-        <v>103.34</v>
+        <v>198.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:17:05</t>
+          <t>09:18:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="F39" t="n">
-        <v>10.1</v>
+        <v>12.3</v>
       </c>
       <c r="G39" t="n">
-        <v>347.3</v>
+        <v>332.9</v>
       </c>
       <c r="H39" t="n">
-        <v>78.90000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-140.35</v>
+        <v>188.47</v>
       </c>
       <c r="K39" t="n">
-        <v>19.25</v>
+        <v>163.78</v>
       </c>
       <c r="L39" t="n">
-        <v>141.66</v>
+        <v>249.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:18:53</t>
+          <t>09:20:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.72</v>
+        <v>3.86</v>
       </c>
       <c r="F40" t="n">
-        <v>9.640000000000001</v>
+        <v>11.59</v>
       </c>
       <c r="G40" t="n">
-        <v>352.4</v>
+        <v>333.5</v>
       </c>
       <c r="H40" t="n">
-        <v>84.40000000000001</v>
+        <v>21.8</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-130.51</v>
+        <v>18.06</v>
       </c>
       <c r="K40" t="n">
-        <v>173.2</v>
+        <v>254.09</v>
       </c>
       <c r="L40" t="n">
-        <v>216.87</v>
+        <v>254.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:23:26</t>
+          <t>09:24:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.89</v>
+        <v>4.08</v>
       </c>
       <c r="F41" t="n">
-        <v>10.42</v>
+        <v>10.46</v>
       </c>
       <c r="G41" t="n">
-        <v>330</v>
+        <v>345.8</v>
       </c>
       <c r="H41" t="n">
-        <v>82.2</v>
+        <v>93.8</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>54.32</v>
+        <v>-275.55</v>
       </c>
       <c r="K41" t="n">
-        <v>378.59</v>
+        <v>-208.72</v>
       </c>
       <c r="L41" t="n">
-        <v>382.47</v>
+        <v>345.68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:24:11</t>
+          <t>09:26:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.86</v>
+        <v>4.63</v>
       </c>
       <c r="F42" t="n">
-        <v>8.83</v>
+        <v>12.14</v>
       </c>
       <c r="G42" t="n">
-        <v>349.4</v>
+        <v>358.3</v>
       </c>
       <c r="H42" t="n">
-        <v>81.59999999999999</v>
+        <v>43.9</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-221.95</v>
+        <v>167.42</v>
       </c>
       <c r="K42" t="n">
-        <v>207.5</v>
+        <v>332.18</v>
       </c>
       <c r="L42" t="n">
-        <v>303.84</v>
+        <v>371.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:25:46</t>
+          <t>09:28:31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.23</v>
+        <v>3.83</v>
       </c>
       <c r="F43" t="n">
-        <v>9.970000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G43" t="n">
-        <v>339.3</v>
+        <v>334.6</v>
       </c>
       <c r="H43" t="n">
-        <v>83.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>341.95</v>
+        <v>56.64</v>
       </c>
       <c r="K43" t="n">
-        <v>74.8</v>
+        <v>251.13</v>
       </c>
       <c r="L43" t="n">
-        <v>350.03</v>
+        <v>257.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:37:38</t>
+          <t>09:37:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.82</v>
+        <v>3.95</v>
       </c>
       <c r="F44" t="n">
-        <v>12.3</v>
+        <v>12.24</v>
       </c>
       <c r="G44" t="n">
-        <v>335.9</v>
+        <v>335</v>
       </c>
       <c r="H44" t="n">
-        <v>84.3</v>
+        <v>37</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>21.17</v>
+        <v>6.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-77</v>
+        <v>59.46</v>
       </c>
       <c r="L44" t="n">
-        <v>79.86</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:39:50</t>
+          <t>09:39:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.72</v>
+        <v>4.26</v>
       </c>
       <c r="F45" t="n">
-        <v>12.3</v>
+        <v>11.11</v>
       </c>
       <c r="G45" t="n">
-        <v>331.2</v>
+        <v>351.6</v>
       </c>
       <c r="H45" t="n">
-        <v>78.59999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="I45" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-39.66</v>
+        <v>-41.2</v>
       </c>
       <c r="K45" t="n">
-        <v>50.1</v>
+        <v>-72.28</v>
       </c>
       <c r="L45" t="n">
-        <v>63.9</v>
+        <v>83.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:41:48</t>
+          <t>09:41:41</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.11</v>
+        <v>4.5</v>
       </c>
       <c r="F46" t="n">
-        <v>11.11</v>
+        <v>11.64</v>
       </c>
       <c r="G46" t="n">
-        <v>330.2</v>
+        <v>331.4</v>
       </c>
       <c r="H46" t="n">
-        <v>81.2</v>
+        <v>58.5</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.52</v>
+        <v>-13.38</v>
       </c>
       <c r="K46" t="n">
-        <v>58.5</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>65.53</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:45:26</t>
+          <t>09:46:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.32</v>
+        <v>4.11</v>
       </c>
       <c r="F47" t="n">
-        <v>11.01</v>
+        <v>8.41</v>
       </c>
       <c r="G47" t="n">
-        <v>333.7</v>
+        <v>346.9</v>
       </c>
       <c r="H47" t="n">
-        <v>82.3</v>
+        <v>57.1</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>1.53</v>
+        <v>-100.33</v>
       </c>
       <c r="K47" t="n">
-        <v>-98.88</v>
+        <v>63.12</v>
       </c>
       <c r="L47" t="n">
-        <v>98.89</v>
+        <v>118.53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:47:46</t>
+          <t>09:48:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="F48" t="n">
-        <v>12.3</v>
+        <v>10.97</v>
       </c>
       <c r="G48" t="n">
-        <v>337.1</v>
+        <v>341.3</v>
       </c>
       <c r="H48" t="n">
-        <v>83.7</v>
+        <v>40.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>-10.89</v>
+        <v>-43.28</v>
       </c>
       <c r="K48" t="n">
-        <v>81.37</v>
+        <v>111.15</v>
       </c>
       <c r="L48" t="n">
-        <v>82.09999999999999</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:49:34</t>
+          <t>09:49:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="F49" t="n">
-        <v>11.95</v>
+        <v>12.03</v>
       </c>
       <c r="G49" t="n">
-        <v>350</v>
+        <v>338.6</v>
       </c>
       <c r="H49" t="n">
-        <v>83.3</v>
+        <v>19</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>104.64</v>
+        <v>143.88</v>
       </c>
       <c r="K49" t="n">
-        <v>18.32</v>
+        <v>72.98</v>
       </c>
       <c r="L49" t="n">
-        <v>106.24</v>
+        <v>161.32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:55:32</t>
+          <t>09:53:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.05</v>
+        <v>4.46</v>
       </c>
       <c r="F50" t="n">
-        <v>12.3</v>
+        <v>10.58</v>
       </c>
       <c r="G50" t="n">
-        <v>349.6</v>
+        <v>338</v>
       </c>
       <c r="H50" t="n">
-        <v>73.2</v>
+        <v>45.8</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>149.26</v>
+        <v>-16.53</v>
       </c>
       <c r="K50" t="n">
-        <v>13.87</v>
+        <v>162.55</v>
       </c>
       <c r="L50" t="n">
-        <v>149.9</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:57:01</t>
+          <t>09:56:09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.63</v>
+        <v>4.35</v>
       </c>
       <c r="F51" t="n">
-        <v>12.08</v>
+        <v>10.86</v>
       </c>
       <c r="G51" t="n">
-        <v>329.6</v>
+        <v>341.2</v>
       </c>
       <c r="H51" t="n">
-        <v>77.8</v>
+        <v>51.7</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J51" t="n">
-        <v>-75.17</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-108.02</v>
+        <v>-152.47</v>
       </c>
       <c r="L51" t="n">
-        <v>131.6</v>
+        <v>167.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:58:09</t>
+          <t>09:58:03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.32</v>
+        <v>4.7</v>
       </c>
       <c r="F52" t="n">
-        <v>10.36</v>
+        <v>12.3</v>
       </c>
       <c r="G52" t="n">
-        <v>348.9</v>
+        <v>337.2</v>
       </c>
       <c r="H52" t="n">
-        <v>80</v>
+        <v>60.8</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J52" t="n">
-        <v>152.86</v>
+        <v>140.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-33.58</v>
+        <v>-14.25</v>
       </c>
       <c r="L52" t="n">
-        <v>156.51</v>
+        <v>141.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:03:49</t>
+          <t>10:03:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.48</v>
+        <v>3.94</v>
       </c>
       <c r="F53" t="n">
-        <v>12.3</v>
+        <v>11.69</v>
       </c>
       <c r="G53" t="n">
-        <v>331.3</v>
+        <v>338.8</v>
       </c>
       <c r="H53" t="n">
-        <v>77.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>184.02</v>
+        <v>-121.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.5</v>
+        <v>53.87</v>
       </c>
       <c r="L53" t="n">
-        <v>184.05</v>
+        <v>132.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:06:33</t>
+          <t>10:05:29</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="F54" t="n">
-        <v>10.62</v>
+        <v>11.72</v>
       </c>
       <c r="G54" t="n">
-        <v>335</v>
+        <v>346.9</v>
       </c>
       <c r="H54" t="n">
-        <v>80.7</v>
+        <v>59.3</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>-176.97</v>
+        <v>-102.55</v>
       </c>
       <c r="K54" t="n">
-        <v>31.04</v>
+        <v>-285.6</v>
       </c>
       <c r="L54" t="n">
-        <v>179.67</v>
+        <v>303.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:08:25</t>
+          <t>10:07:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.97</v>
+        <v>4.08</v>
       </c>
       <c r="F55" t="n">
-        <v>12.3</v>
+        <v>12.14</v>
       </c>
       <c r="G55" t="n">
-        <v>331.2</v>
+        <v>345.3</v>
       </c>
       <c r="H55" t="n">
-        <v>77.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>166.22</v>
+        <v>-158.48</v>
       </c>
       <c r="K55" t="n">
-        <v>195.82</v>
+        <v>151.63</v>
       </c>
       <c r="L55" t="n">
-        <v>256.86</v>
+        <v>219.33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:13:09</t>
+          <t>10:11:24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.1</v>
+        <v>4.57</v>
       </c>
       <c r="F56" t="n">
-        <v>12.3</v>
+        <v>11.91</v>
       </c>
       <c r="G56" t="n">
-        <v>334.4</v>
+        <v>338.4</v>
       </c>
       <c r="H56" t="n">
-        <v>86</v>
+        <v>40.1</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>-183.36</v>
+        <v>-51.77</v>
       </c>
       <c r="K56" t="n">
-        <v>192.86</v>
+        <v>346.27</v>
       </c>
       <c r="L56" t="n">
-        <v>266.12</v>
+        <v>350.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:14:20</t>
+          <t>10:12:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.18</v>
+        <v>4.96</v>
       </c>
       <c r="F57" t="n">
         <v>12.3</v>
       </c>
       <c r="G57" t="n">
-        <v>327.8</v>
+        <v>336.7</v>
       </c>
       <c r="H57" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>283.63</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>96.65000000000001</v>
+        <v>-429.99</v>
       </c>
       <c r="L57" t="n">
-        <v>299.64</v>
+        <v>437.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:15:46</t>
+          <t>10:13:57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.74</v>
+        <v>4.39</v>
       </c>
       <c r="F58" t="n">
-        <v>10.81</v>
+        <v>10.59</v>
       </c>
       <c r="G58" t="n">
-        <v>335.3</v>
+        <v>342.2</v>
       </c>
       <c r="H58" t="n">
-        <v>77.7</v>
+        <v>47.9</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>81.05</v>
+        <v>-267.66</v>
       </c>
       <c r="K58" t="n">
-        <v>488.36</v>
+        <v>-188.9</v>
       </c>
       <c r="L58" t="n">
-        <v>495.05</v>
+        <v>327.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:26:57</t>
+          <t>10:25:34</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.26</v>
+        <v>4.18</v>
       </c>
       <c r="F59" t="n">
-        <v>10.7</v>
+        <v>10.31</v>
       </c>
       <c r="G59" t="n">
-        <v>334</v>
+        <v>333.9</v>
       </c>
       <c r="H59" t="n">
-        <v>85.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-38.92</v>
+        <v>30.02</v>
       </c>
       <c r="K59" t="n">
-        <v>57.31</v>
+        <v>87.63</v>
       </c>
       <c r="L59" t="n">
-        <v>69.27</v>
+        <v>92.63</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:29:06</t>
+          <t>10:27:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.02</v>
+        <v>4.13</v>
       </c>
       <c r="F60" t="n">
         <v>12.3</v>
       </c>
       <c r="G60" t="n">
-        <v>344.2</v>
+        <v>323.9</v>
       </c>
       <c r="H60" t="n">
-        <v>69.7</v>
+        <v>76.5</v>
       </c>
       <c r="I60" t="n">
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>38.27</v>
+        <v>-29.85</v>
       </c>
       <c r="K60" t="n">
-        <v>56.87</v>
+        <v>-76.45999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>68.55</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:31:08</t>
+          <t>10:29:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.91</v>
+        <v>4.37</v>
       </c>
       <c r="F61" t="n">
         <v>12.3</v>
       </c>
       <c r="G61" t="n">
-        <v>328.7</v>
+        <v>350.3</v>
       </c>
       <c r="H61" t="n">
-        <v>80.3</v>
+        <v>33.9</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J61" t="n">
-        <v>-24.3</v>
+        <v>-70.86</v>
       </c>
       <c r="K61" t="n">
-        <v>-55.15</v>
+        <v>63.62</v>
       </c>
       <c r="L61" t="n">
-        <v>60.27</v>
+        <v>95.23</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:36:03</t>
+          <t>10:33:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.95</v>
+        <v>4.69</v>
       </c>
       <c r="F62" t="n">
-        <v>6.09</v>
+        <v>12.3</v>
       </c>
       <c r="G62" t="n">
-        <v>340.5</v>
+        <v>336.7</v>
       </c>
       <c r="H62" t="n">
-        <v>79.40000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>31.31</v>
+        <v>-71.54000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.52</v>
+        <v>111.03</v>
       </c>
       <c r="L62" t="n">
-        <v>31.64</v>
+        <v>132.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:37:32</t>
+          <t>10:35:17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.15</v>
+        <v>4.58</v>
       </c>
       <c r="F63" t="n">
         <v>12.3</v>
       </c>
       <c r="G63" t="n">
-        <v>340.4</v>
+        <v>338.4</v>
       </c>
       <c r="H63" t="n">
-        <v>80.90000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="I63" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>67.88</v>
+        <v>-115.47</v>
       </c>
       <c r="K63" t="n">
-        <v>34.97</v>
+        <v>42.22</v>
       </c>
       <c r="L63" t="n">
-        <v>76.34999999999999</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:39:29</t>
+          <t>10:37:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.47</v>
+        <v>4.52</v>
       </c>
       <c r="F64" t="n">
         <v>12.3</v>
       </c>
       <c r="G64" t="n">
-        <v>334.5</v>
+        <v>339.5</v>
       </c>
       <c r="H64" t="n">
-        <v>73.90000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-83.64</v>
+        <v>-122.48</v>
       </c>
       <c r="K64" t="n">
-        <v>13.57</v>
+        <v>33.2</v>
       </c>
       <c r="L64" t="n">
-        <v>84.73999999999999</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:44:03</t>
+          <t>10:40:54</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.99</v>
+        <v>5.04</v>
       </c>
       <c r="F65" t="n">
         <v>12.3</v>
       </c>
       <c r="G65" t="n">
-        <v>331.3</v>
+        <v>325.3</v>
       </c>
       <c r="H65" t="n">
-        <v>80.7</v>
+        <v>49.7</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>-110.33</v>
+        <v>47.84</v>
       </c>
       <c r="K65" t="n">
-        <v>-42.51</v>
+        <v>192.36</v>
       </c>
       <c r="L65" t="n">
-        <v>118.24</v>
+        <v>198.21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:46:01</t>
+          <t>10:42:22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.08</v>
+        <v>4.55</v>
       </c>
       <c r="F66" t="n">
         <v>12.3</v>
       </c>
       <c r="G66" t="n">
-        <v>336.3</v>
+        <v>326.8</v>
       </c>
       <c r="H66" t="n">
-        <v>81.59999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>173.28</v>
+        <v>-177.71</v>
       </c>
       <c r="K66" t="n">
-        <v>24.35</v>
+        <v>3.2</v>
       </c>
       <c r="L66" t="n">
-        <v>174.99</v>
+        <v>177.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:47:52</t>
+          <t>10:44:16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.8</v>
+        <v>4.36</v>
       </c>
       <c r="F67" t="n">
-        <v>10.57</v>
+        <v>10.93</v>
       </c>
       <c r="G67" t="n">
-        <v>317.2</v>
+        <v>343.9</v>
       </c>
       <c r="H67" t="n">
-        <v>84.3</v>
+        <v>41</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-46.34</v>
+        <v>-99.20999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>103.52</v>
+        <v>-157.08</v>
       </c>
       <c r="L67" t="n">
-        <v>113.42</v>
+        <v>185.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:51:39</t>
+          <t>10:48:06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.36</v>
+        <v>4.39</v>
       </c>
       <c r="F68" t="n">
-        <v>12.3</v>
+        <v>10.95</v>
       </c>
       <c r="G68" t="n">
-        <v>337.6</v>
+        <v>348.4</v>
       </c>
       <c r="H68" t="n">
-        <v>91.59999999999999</v>
+        <v>40.6</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>-184.63</v>
+        <v>-72.92</v>
       </c>
       <c r="K68" t="n">
-        <v>309.4</v>
+        <v>283.94</v>
       </c>
       <c r="L68" t="n">
-        <v>360.3</v>
+        <v>293.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:53:58</t>
+          <t>10:49:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="F69" t="n">
-        <v>12.3</v>
+        <v>11.15</v>
       </c>
       <c r="G69" t="n">
-        <v>339.5</v>
+        <v>336.5</v>
       </c>
       <c r="H69" t="n">
-        <v>78.90000000000001</v>
+        <v>30.5</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>236.37</v>
+        <v>241.53</v>
       </c>
       <c r="K69" t="n">
-        <v>22.03</v>
+        <v>-176.24</v>
       </c>
       <c r="L69" t="n">
-        <v>237.4</v>
+        <v>298.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:55:21</t>
+          <t>10:52:22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="F70" t="n">
-        <v>12.3</v>
+        <v>11.78</v>
       </c>
       <c r="G70" t="n">
-        <v>346.5</v>
+        <v>344.3</v>
       </c>
       <c r="H70" t="n">
-        <v>81.09999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>254.5</v>
+        <v>-150.27</v>
       </c>
       <c r="K70" t="n">
-        <v>17</v>
+        <v>-248.94</v>
       </c>
       <c r="L70" t="n">
-        <v>255.07</v>
+        <v>290.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:59:48</t>
+          <t>10:57:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.24</v>
+        <v>4.43</v>
       </c>
       <c r="F71" t="n">
         <v>12.3</v>
       </c>
       <c r="G71" t="n">
-        <v>341.7</v>
+        <v>311.7</v>
       </c>
       <c r="H71" t="n">
-        <v>86.7</v>
+        <v>73.2</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>25.26</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>267.61</v>
+        <v>316.11</v>
       </c>
       <c r="L71" t="n">
-        <v>268.8</v>
+        <v>327.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11:01:00</t>
+          <t>10:58:20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.8</v>
+        <v>4.44</v>
       </c>
       <c r="F72" t="n">
         <v>12.3</v>
       </c>
       <c r="G72" t="n">
-        <v>339.7</v>
+        <v>336.6</v>
       </c>
       <c r="H72" t="n">
-        <v>79</v>
+        <v>44.7</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>111.15</v>
+        <v>-328.72</v>
       </c>
       <c r="K72" t="n">
-        <v>290.68</v>
+        <v>-55.51</v>
       </c>
       <c r="L72" t="n">
-        <v>311.21</v>
+        <v>333.37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11:01:41</t>
+          <t>10:59:08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="F73" t="n">
         <v>12.3</v>
       </c>
       <c r="G73" t="n">
-        <v>336.6</v>
+        <v>340.5</v>
       </c>
       <c r="H73" t="n">
-        <v>73.90000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-42.22</v>
+        <v>-189.85</v>
       </c>
       <c r="K73" t="n">
-        <v>-248.58</v>
+        <v>271.13</v>
       </c>
       <c r="L73" t="n">
-        <v>252.14</v>
+        <v>330.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:13:32</t>
+          <t>11:09:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.95</v>
+        <v>4.98</v>
       </c>
       <c r="F74" t="n">
-        <v>10.83</v>
+        <v>11.37</v>
       </c>
       <c r="G74" t="n">
-        <v>333.4</v>
+        <v>329.8</v>
       </c>
       <c r="H74" t="n">
-        <v>86.40000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>-64.84</v>
+        <v>-133.46</v>
       </c>
       <c r="K74" t="n">
-        <v>12.23</v>
+        <v>-3.2</v>
       </c>
       <c r="L74" t="n">
-        <v>65.98</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:15:36</t>
+          <t>11:10:18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="F75" t="n">
-        <v>11.74</v>
+        <v>10.85</v>
       </c>
       <c r="G75" t="n">
-        <v>337.4</v>
+        <v>339.4</v>
       </c>
       <c r="H75" t="n">
-        <v>82.40000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>78.90000000000001</v>
+        <v>-21.8</v>
       </c>
       <c r="K75" t="n">
-        <v>42.4</v>
+        <v>51.08</v>
       </c>
       <c r="L75" t="n">
-        <v>89.58</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:16:53</t>
+          <t>11:11:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="F76" t="n">
         <v>12.3</v>
       </c>
       <c r="G76" t="n">
-        <v>322.8</v>
+        <v>340.8</v>
       </c>
       <c r="H76" t="n">
-        <v>78.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>-64.64</v>
+        <v>-55.18</v>
       </c>
       <c r="K76" t="n">
-        <v>-50.86</v>
+        <v>52.19</v>
       </c>
       <c r="L76" t="n">
-        <v>82.25</v>
+        <v>75.95</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:22:05</t>
+          <t>11:16:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="F77" t="n">
         <v>12.3</v>
       </c>
       <c r="G77" t="n">
-        <v>341.9</v>
+        <v>349.3</v>
       </c>
       <c r="H77" t="n">
-        <v>84.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I77" t="n">
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>88.68000000000001</v>
+        <v>7.11</v>
       </c>
       <c r="K77" t="n">
-        <v>-25.56</v>
+        <v>153.09</v>
       </c>
       <c r="L77" t="n">
-        <v>92.29000000000001</v>
+        <v>153.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:23:28</t>
+          <t>11:17:07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.12</v>
+        <v>4.53</v>
       </c>
       <c r="F78" t="n">
-        <v>12.3</v>
+        <v>12.02</v>
       </c>
       <c r="G78" t="n">
-        <v>336.6</v>
+        <v>347.9</v>
       </c>
       <c r="H78" t="n">
-        <v>83.5</v>
+        <v>64.2</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-18.52</v>
+        <v>73.28</v>
       </c>
       <c r="K78" t="n">
-        <v>-74.78</v>
+        <v>109.9</v>
       </c>
       <c r="L78" t="n">
-        <v>77.04000000000001</v>
+        <v>132.09</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:24:26</t>
+          <t>11:17:43</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.94</v>
+        <v>4.67</v>
       </c>
       <c r="F79" t="n">
-        <v>11.51</v>
+        <v>12.3</v>
       </c>
       <c r="G79" t="n">
-        <v>335.4</v>
+        <v>337.5</v>
       </c>
       <c r="H79" t="n">
-        <v>83.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-18.31</v>
+        <v>44.68</v>
       </c>
       <c r="K79" t="n">
-        <v>-73.42</v>
+        <v>-168.96</v>
       </c>
       <c r="L79" t="n">
-        <v>75.67</v>
+        <v>174.77</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:30:27</t>
+          <t>11:21:39</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
       <c r="F80" t="n">
         <v>12.3</v>
       </c>
       <c r="G80" t="n">
-        <v>343.6</v>
+        <v>348</v>
       </c>
       <c r="H80" t="n">
-        <v>88</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>-152.6</v>
+        <v>-188.35</v>
       </c>
       <c r="K80" t="n">
-        <v>7.58</v>
+        <v>275.61</v>
       </c>
       <c r="L80" t="n">
-        <v>152.79</v>
+        <v>333.82</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:32:02</t>
+          <t>11:23:38</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.9</v>
+        <v>4.76</v>
       </c>
       <c r="F81" t="n">
         <v>12.3</v>
       </c>
       <c r="G81" t="n">
-        <v>334.4</v>
+        <v>340.4</v>
       </c>
       <c r="H81" t="n">
-        <v>88.40000000000001</v>
+        <v>50.1</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>-164.33</v>
+        <v>148.04</v>
       </c>
       <c r="K81" t="n">
-        <v>-38.7</v>
+        <v>47.29</v>
       </c>
       <c r="L81" t="n">
-        <v>168.82</v>
+        <v>155.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:34:17</t>
+          <t>11:25:12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.76</v>
+        <v>4.29</v>
       </c>
       <c r="F82" t="n">
-        <v>12.3</v>
+        <v>11.38</v>
       </c>
       <c r="G82" t="n">
-        <v>355.2</v>
+        <v>323.6</v>
       </c>
       <c r="H82" t="n">
-        <v>78.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>-94.83</v>
+        <v>58.7</v>
       </c>
       <c r="K82" t="n">
-        <v>180.12</v>
+        <v>-177.78</v>
       </c>
       <c r="L82" t="n">
-        <v>203.55</v>
+        <v>187.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:39:03</t>
+          <t>11:30:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.99</v>
+        <v>4.54</v>
       </c>
       <c r="F83" t="n">
         <v>12.3</v>
       </c>
       <c r="G83" t="n">
-        <v>325.5</v>
+        <v>342.3</v>
       </c>
       <c r="H83" t="n">
-        <v>80.90000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J83" t="n">
-        <v>61.78</v>
+        <v>-281.19</v>
       </c>
       <c r="K83" t="n">
-        <v>203.38</v>
+        <v>103.51</v>
       </c>
       <c r="L83" t="n">
-        <v>212.56</v>
+        <v>299.64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:39:45</t>
+          <t>11:31:13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3568,31 +3568,31 @@
         <v>4.67</v>
       </c>
       <c r="F84" t="n">
-        <v>11.91</v>
+        <v>12.3</v>
       </c>
       <c r="G84" t="n">
-        <v>343</v>
+        <v>345.5</v>
       </c>
       <c r="H84" t="n">
-        <v>84.5</v>
+        <v>53.7</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>60.8</v>
+        <v>44.03</v>
       </c>
       <c r="K84" t="n">
-        <v>216.54</v>
+        <v>254.18</v>
       </c>
       <c r="L84" t="n">
-        <v>224.91</v>
+        <v>257.96</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:40:55</t>
+          <t>11:32:34</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.73</v>
+        <v>4.18</v>
       </c>
       <c r="F85" t="n">
-        <v>12.3</v>
+        <v>9.58</v>
       </c>
       <c r="G85" t="n">
-        <v>329.5</v>
+        <v>345</v>
       </c>
       <c r="H85" t="n">
-        <v>77.3</v>
+        <v>50.9</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>62.73</v>
+        <v>-225.76</v>
       </c>
       <c r="K85" t="n">
-        <v>252.27</v>
+        <v>160.06</v>
       </c>
       <c r="L85" t="n">
-        <v>259.95</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:45:26</t>
+          <t>11:36:51</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.93</v>
+        <v>5.38</v>
       </c>
       <c r="F86" t="n">
         <v>12.3</v>
       </c>
       <c r="G86" t="n">
-        <v>321.6</v>
+        <v>339.6</v>
       </c>
       <c r="H86" t="n">
-        <v>84.8</v>
+        <v>88</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>-195.38</v>
+        <v>-260.25</v>
       </c>
       <c r="K86" t="n">
-        <v>304.04</v>
+        <v>386.53</v>
       </c>
       <c r="L86" t="n">
-        <v>361.41</v>
+        <v>465.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:47:58</t>
+          <t>11:37:35</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.9</v>
+        <v>4.87</v>
       </c>
       <c r="F87" t="n">
         <v>12.3</v>
       </c>
       <c r="G87" t="n">
-        <v>344.5</v>
+        <v>348.1</v>
       </c>
       <c r="H87" t="n">
-        <v>83.59999999999999</v>
+        <v>45.1</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>-236.47</v>
+        <v>-354.2</v>
       </c>
       <c r="K87" t="n">
-        <v>-89.48</v>
+        <v>19.77</v>
       </c>
       <c r="L87" t="n">
-        <v>252.84</v>
+        <v>354.75</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:49:26</t>
+          <t>11:38:38</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.8</v>
+        <v>4.73</v>
       </c>
       <c r="F88" t="n">
-        <v>11.2</v>
+        <v>12.15</v>
       </c>
       <c r="G88" t="n">
-        <v>345.4</v>
+        <v>331.4</v>
       </c>
       <c r="H88" t="n">
-        <v>75.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>79.06999999999999</v>
+        <v>-362.1</v>
       </c>
       <c r="K88" t="n">
-        <v>-7.41</v>
+        <v>337.45</v>
       </c>
       <c r="L88" t="n">
-        <v>79.42</v>
+        <v>494.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="F14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="G14" t="n">
-        <v>326.8</v>
+        <v>332.2</v>
       </c>
       <c r="H14" t="n">
-        <v>42.9</v>
+        <v>71.7</v>
       </c>
       <c r="I14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-76.69</v>
+        <v>-55.72</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.75</v>
+        <v>-56.17</v>
       </c>
       <c r="L14" t="n">
-        <v>76.91</v>
+        <v>79.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:08:01</t>
+          <t>08:08:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.24</v>
+        <v>4.45</v>
       </c>
       <c r="F15" t="n">
-        <v>8.02</v>
+        <v>11.25</v>
       </c>
       <c r="G15" t="n">
-        <v>335.5</v>
+        <v>320.2</v>
       </c>
       <c r="H15" t="n">
-        <v>39.8</v>
+        <v>29.4</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-33.21</v>
+        <v>-117.9</v>
       </c>
       <c r="K15" t="n">
-        <v>68.64</v>
+        <v>-45.21</v>
       </c>
       <c r="L15" t="n">
-        <v>76.26000000000001</v>
+        <v>126.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:10:08</t>
+          <t>08:09:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="F16" t="n">
-        <v>9.619999999999999</v>
+        <v>11.09</v>
       </c>
       <c r="G16" t="n">
-        <v>341.3</v>
+        <v>345.1</v>
       </c>
       <c r="H16" t="n">
-        <v>60.5</v>
+        <v>83.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.7</v>
+        <v>-50</v>
       </c>
       <c r="K16" t="n">
-        <v>23.44</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>56.76</v>
+        <v>83.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:14:53</t>
+          <t>08:13:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="F17" t="n">
-        <v>10.15</v>
+        <v>10.33</v>
       </c>
       <c r="G17" t="n">
-        <v>345.9</v>
+        <v>348.3</v>
       </c>
       <c r="H17" t="n">
-        <v>41.6</v>
+        <v>52.1</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>18.06</v>
+        <v>-108.82</v>
       </c>
       <c r="K17" t="n">
-        <v>89.88</v>
+        <v>-20.31</v>
       </c>
       <c r="L17" t="n">
-        <v>91.68000000000001</v>
+        <v>110.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:17:02</t>
+          <t>08:15:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.62</v>
+        <v>3.73</v>
       </c>
       <c r="F18" t="n">
-        <v>10.97</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>336.4</v>
+        <v>339.1</v>
       </c>
       <c r="H18" t="n">
-        <v>31.7</v>
+        <v>47.9</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-162.51</v>
+        <v>64.05</v>
       </c>
       <c r="K18" t="n">
-        <v>122.32</v>
+        <v>-83.13</v>
       </c>
       <c r="L18" t="n">
-        <v>203.4</v>
+        <v>104.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:18:23</t>
+          <t>08:17:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -838,31 +838,31 @@
         <v>3.64</v>
       </c>
       <c r="F19" t="n">
-        <v>8.99</v>
+        <v>10.37</v>
       </c>
       <c r="G19" t="n">
-        <v>342.6</v>
+        <v>334.6</v>
       </c>
       <c r="H19" t="n">
-        <v>37.4</v>
+        <v>61.4</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>-98.55</v>
+        <v>-71.3</v>
       </c>
       <c r="K19" t="n">
-        <v>19.73</v>
+        <v>-69.63</v>
       </c>
       <c r="L19" t="n">
-        <v>100.5</v>
+        <v>99.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:24:09</t>
+          <t>08:21:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="F20" t="n">
-        <v>9.970000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="G20" t="n">
-        <v>328.9</v>
+        <v>338.6</v>
       </c>
       <c r="H20" t="n">
-        <v>37.4</v>
+        <v>53.1</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>-193.83</v>
+        <v>170.19</v>
       </c>
       <c r="K20" t="n">
-        <v>186.47</v>
+        <v>119.16</v>
       </c>
       <c r="L20" t="n">
-        <v>268.96</v>
+        <v>207.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:25:37</t>
+          <t>08:24:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.28</v>
+        <v>4.01</v>
       </c>
       <c r="F21" t="n">
-        <v>12.29</v>
+        <v>10.02</v>
       </c>
       <c r="G21" t="n">
         <v>338.9</v>
       </c>
       <c r="H21" t="n">
-        <v>69.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>-188.4</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>17.32</v>
+        <v>122.52</v>
       </c>
       <c r="L21" t="n">
-        <v>189.2</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:27:27</t>
+          <t>08:26:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.49</v>
+        <v>4.09</v>
       </c>
       <c r="F22" t="n">
-        <v>8.16</v>
+        <v>10.68</v>
       </c>
       <c r="G22" t="n">
-        <v>347.6</v>
+        <v>330.5</v>
       </c>
       <c r="H22" t="n">
-        <v>41.6</v>
+        <v>55.4</v>
       </c>
       <c r="I22" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>2.96</v>
+        <v>58.35</v>
       </c>
       <c r="K22" t="n">
-        <v>-116.19</v>
+        <v>-135.65</v>
       </c>
       <c r="L22" t="n">
-        <v>116.22</v>
+        <v>147.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:31:20</t>
+          <t>08:30:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.15</v>
+        <v>4.36</v>
       </c>
       <c r="F23" t="n">
-        <v>9.94</v>
+        <v>11.4</v>
       </c>
       <c r="G23" t="n">
-        <v>328.8</v>
+        <v>335.5</v>
       </c>
       <c r="H23" t="n">
-        <v>45.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>-276.79</v>
+        <v>214.38</v>
       </c>
       <c r="K23" t="n">
-        <v>4.74</v>
+        <v>164.22</v>
       </c>
       <c r="L23" t="n">
-        <v>276.83</v>
+        <v>270.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:32:53</t>
+          <t>08:31:23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.14</v>
+        <v>3.3</v>
       </c>
       <c r="F24" t="n">
-        <v>10.76</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>324.9</v>
+        <v>330.3</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J24" t="n">
-        <v>-445.72</v>
+        <v>203.86</v>
       </c>
       <c r="K24" t="n">
-        <v>75.42</v>
+        <v>52.64</v>
       </c>
       <c r="L24" t="n">
-        <v>452.06</v>
+        <v>210.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:33:42</t>
+          <t>08:33:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.57</v>
+        <v>4.92</v>
       </c>
       <c r="F25" t="n">
-        <v>7.9</v>
+        <v>12.3</v>
       </c>
       <c r="G25" t="n">
-        <v>352.9</v>
+        <v>334.6</v>
       </c>
       <c r="H25" t="n">
-        <v>70.2</v>
+        <v>58.2</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>-207</v>
+        <v>330.41</v>
       </c>
       <c r="K25" t="n">
-        <v>71.64</v>
+        <v>-118.76</v>
       </c>
       <c r="L25" t="n">
-        <v>219.04</v>
+        <v>351.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:38:10</t>
+          <t>08:39:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.09</v>
+        <v>3.9</v>
       </c>
       <c r="F26" t="n">
-        <v>7.66</v>
+        <v>10.09</v>
       </c>
       <c r="G26" t="n">
-        <v>331.9</v>
+        <v>332</v>
       </c>
       <c r="H26" t="n">
-        <v>52.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-107.73</v>
+        <v>-86.31999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-227.35</v>
+        <v>-282.4</v>
       </c>
       <c r="L26" t="n">
-        <v>251.58</v>
+        <v>295.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:39:57</t>
+          <t>08:40:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="F27" t="n">
-        <v>11.78</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>353.2</v>
+        <v>342.9</v>
       </c>
       <c r="H27" t="n">
-        <v>67.09999999999999</v>
+        <v>41.9</v>
       </c>
       <c r="I27" t="n">
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-11.13</v>
+        <v>263.18</v>
       </c>
       <c r="K27" t="n">
-        <v>309.59</v>
+        <v>-277.83</v>
       </c>
       <c r="L27" t="n">
-        <v>309.79</v>
+        <v>382.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:41:03</t>
+          <t>08:41:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.28</v>
+        <v>3.71</v>
       </c>
       <c r="F28" t="n">
-        <v>12.3</v>
+        <v>8.92</v>
       </c>
       <c r="G28" t="n">
-        <v>332.3</v>
+        <v>334.5</v>
       </c>
       <c r="H28" t="n">
-        <v>55</v>
+        <v>38.5</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>358.73</v>
+        <v>-331.62</v>
       </c>
       <c r="K28" t="n">
-        <v>135.1</v>
+        <v>5.62</v>
       </c>
       <c r="L28" t="n">
-        <v>383.32</v>
+        <v>331.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:52:51</t>
+          <t>08:53:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.82</v>
+        <v>4.42</v>
       </c>
       <c r="F29" t="n">
-        <v>8.57</v>
+        <v>12.3</v>
       </c>
       <c r="G29" t="n">
-        <v>322.4</v>
+        <v>337.4</v>
       </c>
       <c r="H29" t="n">
-        <v>42.2</v>
+        <v>59.1</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>36.23</v>
+        <v>-83.89</v>
       </c>
       <c r="K29" t="n">
-        <v>60.02</v>
+        <v>-66.56</v>
       </c>
       <c r="L29" t="n">
-        <v>70.11</v>
+        <v>107.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:54:25</t>
+          <t>08:55:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="F30" t="n">
-        <v>10.86</v>
+        <v>12.01</v>
       </c>
       <c r="G30" t="n">
-        <v>350</v>
+        <v>338.3</v>
       </c>
       <c r="H30" t="n">
-        <v>66</v>
+        <v>84.8</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>-90.09999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.94</v>
+        <v>86.75</v>
       </c>
       <c r="L30" t="n">
-        <v>90.29000000000001</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:55:58</t>
+          <t>08:57:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.04</v>
+        <v>3.57</v>
       </c>
       <c r="F31" t="n">
-        <v>9.98</v>
+        <v>10.42</v>
       </c>
       <c r="G31" t="n">
-        <v>326.5</v>
+        <v>346.7</v>
       </c>
       <c r="H31" t="n">
-        <v>38.9</v>
+        <v>35.1</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.11</v>
+        <v>-79.28</v>
       </c>
       <c r="K31" t="n">
-        <v>-17.49</v>
+        <v>0.24</v>
       </c>
       <c r="L31" t="n">
-        <v>30.6</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:59:55</t>
+          <t>09:01:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.35</v>
+        <v>4.17</v>
       </c>
       <c r="F32" t="n">
-        <v>8.880000000000001</v>
+        <v>10.34</v>
       </c>
       <c r="G32" t="n">
-        <v>321.6</v>
+        <v>332</v>
       </c>
       <c r="H32" t="n">
-        <v>35.1</v>
+        <v>55.5</v>
       </c>
       <c r="I32" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-74.90000000000001</v>
+        <v>-69.94</v>
       </c>
       <c r="K32" t="n">
-        <v>47.45</v>
+        <v>91.08</v>
       </c>
       <c r="L32" t="n">
-        <v>88.66</v>
+        <v>114.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:01:39</t>
+          <t>09:02:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,28 +1423,28 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="F33" t="n">
-        <v>12.3</v>
+        <v>11.71</v>
       </c>
       <c r="G33" t="n">
-        <v>348.5</v>
+        <v>345.7</v>
       </c>
       <c r="H33" t="n">
-        <v>34.9</v>
+        <v>60.2</v>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>108.38</v>
+        <v>68.19</v>
       </c>
       <c r="K33" t="n">
-        <v>-34.98</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>113.89</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="34">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.99</v>
+        <v>3.66</v>
       </c>
       <c r="F34" t="n">
-        <v>11.24</v>
+        <v>9.73</v>
       </c>
       <c r="G34" t="n">
-        <v>337.6</v>
+        <v>335.2</v>
       </c>
       <c r="H34" t="n">
-        <v>14.6</v>
+        <v>28.3</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-66.7</v>
+        <v>35.35</v>
       </c>
       <c r="K34" t="n">
-        <v>-55.51</v>
+        <v>70.63</v>
       </c>
       <c r="L34" t="n">
-        <v>86.78</v>
+        <v>78.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:09:25</t>
+          <t>09:09:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="F35" t="n">
-        <v>11.38</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>337.4</v>
+        <v>337.9</v>
       </c>
       <c r="H35" t="n">
-        <v>58.3</v>
+        <v>66.8</v>
       </c>
       <c r="I35" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-26.74</v>
+        <v>25.16</v>
       </c>
       <c r="K35" t="n">
-        <v>107.9</v>
+        <v>114.92</v>
       </c>
       <c r="L35" t="n">
-        <v>111.16</v>
+        <v>117.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:10:07</t>
+          <t>09:12:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.23</v>
+        <v>3.97</v>
       </c>
       <c r="F36" t="n">
-        <v>12.3</v>
+        <v>9.76</v>
       </c>
       <c r="G36" t="n">
-        <v>343.7</v>
+        <v>337.6</v>
       </c>
       <c r="H36" t="n">
-        <v>67.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>47.53</v>
+        <v>-99.37</v>
       </c>
       <c r="K36" t="n">
-        <v>130.5</v>
+        <v>-135.3</v>
       </c>
       <c r="L36" t="n">
-        <v>138.88</v>
+        <v>167.87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:11:52</t>
+          <t>09:12:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="F37" t="n">
-        <v>8.33</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>338.1</v>
+        <v>337.2</v>
       </c>
       <c r="H37" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I37" t="n">
         <v>25</v>
       </c>
-      <c r="I37" t="n">
-        <v>27</v>
-      </c>
       <c r="J37" t="n">
-        <v>-21.83</v>
+        <v>152.11</v>
       </c>
       <c r="K37" t="n">
-        <v>165.02</v>
+        <v>56.51</v>
       </c>
       <c r="L37" t="n">
-        <v>166.46</v>
+        <v>162.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:16:56</t>
+          <t>09:16:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="F38" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="G38" t="n">
-        <v>329.1</v>
+        <v>336.2</v>
       </c>
       <c r="H38" t="n">
-        <v>31.1</v>
+        <v>54</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-126.42</v>
+        <v>118.72</v>
       </c>
       <c r="K38" t="n">
-        <v>152.68</v>
+        <v>275.34</v>
       </c>
       <c r="L38" t="n">
-        <v>198.22</v>
+        <v>299.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:18:35</t>
+          <t>09:17:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.3</v>
+        <v>4.08</v>
       </c>
       <c r="F39" t="n">
-        <v>12.3</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>332.9</v>
+        <v>337.3</v>
       </c>
       <c r="H39" t="n">
-        <v>62.5</v>
+        <v>58.2</v>
       </c>
       <c r="I39" t="n">
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>188.47</v>
+        <v>218.3</v>
       </c>
       <c r="K39" t="n">
-        <v>163.78</v>
+        <v>137.89</v>
       </c>
       <c r="L39" t="n">
-        <v>249.69</v>
+        <v>258.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:20:28</t>
+          <t>09:19:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.86</v>
+        <v>4.02</v>
       </c>
       <c r="F40" t="n">
-        <v>11.59</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>333.5</v>
+        <v>345.5</v>
       </c>
       <c r="H40" t="n">
-        <v>21.8</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>18.06</v>
+        <v>204.77</v>
       </c>
       <c r="K40" t="n">
-        <v>254.09</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>254.73</v>
+        <v>224.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:24:12</t>
+          <t>09:24:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="F41" t="n">
-        <v>10.46</v>
+        <v>12.3</v>
       </c>
       <c r="G41" t="n">
-        <v>345.8</v>
+        <v>342.8</v>
       </c>
       <c r="H41" t="n">
-        <v>93.8</v>
+        <v>2.6</v>
       </c>
       <c r="I41" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J41" t="n">
-        <v>-275.55</v>
+        <v>-307.58</v>
       </c>
       <c r="K41" t="n">
-        <v>-208.72</v>
+        <v>-103.63</v>
       </c>
       <c r="L41" t="n">
-        <v>345.68</v>
+        <v>324.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:26:36</t>
+          <t>09:27:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.63</v>
+        <v>4.14</v>
       </c>
       <c r="F42" t="n">
-        <v>12.14</v>
+        <v>10.67</v>
       </c>
       <c r="G42" t="n">
-        <v>358.3</v>
+        <v>326.6</v>
       </c>
       <c r="H42" t="n">
-        <v>43.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>167.42</v>
+        <v>-181.45</v>
       </c>
       <c r="K42" t="n">
-        <v>332.18</v>
+        <v>241.37</v>
       </c>
       <c r="L42" t="n">
-        <v>371.98</v>
+        <v>301.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:28:31</t>
+          <t>09:28:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.83</v>
+        <v>4.81</v>
       </c>
       <c r="F43" t="n">
-        <v>8.82</v>
+        <v>12.3</v>
       </c>
       <c r="G43" t="n">
-        <v>334.6</v>
+        <v>345.6</v>
       </c>
       <c r="H43" t="n">
-        <v>66.2</v>
+        <v>55.5</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>56.64</v>
+        <v>248.11</v>
       </c>
       <c r="K43" t="n">
-        <v>251.13</v>
+        <v>-297.19</v>
       </c>
       <c r="L43" t="n">
-        <v>257.44</v>
+        <v>387.14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:37:25</t>
+          <t>09:37:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="F44" t="n">
-        <v>12.24</v>
+        <v>9.99</v>
       </c>
       <c r="G44" t="n">
-        <v>335</v>
+        <v>331.2</v>
       </c>
       <c r="H44" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>6.34</v>
+        <v>-55.93</v>
       </c>
       <c r="K44" t="n">
-        <v>59.46</v>
+        <v>32.18</v>
       </c>
       <c r="L44" t="n">
-        <v>59.79</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:39:57</t>
+          <t>09:38:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.26</v>
+        <v>4.39</v>
       </c>
       <c r="F45" t="n">
-        <v>11.11</v>
+        <v>12.3</v>
       </c>
       <c r="G45" t="n">
-        <v>351.6</v>
+        <v>332.6</v>
       </c>
       <c r="H45" t="n">
-        <v>59.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.2</v>
+        <v>-93.14</v>
       </c>
       <c r="K45" t="n">
-        <v>-72.28</v>
+        <v>10.14</v>
       </c>
       <c r="L45" t="n">
-        <v>83.19</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:41:41</t>
+          <t>09:40:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="F46" t="n">
-        <v>11.64</v>
+        <v>12.26</v>
       </c>
       <c r="G46" t="n">
-        <v>331.4</v>
+        <v>326.3</v>
       </c>
       <c r="H46" t="n">
-        <v>58.5</v>
+        <v>67.5</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.38</v>
+        <v>-83.89</v>
       </c>
       <c r="K46" t="n">
-        <v>78.73999999999999</v>
+        <v>34.99</v>
       </c>
       <c r="L46" t="n">
-        <v>79.87</v>
+        <v>90.89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:46:16</t>
+          <t>09:45:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.11</v>
+        <v>5.05</v>
       </c>
       <c r="F47" t="n">
-        <v>8.41</v>
+        <v>12.3</v>
       </c>
       <c r="G47" t="n">
-        <v>346.9</v>
+        <v>342.2</v>
       </c>
       <c r="H47" t="n">
-        <v>57.1</v>
+        <v>36.8</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>-100.33</v>
+        <v>67.12</v>
       </c>
       <c r="K47" t="n">
-        <v>63.12</v>
+        <v>278.05</v>
       </c>
       <c r="L47" t="n">
-        <v>118.53</v>
+        <v>286.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:48:10</t>
+          <t>09:46:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F48" t="n">
-        <v>10.97</v>
+        <v>10.35</v>
       </c>
       <c r="G48" t="n">
-        <v>341.3</v>
+        <v>358.2</v>
       </c>
       <c r="H48" t="n">
-        <v>40.5</v>
+        <v>57.7</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-43.28</v>
+        <v>95.8</v>
       </c>
       <c r="K48" t="n">
-        <v>111.15</v>
+        <v>-15.75</v>
       </c>
       <c r="L48" t="n">
-        <v>119.28</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:49:36</t>
+          <t>09:47:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.48</v>
+        <v>3.89</v>
       </c>
       <c r="F49" t="n">
-        <v>12.03</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>338.6</v>
+        <v>330.7</v>
       </c>
       <c r="H49" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>143.88</v>
+        <v>-110.57</v>
       </c>
       <c r="K49" t="n">
-        <v>72.98</v>
+        <v>16.48</v>
       </c>
       <c r="L49" t="n">
-        <v>161.32</v>
+        <v>111.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:53:50</t>
+          <t>09:52:37</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="F50" t="n">
-        <v>10.58</v>
+        <v>11.98</v>
       </c>
       <c r="G50" t="n">
-        <v>338</v>
+        <v>344.8</v>
       </c>
       <c r="H50" t="n">
-        <v>45.8</v>
+        <v>67.3</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J50" t="n">
-        <v>-16.53</v>
+        <v>55.56</v>
       </c>
       <c r="K50" t="n">
-        <v>162.55</v>
+        <v>-160.69</v>
       </c>
       <c r="L50" t="n">
-        <v>163.38</v>
+        <v>170.02</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:56:09</t>
+          <t>09:53:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.35</v>
+        <v>4.53</v>
       </c>
       <c r="F51" t="n">
-        <v>10.86</v>
+        <v>10.84</v>
       </c>
       <c r="G51" t="n">
-        <v>341.2</v>
+        <v>340.6</v>
       </c>
       <c r="H51" t="n">
-        <v>51.7</v>
+        <v>44.7</v>
       </c>
       <c r="I51" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>70.06999999999999</v>
+        <v>-27.89</v>
       </c>
       <c r="K51" t="n">
-        <v>-152.47</v>
+        <v>-156.84</v>
       </c>
       <c r="L51" t="n">
-        <v>167.8</v>
+        <v>159.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:58:03</t>
+          <t>09:54:48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.7</v>
+        <v>4.29</v>
       </c>
       <c r="F52" t="n">
         <v>12.3</v>
       </c>
       <c r="G52" t="n">
-        <v>337.2</v>
+        <v>341.9</v>
       </c>
       <c r="H52" t="n">
-        <v>60.8</v>
+        <v>64.3</v>
       </c>
       <c r="I52" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>140.98</v>
+        <v>170.5</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.25</v>
+        <v>49.71</v>
       </c>
       <c r="L52" t="n">
-        <v>141.7</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:03:29</t>
+          <t>10:00:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.94</v>
+        <v>4.49</v>
       </c>
       <c r="F53" t="n">
-        <v>11.69</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>338.8</v>
+        <v>337.7</v>
       </c>
       <c r="H53" t="n">
-        <v>90.90000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="I53" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>-121.36</v>
+        <v>-238.93</v>
       </c>
       <c r="K53" t="n">
-        <v>53.87</v>
+        <v>57.28</v>
       </c>
       <c r="L53" t="n">
-        <v>132.78</v>
+        <v>245.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:05:29</t>
+          <t>10:02:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.64</v>
+        <v>4.39</v>
       </c>
       <c r="F54" t="n">
-        <v>11.72</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>346.9</v>
+        <v>338.6</v>
       </c>
       <c r="H54" t="n">
-        <v>59.3</v>
+        <v>6.3</v>
       </c>
       <c r="I54" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-102.55</v>
+        <v>-248.17</v>
       </c>
       <c r="K54" t="n">
-        <v>-285.6</v>
+        <v>175.81</v>
       </c>
       <c r="L54" t="n">
-        <v>303.45</v>
+        <v>304.14</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:07:14</t>
+          <t>10:04:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.08</v>
+        <v>4.51</v>
       </c>
       <c r="F55" t="n">
-        <v>12.14</v>
+        <v>12.3</v>
       </c>
       <c r="G55" t="n">
-        <v>345.3</v>
+        <v>334.1</v>
       </c>
       <c r="H55" t="n">
-        <v>63.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-158.48</v>
+        <v>178.85</v>
       </c>
       <c r="K55" t="n">
-        <v>151.63</v>
+        <v>253.37</v>
       </c>
       <c r="L55" t="n">
-        <v>219.33</v>
+        <v>310.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:11:24</t>
+          <t>10:08:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.57</v>
+        <v>4.08</v>
       </c>
       <c r="F56" t="n">
-        <v>11.91</v>
+        <v>10.64</v>
       </c>
       <c r="G56" t="n">
-        <v>338.4</v>
+        <v>342</v>
       </c>
       <c r="H56" t="n">
-        <v>40.1</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>-51.77</v>
+        <v>201.64</v>
       </c>
       <c r="K56" t="n">
-        <v>346.27</v>
+        <v>-272.9</v>
       </c>
       <c r="L56" t="n">
-        <v>350.12</v>
+        <v>339.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:12:26</t>
+          <t>10:10:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.96</v>
+        <v>4.12</v>
       </c>
       <c r="F57" t="n">
-        <v>12.3</v>
+        <v>9.68</v>
       </c>
       <c r="G57" t="n">
-        <v>336.7</v>
+        <v>341.5</v>
       </c>
       <c r="H57" t="n">
-        <v>82.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="I57" t="n">
         <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>83.15000000000001</v>
+        <v>-293.43</v>
       </c>
       <c r="K57" t="n">
-        <v>-429.99</v>
+        <v>144.7</v>
       </c>
       <c r="L57" t="n">
-        <v>437.96</v>
+        <v>327.17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:13:57</t>
+          <t>10:12:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.39</v>
+        <v>4.98</v>
       </c>
       <c r="F58" t="n">
-        <v>10.59</v>
+        <v>12.3</v>
       </c>
       <c r="G58" t="n">
-        <v>342.2</v>
+        <v>344.6</v>
       </c>
       <c r="H58" t="n">
-        <v>47.9</v>
+        <v>33.5</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>-267.66</v>
+        <v>-447.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-188.9</v>
+        <v>58.76</v>
       </c>
       <c r="L58" t="n">
-        <v>327.61</v>
+        <v>451.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:25:34</t>
+          <t>10:24:32</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.18</v>
+        <v>4.55</v>
       </c>
       <c r="F59" t="n">
-        <v>10.31</v>
+        <v>10.89</v>
       </c>
       <c r="G59" t="n">
-        <v>333.9</v>
+        <v>337.5</v>
       </c>
       <c r="H59" t="n">
-        <v>58.3</v>
+        <v>37.5</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J59" t="n">
-        <v>30.02</v>
+        <v>11.88</v>
       </c>
       <c r="K59" t="n">
-        <v>87.63</v>
+        <v>-120.35</v>
       </c>
       <c r="L59" t="n">
-        <v>92.63</v>
+        <v>120.93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:27:35</t>
+          <t>10:26:52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.13</v>
+        <v>4.89</v>
       </c>
       <c r="F60" t="n">
         <v>12.3</v>
       </c>
       <c r="G60" t="n">
-        <v>323.9</v>
+        <v>344.7</v>
       </c>
       <c r="H60" t="n">
-        <v>76.5</v>
+        <v>65.3</v>
       </c>
       <c r="I60" t="n">
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.85</v>
+        <v>-110.3</v>
       </c>
       <c r="K60" t="n">
-        <v>-76.45999999999999</v>
+        <v>-33.54</v>
       </c>
       <c r="L60" t="n">
-        <v>82.08</v>
+        <v>115.29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:29:07</t>
+          <t>10:29:03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.37</v>
+        <v>4.86</v>
       </c>
       <c r="F61" t="n">
         <v>12.3</v>
       </c>
       <c r="G61" t="n">
-        <v>350.3</v>
+        <v>333.3</v>
       </c>
       <c r="H61" t="n">
-        <v>33.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>-70.86</v>
+        <v>-132.86</v>
       </c>
       <c r="K61" t="n">
-        <v>63.62</v>
+        <v>135.69</v>
       </c>
       <c r="L61" t="n">
-        <v>95.23</v>
+        <v>189.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:33:55</t>
+          <t>10:33:26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.69</v>
+        <v>4.43</v>
       </c>
       <c r="F62" t="n">
-        <v>12.3</v>
+        <v>11.94</v>
       </c>
       <c r="G62" t="n">
-        <v>336.7</v>
+        <v>329.6</v>
       </c>
       <c r="H62" t="n">
-        <v>16.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-71.54000000000001</v>
+        <v>-42.83</v>
       </c>
       <c r="K62" t="n">
-        <v>111.03</v>
+        <v>87.45</v>
       </c>
       <c r="L62" t="n">
-        <v>132.08</v>
+        <v>97.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:35:17</t>
+          <t>10:34:23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.58</v>
+        <v>4.78</v>
       </c>
       <c r="F63" t="n">
-        <v>12.3</v>
+        <v>11.79</v>
       </c>
       <c r="G63" t="n">
-        <v>338.4</v>
+        <v>334.5</v>
       </c>
       <c r="H63" t="n">
-        <v>60.2</v>
+        <v>49.1</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-115.47</v>
+        <v>20.98</v>
       </c>
       <c r="K63" t="n">
-        <v>42.22</v>
+        <v>193.26</v>
       </c>
       <c r="L63" t="n">
-        <v>122.95</v>
+        <v>194.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:37:10</t>
+          <t>10:36:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.52</v>
+        <v>4.77</v>
       </c>
       <c r="F64" t="n">
         <v>12.3</v>
       </c>
       <c r="G64" t="n">
-        <v>339.5</v>
+        <v>333.7</v>
       </c>
       <c r="H64" t="n">
-        <v>43.4</v>
+        <v>61.8</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>-122.48</v>
+        <v>-152.69</v>
       </c>
       <c r="K64" t="n">
-        <v>33.2</v>
+        <v>-34.66</v>
       </c>
       <c r="L64" t="n">
-        <v>126.9</v>
+        <v>156.58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:40:54</t>
+          <t>10:42:01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.04</v>
+        <v>4.26</v>
       </c>
       <c r="F65" t="n">
-        <v>12.3</v>
+        <v>12.16</v>
       </c>
       <c r="G65" t="n">
-        <v>325.3</v>
+        <v>346.1</v>
       </c>
       <c r="H65" t="n">
-        <v>49.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>47.84</v>
+        <v>78.97</v>
       </c>
       <c r="K65" t="n">
-        <v>192.36</v>
+        <v>129.96</v>
       </c>
       <c r="L65" t="n">
-        <v>198.21</v>
+        <v>152.07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:42:22</t>
+          <t>10:42:59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.55</v>
+        <v>4.64</v>
       </c>
       <c r="F66" t="n">
-        <v>12.3</v>
+        <v>11.81</v>
       </c>
       <c r="G66" t="n">
-        <v>326.8</v>
+        <v>338.8</v>
       </c>
       <c r="H66" t="n">
-        <v>15.9</v>
+        <v>31.6</v>
       </c>
       <c r="I66" t="n">
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-177.71</v>
+        <v>205.02</v>
       </c>
       <c r="K66" t="n">
-        <v>3.2</v>
+        <v>-35.99</v>
       </c>
       <c r="L66" t="n">
-        <v>177.74</v>
+        <v>208.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:44:16</t>
+          <t>10:45:17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.36</v>
+        <v>4.75</v>
       </c>
       <c r="F67" t="n">
-        <v>10.93</v>
+        <v>11.15</v>
       </c>
       <c r="G67" t="n">
-        <v>343.9</v>
+        <v>336.2</v>
       </c>
       <c r="H67" t="n">
-        <v>41</v>
+        <v>48.2</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-99.20999999999999</v>
+        <v>-127.63</v>
       </c>
       <c r="K67" t="n">
-        <v>-157.08</v>
+        <v>150.89</v>
       </c>
       <c r="L67" t="n">
-        <v>185.79</v>
+        <v>197.62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:48:06</t>
+          <t>10:49:21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="F68" t="n">
-        <v>10.95</v>
+        <v>12.23</v>
       </c>
       <c r="G68" t="n">
-        <v>348.4</v>
+        <v>335.1</v>
       </c>
       <c r="H68" t="n">
-        <v>40.6</v>
+        <v>69.3</v>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-72.92</v>
+        <v>-0.3</v>
       </c>
       <c r="K68" t="n">
-        <v>283.94</v>
+        <v>300.87</v>
       </c>
       <c r="L68" t="n">
-        <v>293.15</v>
+        <v>300.87</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:49:45</t>
+          <t>10:50:28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
       <c r="F69" t="n">
-        <v>11.15</v>
+        <v>12.3</v>
       </c>
       <c r="G69" t="n">
-        <v>336.5</v>
+        <v>340.1</v>
       </c>
       <c r="H69" t="n">
-        <v>30.5</v>
+        <v>33.9</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>241.53</v>
+        <v>-59.23</v>
       </c>
       <c r="K69" t="n">
-        <v>-176.24</v>
+        <v>-270.01</v>
       </c>
       <c r="L69" t="n">
-        <v>298.99</v>
+        <v>276.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:52:22</t>
+          <t>10:51:38</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="F70" t="n">
-        <v>11.78</v>
+        <v>12.3</v>
       </c>
       <c r="G70" t="n">
-        <v>344.3</v>
+        <v>341.9</v>
       </c>
       <c r="H70" t="n">
-        <v>25.4</v>
+        <v>49.2</v>
       </c>
       <c r="I70" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-150.27</v>
+        <v>-286.88</v>
       </c>
       <c r="K70" t="n">
-        <v>-248.94</v>
+        <v>142.48</v>
       </c>
       <c r="L70" t="n">
-        <v>290.77</v>
+        <v>320.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:57:16</t>
+          <t>10:55:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
       <c r="F71" t="n">
-        <v>12.3</v>
+        <v>9.42</v>
       </c>
       <c r="G71" t="n">
-        <v>311.7</v>
+        <v>335.9</v>
       </c>
       <c r="H71" t="n">
-        <v>73.2</v>
+        <v>84.5</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J71" t="n">
-        <v>84.45999999999999</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>316.11</v>
+        <v>-371.34</v>
       </c>
       <c r="L71" t="n">
-        <v>327.2</v>
+        <v>377.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:58:20</t>
+          <t>10:57:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.44</v>
+        <v>3.95</v>
       </c>
       <c r="F72" t="n">
-        <v>12.3</v>
+        <v>10.04</v>
       </c>
       <c r="G72" t="n">
-        <v>336.6</v>
+        <v>350.5</v>
       </c>
       <c r="H72" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-328.72</v>
+        <v>-260.48</v>
       </c>
       <c r="K72" t="n">
-        <v>-55.51</v>
+        <v>208.71</v>
       </c>
       <c r="L72" t="n">
-        <v>333.37</v>
+        <v>333.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:59:08</t>
+          <t>10:59:33</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="F73" t="n">
         <v>12.3</v>
       </c>
       <c r="G73" t="n">
-        <v>340.5</v>
+        <v>341.5</v>
       </c>
       <c r="H73" t="n">
-        <v>56.2</v>
+        <v>61</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>-189.85</v>
+        <v>421.09</v>
       </c>
       <c r="K73" t="n">
-        <v>271.13</v>
+        <v>-142.51</v>
       </c>
       <c r="L73" t="n">
-        <v>330.99</v>
+        <v>444.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:09:24</t>
+          <t>11:09:27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.98</v>
+        <v>4.43</v>
       </c>
       <c r="F74" t="n">
-        <v>11.37</v>
+        <v>12.06</v>
       </c>
       <c r="G74" t="n">
-        <v>329.8</v>
+        <v>330.5</v>
       </c>
       <c r="H74" t="n">
-        <v>55.1</v>
+        <v>66.7</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-133.46</v>
+        <v>-44.32</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.2</v>
+        <v>113.3</v>
       </c>
       <c r="L74" t="n">
-        <v>133.5</v>
+        <v>121.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:10:18</t>
+          <t>11:11:38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.2</v>
+        <v>4.46</v>
       </c>
       <c r="F75" t="n">
-        <v>10.85</v>
+        <v>12.3</v>
       </c>
       <c r="G75" t="n">
-        <v>339.4</v>
+        <v>334.4</v>
       </c>
       <c r="H75" t="n">
-        <v>50.4</v>
+        <v>33.4</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>-21.8</v>
+        <v>55.39</v>
       </c>
       <c r="K75" t="n">
-        <v>51.08</v>
+        <v>-68.98</v>
       </c>
       <c r="L75" t="n">
-        <v>55.54</v>
+        <v>88.45999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:11:41</t>
+          <t>11:14:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.75</v>
+        <v>4.86</v>
       </c>
       <c r="F76" t="n">
         <v>12.3</v>
       </c>
       <c r="G76" t="n">
-        <v>340.8</v>
+        <v>345.8</v>
       </c>
       <c r="H76" t="n">
-        <v>74.90000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.18</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>52.19</v>
+        <v>-51.4</v>
       </c>
       <c r="L76" t="n">
-        <v>75.95</v>
+        <v>109.39</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:16:01</t>
+          <t>11:18:20</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="F77" t="n">
         <v>12.3</v>
       </c>
       <c r="G77" t="n">
-        <v>349.3</v>
+        <v>336.4</v>
       </c>
       <c r="H77" t="n">
-        <v>73.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>7.11</v>
+        <v>-56.91</v>
       </c>
       <c r="K77" t="n">
-        <v>153.09</v>
+        <v>150.68</v>
       </c>
       <c r="L77" t="n">
-        <v>153.25</v>
+        <v>161.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:17:07</t>
+          <t>11:19:22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="F78" t="n">
-        <v>12.02</v>
+        <v>12.09</v>
       </c>
       <c r="G78" t="n">
-        <v>347.9</v>
+        <v>349.9</v>
       </c>
       <c r="H78" t="n">
-        <v>64.2</v>
+        <v>52.6</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>73.28</v>
+        <v>114.52</v>
       </c>
       <c r="K78" t="n">
-        <v>109.9</v>
+        <v>-70.69</v>
       </c>
       <c r="L78" t="n">
-        <v>132.09</v>
+        <v>134.58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:17:43</t>
+          <t>11:20:51</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.67</v>
+        <v>4.49</v>
       </c>
       <c r="F79" t="n">
         <v>12.3</v>
       </c>
       <c r="G79" t="n">
-        <v>337.5</v>
+        <v>340.6</v>
       </c>
       <c r="H79" t="n">
-        <v>79.09999999999999</v>
+        <v>54</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>44.68</v>
+        <v>-138.95</v>
       </c>
       <c r="K79" t="n">
-        <v>-168.96</v>
+        <v>2.43</v>
       </c>
       <c r="L79" t="n">
-        <v>174.77</v>
+        <v>138.97</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:21:39</t>
+          <t>11:23:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.41</v>
+        <v>4.16</v>
       </c>
       <c r="F80" t="n">
         <v>12.3</v>
       </c>
       <c r="G80" t="n">
-        <v>348</v>
+        <v>339.8</v>
       </c>
       <c r="H80" t="n">
-        <v>67.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-188.35</v>
+        <v>-142.77</v>
       </c>
       <c r="K80" t="n">
-        <v>275.61</v>
+        <v>39.94</v>
       </c>
       <c r="L80" t="n">
-        <v>333.82</v>
+        <v>148.26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:23:38</t>
+          <t>11:26:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="F81" t="n">
         <v>12.3</v>
       </c>
       <c r="G81" t="n">
-        <v>340.4</v>
+        <v>333.3</v>
       </c>
       <c r="H81" t="n">
-        <v>50.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>148.04</v>
+        <v>43.67</v>
       </c>
       <c r="K81" t="n">
-        <v>47.29</v>
+        <v>160.47</v>
       </c>
       <c r="L81" t="n">
-        <v>155.41</v>
+        <v>166.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:25:12</t>
+          <t>11:27:04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.29</v>
+        <v>4.83</v>
       </c>
       <c r="F82" t="n">
-        <v>11.38</v>
+        <v>12.3</v>
       </c>
       <c r="G82" t="n">
-        <v>323.6</v>
+        <v>350.6</v>
       </c>
       <c r="H82" t="n">
-        <v>83.09999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="I82" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>58.7</v>
+        <v>-128.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-177.78</v>
+        <v>139.59</v>
       </c>
       <c r="L82" t="n">
-        <v>187.22</v>
+        <v>189.61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:30:04</t>
+          <t>11:32:38</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3529,28 +3529,28 @@
         <v>12.3</v>
       </c>
       <c r="G83" t="n">
-        <v>342.3</v>
+        <v>339.7</v>
       </c>
       <c r="H83" t="n">
-        <v>29.4</v>
+        <v>77.2</v>
       </c>
       <c r="I83" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>-281.19</v>
+        <v>277.58</v>
       </c>
       <c r="K83" t="n">
-        <v>103.51</v>
+        <v>-182.77</v>
       </c>
       <c r="L83" t="n">
-        <v>299.64</v>
+        <v>332.35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:31:13</t>
+          <t>11:34:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.67</v>
+        <v>4.78</v>
       </c>
       <c r="F84" t="n">
         <v>12.3</v>
       </c>
       <c r="G84" t="n">
-        <v>345.5</v>
+        <v>340.2</v>
       </c>
       <c r="H84" t="n">
-        <v>53.7</v>
+        <v>85.7</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>44.03</v>
+        <v>-17.17</v>
       </c>
       <c r="K84" t="n">
-        <v>254.18</v>
+        <v>365.68</v>
       </c>
       <c r="L84" t="n">
-        <v>257.96</v>
+        <v>366.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:32:34</t>
+          <t>11:36:10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.18</v>
+        <v>4.73</v>
       </c>
       <c r="F85" t="n">
-        <v>9.58</v>
+        <v>12.3</v>
       </c>
       <c r="G85" t="n">
-        <v>345</v>
+        <v>338.4</v>
       </c>
       <c r="H85" t="n">
-        <v>50.9</v>
+        <v>10.2</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-225.76</v>
+        <v>-301.17</v>
       </c>
       <c r="K85" t="n">
-        <v>160.06</v>
+        <v>54.72</v>
       </c>
       <c r="L85" t="n">
-        <v>276.74</v>
+        <v>306.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:36:51</t>
+          <t>11:41:23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.38</v>
+        <v>5.31</v>
       </c>
       <c r="F86" t="n">
         <v>12.3</v>
       </c>
       <c r="G86" t="n">
-        <v>339.6</v>
+        <v>339.7</v>
       </c>
       <c r="H86" t="n">
-        <v>88</v>
+        <v>72.7</v>
       </c>
       <c r="I86" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-260.25</v>
+        <v>-363.06</v>
       </c>
       <c r="K86" t="n">
-        <v>386.53</v>
+        <v>-338.28</v>
       </c>
       <c r="L86" t="n">
-        <v>465.98</v>
+        <v>496.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:37:35</t>
+          <t>11:43:03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.87</v>
+        <v>4.69</v>
       </c>
       <c r="F87" t="n">
         <v>12.3</v>
       </c>
       <c r="G87" t="n">
-        <v>348.1</v>
+        <v>342</v>
       </c>
       <c r="H87" t="n">
-        <v>45.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-354.2</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>19.77</v>
+        <v>294.35</v>
       </c>
       <c r="L87" t="n">
-        <v>354.75</v>
+        <v>308.64</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:38:38</t>
+          <t>11:45:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.73</v>
+        <v>4.18</v>
       </c>
       <c r="F88" t="n">
-        <v>12.15</v>
+        <v>12.3</v>
       </c>
       <c r="G88" t="n">
-        <v>331.4</v>
+        <v>331</v>
       </c>
       <c r="H88" t="n">
-        <v>71.59999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-362.1</v>
+        <v>289.53</v>
       </c>
       <c r="K88" t="n">
-        <v>337.45</v>
+        <v>-166.29</v>
       </c>
       <c r="L88" t="n">
-        <v>494.96</v>
+        <v>333.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-76.19</v>
+        <v>-79.76000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>32.31</v>
+        <v>33.82</v>
       </c>
       <c r="L14" t="n">
-        <v>82.76000000000001</v>
+        <v>86.64</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-78.76000000000001</v>
+        <v>-85.55</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.98</v>
+        <v>-22.79</v>
       </c>
       <c r="L15" t="n">
-        <v>81.5</v>
+        <v>88.54000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>34.84</v>
+        <v>42.26</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.98</v>
+        <v>-49.72</v>
       </c>
       <c r="L16" t="n">
-        <v>53.79</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>90.79000000000001</v>
+        <v>100.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-43.18</v>
+        <v>-47.81</v>
       </c>
       <c r="L17" t="n">
-        <v>100.54</v>
+        <v>111.32</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>92.2</v>
+        <v>94.95</v>
       </c>
       <c r="K18" t="n">
-        <v>74.23</v>
+        <v>76.45</v>
       </c>
       <c r="L18" t="n">
-        <v>118.37</v>
+        <v>121.9</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>36.09</v>
+        <v>39.16</v>
       </c>
       <c r="K19" t="n">
-        <v>91.61</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>98.47</v>
+        <v>106.84</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>11.49</v>
+        <v>13.69</v>
       </c>
       <c r="K20" t="n">
-        <v>96.31</v>
+        <v>114.74</v>
       </c>
       <c r="L20" t="n">
-        <v>97</v>
+        <v>115.55</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>125.04</v>
+        <v>145.85</v>
       </c>
       <c r="K21" t="n">
-        <v>33.14</v>
+        <v>38.66</v>
       </c>
       <c r="L21" t="n">
-        <v>129.36</v>
+        <v>150.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>46.37</v>
+        <v>55.61</v>
       </c>
       <c r="K22" t="n">
-        <v>97.55</v>
+        <v>116.97</v>
       </c>
       <c r="L22" t="n">
-        <v>108.01</v>
+        <v>129.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-161.62</v>
+        <v>-188.38</v>
       </c>
       <c r="K23" t="n">
-        <v>96.13</v>
+        <v>112.04</v>
       </c>
       <c r="L23" t="n">
-        <v>188.05</v>
+        <v>219.18</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-164.47</v>
+        <v>-192.88</v>
       </c>
       <c r="K24" t="n">
-        <v>-45.73</v>
+        <v>-53.63</v>
       </c>
       <c r="L24" t="n">
-        <v>170.71</v>
+        <v>200.2</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-152.43</v>
+        <v>-185.25</v>
       </c>
       <c r="K25" t="n">
-        <v>19.13</v>
+        <v>23.24</v>
       </c>
       <c r="L25" t="n">
-        <v>153.62</v>
+        <v>186.7</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>175.03</v>
+        <v>221.59</v>
       </c>
       <c r="K26" t="n">
-        <v>211.11</v>
+        <v>267.26</v>
       </c>
       <c r="L26" t="n">
-        <v>274.23</v>
+        <v>347.18</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-183.06</v>
+        <v>-244.89</v>
       </c>
       <c r="K27" t="n">
-        <v>64.28</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>194.02</v>
+        <v>259.55</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="n">
-        <v>-13.67</v>
+        <v>-17.38</v>
       </c>
       <c r="K28" t="n">
-        <v>211.22</v>
+        <v>268.58</v>
       </c>
       <c r="L28" t="n">
-        <v>211.66</v>
+        <v>269.14</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>39.04</v>
+        <v>46.24</v>
       </c>
       <c r="K29" t="n">
-        <v>-37.44</v>
+        <v>-44.35</v>
       </c>
       <c r="L29" t="n">
-        <v>54.09</v>
+        <v>64.06999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.04</v>
+        <v>-3.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-77.69</v>
+        <v>-84.98</v>
       </c>
       <c r="L30" t="n">
-        <v>77.75</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>78.79000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.16</v>
+        <v>-28.02</v>
       </c>
       <c r="L31" t="n">
-        <v>83.34</v>
+        <v>85.98999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.23</v>
+        <v>-4.7</v>
       </c>
       <c r="K32" t="n">
-        <v>-87.81999999999999</v>
+        <v>-97.72</v>
       </c>
       <c r="L32" t="n">
-        <v>87.92</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-21.09</v>
+        <v>-25.43</v>
       </c>
       <c r="K33" t="n">
-        <v>61.99</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>65.48</v>
+        <v>78.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>68.75</v>
+        <v>78.06</v>
       </c>
       <c r="K34" t="n">
-        <v>-31.25</v>
+        <v>-35.48</v>
       </c>
       <c r="L34" t="n">
-        <v>75.52</v>
+        <v>85.75</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-44.8</v>
+        <v>-51.69</v>
       </c>
       <c r="K35" t="n">
-        <v>-126.82</v>
+        <v>-146.31</v>
       </c>
       <c r="L35" t="n">
-        <v>134.51</v>
+        <v>155.18</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>-127.38</v>
+        <v>-149.84</v>
       </c>
       <c r="K36" t="n">
-        <v>39.16</v>
+        <v>46.06</v>
       </c>
       <c r="L36" t="n">
-        <v>133.27</v>
+        <v>156.75</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-60.19</v>
+        <v>-71.42</v>
       </c>
       <c r="K37" t="n">
-        <v>108.34</v>
+        <v>128.54</v>
       </c>
       <c r="L37" t="n">
-        <v>123.93</v>
+        <v>147.05</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-46.09</v>
+        <v>-60.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-100.98</v>
+        <v>-131.9</v>
       </c>
       <c r="L38" t="n">
-        <v>111</v>
+        <v>144.99</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-104.65</v>
+        <v>-139.34</v>
       </c>
       <c r="K39" t="n">
-        <v>-43.06</v>
+        <v>-57.33</v>
       </c>
       <c r="L39" t="n">
-        <v>113.16</v>
+        <v>150.67</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-120.31</v>
+        <v>-154.34</v>
       </c>
       <c r="K40" t="n">
-        <v>131.96</v>
+        <v>169.29</v>
       </c>
       <c r="L40" t="n">
-        <v>178.57</v>
+        <v>229.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>75.03</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>322.16</v>
+        <v>428.5</v>
       </c>
       <c r="L41" t="n">
-        <v>330.78</v>
+        <v>439.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-199.06</v>
+        <v>-243.99</v>
       </c>
       <c r="K42" t="n">
-        <v>157.22</v>
+        <v>192.71</v>
       </c>
       <c r="L42" t="n">
-        <v>253.66</v>
+        <v>310.92</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>325.11</v>
+        <v>388.85</v>
       </c>
       <c r="K43" t="n">
-        <v>48.44</v>
+        <v>57.94</v>
       </c>
       <c r="L43" t="n">
-        <v>328.7</v>
+        <v>393.14</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>20.58</v>
+        <v>22.35</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.18000000000001</v>
+        <v>-79.5</v>
       </c>
       <c r="L44" t="n">
-        <v>76.02</v>
+        <v>82.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-41.05</v>
+        <v>-46.87</v>
       </c>
       <c r="K45" t="n">
-        <v>51.55</v>
+        <v>58.87</v>
       </c>
       <c r="L45" t="n">
-        <v>65.90000000000001</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-24.99</v>
+        <v>-29.71</v>
       </c>
       <c r="K46" t="n">
-        <v>50.65</v>
+        <v>60.23</v>
       </c>
       <c r="L46" t="n">
-        <v>56.47</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="K47" t="n">
-        <v>-87.43000000000001</v>
+        <v>-98.75</v>
       </c>
       <c r="L47" t="n">
-        <v>87.5</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-8.09</v>
+        <v>-9.49</v>
       </c>
       <c r="K48" t="n">
-        <v>72.23999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="L48" t="n">
-        <v>72.69</v>
+        <v>85.26000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>89.87</v>
+        <v>99.38</v>
       </c>
       <c r="K49" t="n">
-        <v>12.36</v>
+        <v>13.67</v>
       </c>
       <c r="L49" t="n">
-        <v>90.72</v>
+        <v>100.31</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>154.76</v>
+        <v>178.74</v>
       </c>
       <c r="K50" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="L50" t="n">
-        <v>154.76</v>
+        <v>178.74</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-61.97</v>
+        <v>-74.16</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.1</v>
+        <v>-140.14</v>
       </c>
       <c r="L51" t="n">
-        <v>132.49</v>
+        <v>158.55</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>144.97</v>
+        <v>164.39</v>
       </c>
       <c r="K52" t="n">
-        <v>-44.26</v>
+        <v>-50.18</v>
       </c>
       <c r="L52" t="n">
-        <v>151.57</v>
+        <v>171.88</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>207.05</v>
+        <v>256.85</v>
       </c>
       <c r="K53" t="n">
-        <v>-27.1</v>
+        <v>-33.61</v>
       </c>
       <c r="L53" t="n">
-        <v>208.82</v>
+        <v>259.04</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-173.92</v>
+        <v>-218.38</v>
       </c>
       <c r="K54" t="n">
-        <v>9.210000000000001</v>
+        <v>11.57</v>
       </c>
       <c r="L54" t="n">
-        <v>174.16</v>
+        <v>218.68</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>113.43</v>
+        <v>146.54</v>
       </c>
       <c r="K55" t="n">
-        <v>-125.36</v>
+        <v>-161.96</v>
       </c>
       <c r="L55" t="n">
-        <v>169.06</v>
+        <v>218.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>98.26000000000001</v>
+        <v>122.53</v>
       </c>
       <c r="K56" t="n">
-        <v>337.76</v>
+        <v>421.21</v>
       </c>
       <c r="L56" t="n">
-        <v>351.76</v>
+        <v>438.67</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-43.68</v>
+        <v>-59.42</v>
       </c>
       <c r="K57" t="n">
-        <v>228.95</v>
+        <v>311.41</v>
       </c>
       <c r="L57" t="n">
-        <v>233.08</v>
+        <v>317.03</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>324.2</v>
+        <v>387.66</v>
       </c>
       <c r="K58" t="n">
-        <v>-76.55</v>
+        <v>-91.53</v>
       </c>
       <c r="L58" t="n">
-        <v>333.12</v>
+        <v>398.32</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>43.68</v>
+        <v>47.06</v>
       </c>
       <c r="K59" t="n">
-        <v>63.8</v>
+        <v>68.75</v>
       </c>
       <c r="L59" t="n">
-        <v>77.31999999999999</v>
+        <v>83.31999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>37.2</v>
+        <v>40.61</v>
       </c>
       <c r="K60" t="n">
-        <v>57.23</v>
+        <v>62.48</v>
       </c>
       <c r="L60" t="n">
-        <v>68.26000000000001</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.28</v>
+        <v>-36.66</v>
       </c>
       <c r="K61" t="n">
-        <v>-72.68000000000001</v>
+        <v>-77.73999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>80.36</v>
+        <v>85.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>35.95</v>
+        <v>45.09</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.78</v>
+        <v>-16.03</v>
       </c>
       <c r="L62" t="n">
-        <v>38.16</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>68.13</v>
+        <v>77.95</v>
       </c>
       <c r="K63" t="n">
-        <v>31.08</v>
+        <v>35.56</v>
       </c>
       <c r="L63" t="n">
-        <v>74.88</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-73.58</v>
+        <v>-85.54000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>8.039999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="L64" t="n">
-        <v>74.01000000000001</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-82.59</v>
+        <v>-108.58</v>
       </c>
       <c r="K65" t="n">
-        <v>-67.59</v>
+        <v>-88.86</v>
       </c>
       <c r="L65" t="n">
-        <v>106.72</v>
+        <v>140.3</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>186.29</v>
+        <v>219.25</v>
       </c>
       <c r="K66" t="n">
-        <v>9.99</v>
+        <v>11.75</v>
       </c>
       <c r="L66" t="n">
-        <v>186.56</v>
+        <v>219.57</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-35.45</v>
+        <v>-42.96</v>
       </c>
       <c r="K67" t="n">
-        <v>103.25</v>
+        <v>125.13</v>
       </c>
       <c r="L67" t="n">
-        <v>109.17</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-143.41</v>
+        <v>-177.27</v>
       </c>
       <c r="K68" t="n">
-        <v>249.73</v>
+        <v>308.7</v>
       </c>
       <c r="L68" t="n">
-        <v>287.98</v>
+        <v>355.98</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>202.42</v>
+        <v>235.41</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.78</v>
+        <v>-3.23</v>
       </c>
       <c r="L69" t="n">
-        <v>202.44</v>
+        <v>235.43</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>224.48</v>
+        <v>273.99</v>
       </c>
       <c r="K70" t="n">
-        <v>-9.9</v>
+        <v>-12.08</v>
       </c>
       <c r="L70" t="n">
-        <v>224.7</v>
+        <v>274.25</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>41.96</v>
+        <v>55.62</v>
       </c>
       <c r="K71" t="n">
-        <v>221.31</v>
+        <v>293.35</v>
       </c>
       <c r="L71" t="n">
-        <v>225.25</v>
+        <v>298.57</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>109.78</v>
+        <v>155.72</v>
       </c>
       <c r="K72" t="n">
-        <v>202.1</v>
+        <v>286.67</v>
       </c>
       <c r="L72" t="n">
-        <v>229.99</v>
+        <v>326.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-12.96</v>
+        <v>-18.58</v>
       </c>
       <c r="K73" t="n">
-        <v>-194.09</v>
+        <v>-278.28</v>
       </c>
       <c r="L73" t="n">
-        <v>194.52</v>
+        <v>278.9</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-63.42</v>
+        <v>-70.90000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>11.22</v>
+        <v>12.54</v>
       </c>
       <c r="L74" t="n">
-        <v>64.41</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>66.62</v>
+        <v>73.22</v>
       </c>
       <c r="K75" t="n">
-        <v>34.48</v>
+        <v>37.89</v>
       </c>
       <c r="L75" t="n">
-        <v>75.01000000000001</v>
+        <v>82.45</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.1</v>
+        <v>-61.69</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.15</v>
+        <v>-50.55</v>
       </c>
       <c r="L76" t="n">
-        <v>71.23</v>
+        <v>79.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>67.45</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.61</v>
+        <v>-27.67</v>
       </c>
       <c r="L77" t="n">
-        <v>71.47</v>
+        <v>83.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-13.7</v>
+        <v>-16.39</v>
       </c>
       <c r="K78" t="n">
-        <v>-72.68000000000001</v>
+        <v>-86.97</v>
       </c>
       <c r="L78" t="n">
-        <v>73.95999999999999</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-15.31</v>
+        <v>-17.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-73.54000000000001</v>
+        <v>-86.11</v>
       </c>
       <c r="L79" t="n">
-        <v>75.12</v>
+        <v>87.95999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-130.03</v>
+        <v>-154.11</v>
       </c>
       <c r="K80" t="n">
-        <v>-5.97</v>
+        <v>-7.07</v>
       </c>
       <c r="L80" t="n">
-        <v>130.17</v>
+        <v>154.27</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-174.22</v>
+        <v>-202.95</v>
       </c>
       <c r="K81" t="n">
-        <v>-56.4</v>
+        <v>-65.7</v>
       </c>
       <c r="L81" t="n">
-        <v>183.12</v>
+        <v>213.32</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-86.76000000000001</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>145.4</v>
+        <v>166.88</v>
       </c>
       <c r="L82" t="n">
-        <v>169.32</v>
+        <v>194.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>80.98999999999999</v>
+        <v>104.49</v>
       </c>
       <c r="K83" t="n">
-        <v>172.5</v>
+        <v>222.56</v>
       </c>
       <c r="L83" t="n">
-        <v>190.57</v>
+        <v>245.87</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>67.58</v>
+        <v>87.39</v>
       </c>
       <c r="K84" t="n">
-        <v>174.51</v>
+        <v>225.66</v>
       </c>
       <c r="L84" t="n">
-        <v>187.14</v>
+        <v>241.99</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>70.06</v>
+        <v>84.83</v>
       </c>
       <c r="K85" t="n">
-        <v>218.4</v>
+        <v>264.44</v>
       </c>
       <c r="L85" t="n">
-        <v>229.37</v>
+        <v>277.71</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-132.8</v>
+        <v>-181.43</v>
       </c>
       <c r="K86" t="n">
-        <v>259.1</v>
+        <v>353.98</v>
       </c>
       <c r="L86" t="n">
-        <v>291.16</v>
+        <v>397.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>-191.62</v>
+        <v>-238.56</v>
       </c>
       <c r="K87" t="n">
-        <v>-107.61</v>
+        <v>-133.97</v>
       </c>
       <c r="L87" t="n">
-        <v>219.77</v>
+        <v>273.6</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>78.03</v>
+        <v>110.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-118.6</v>
+        <v>-167.7</v>
       </c>
       <c r="L88" t="n">
-        <v>141.96</v>
+        <v>200.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-25.xlsx
+++ b/output/2024-10-25.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-79.76000000000001</v>
+        <v>-98.17</v>
       </c>
       <c r="K14" t="n">
-        <v>33.82</v>
+        <v>41.62</v>
       </c>
       <c r="L14" t="n">
-        <v>86.64</v>
+        <v>106.63</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-85.55</v>
+        <v>-106.38</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.79</v>
+        <v>-28.33</v>
       </c>
       <c r="L15" t="n">
-        <v>88.54000000000001</v>
+        <v>110.08</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>42.26</v>
+        <v>53.2</v>
       </c>
       <c r="K16" t="n">
-        <v>-49.72</v>
+        <v>-62.58</v>
       </c>
       <c r="L16" t="n">
-        <v>65.25</v>
+        <v>82.14</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>100.53</v>
+        <v>122.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-47.81</v>
+        <v>-58.15</v>
       </c>
       <c r="L17" t="n">
-        <v>111.32</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>94.95</v>
+        <v>105.31</v>
       </c>
       <c r="K18" t="n">
-        <v>76.45</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>121.9</v>
+        <v>135.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>39.16</v>
+        <v>43.56</v>
       </c>
       <c r="K19" t="n">
-        <v>99.40000000000001</v>
+        <v>110.58</v>
       </c>
       <c r="L19" t="n">
-        <v>106.84</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>46.24</v>
+        <v>54.52</v>
       </c>
       <c r="K29" t="n">
-        <v>-44.35</v>
+        <v>-52.28</v>
       </c>
       <c r="L29" t="n">
-        <v>64.06999999999999</v>
+        <v>75.54000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.33</v>
+        <v>-4.27</v>
       </c>
       <c r="K30" t="n">
-        <v>-84.98</v>
+        <v>-109.17</v>
       </c>
       <c r="L30" t="n">
-        <v>85.05</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>81.29000000000001</v>
+        <v>94.28</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.02</v>
+        <v>-32.5</v>
       </c>
       <c r="L31" t="n">
-        <v>85.98999999999999</v>
+        <v>99.73</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.7</v>
+        <v>-5.56</v>
       </c>
       <c r="K32" t="n">
-        <v>-97.72</v>
+        <v>-115.6</v>
       </c>
       <c r="L32" t="n">
-        <v>97.84</v>
+        <v>115.74</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>-25.43</v>
+        <v>-31.55</v>
       </c>
       <c r="K33" t="n">
-        <v>74.73999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="L33" t="n">
-        <v>78.94</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>78.06</v>
+        <v>103.64</v>
       </c>
       <c r="K34" t="n">
-        <v>-35.48</v>
+        <v>-47.11</v>
       </c>
       <c r="L34" t="n">
-        <v>85.75</v>
+        <v>113.84</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>22.35</v>
+        <v>31.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-79.5</v>
+        <v>-113.06</v>
       </c>
       <c r="L44" t="n">
-        <v>82.58</v>
+        <v>117.45</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-46.87</v>
+        <v>-65.37</v>
       </c>
       <c r="K45" t="n">
-        <v>58.87</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>75.25</v>
+        <v>104.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.71</v>
+        <v>-36.65</v>
       </c>
       <c r="K46" t="n">
-        <v>60.23</v>
+        <v>74.27</v>
       </c>
       <c r="L46" t="n">
-        <v>67.16</v>
+        <v>82.81999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>3.76</v>
+        <v>4.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-98.75</v>
+        <v>-119</v>
       </c>
       <c r="L47" t="n">
-        <v>98.81999999999999</v>
+        <v>119.09</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.49</v>
+        <v>-11.13</v>
       </c>
       <c r="K48" t="n">
-        <v>84.73</v>
+        <v>99.3</v>
       </c>
       <c r="L48" t="n">
-        <v>85.26000000000001</v>
+        <v>99.92</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>99.38</v>
+        <v>123.71</v>
       </c>
       <c r="K49" t="n">
-        <v>13.67</v>
+        <v>17.02</v>
       </c>
       <c r="L49" t="n">
-        <v>100.31</v>
+        <v>124.88</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>47.06</v>
+        <v>61.57</v>
       </c>
       <c r="K59" t="n">
-        <v>68.75</v>
+        <v>89.94</v>
       </c>
       <c r="L59" t="n">
-        <v>83.31999999999999</v>
+        <v>108.99</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>40.61</v>
+        <v>49.48</v>
       </c>
       <c r="K60" t="n">
-        <v>62.48</v>
+        <v>76.11</v>
       </c>
       <c r="L60" t="n">
-        <v>74.52</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-36.66</v>
+        <v>-52.24</v>
       </c>
       <c r="K61" t="n">
-        <v>-77.73999999999999</v>
+        <v>-110.78</v>
       </c>
       <c r="L61" t="n">
-        <v>85.95</v>
+        <v>122.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>45.09</v>
+        <v>52.61</v>
       </c>
       <c r="K62" t="n">
-        <v>-16.03</v>
+        <v>-18.7</v>
       </c>
       <c r="L62" t="n">
-        <v>47.86</v>
+        <v>55.83</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>77.95</v>
+        <v>91.5</v>
       </c>
       <c r="K63" t="n">
-        <v>35.56</v>
+        <v>41.74</v>
       </c>
       <c r="L63" t="n">
-        <v>85.68000000000001</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-85.54000000000001</v>
+        <v>-105.51</v>
       </c>
       <c r="K64" t="n">
-        <v>9.35</v>
+        <v>11.53</v>
       </c>
       <c r="L64" t="n">
-        <v>86.05</v>
+        <v>106.14</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-70.90000000000001</v>
+        <v>-84.62</v>
       </c>
       <c r="K74" t="n">
-        <v>12.54</v>
+        <v>14.97</v>
       </c>
       <c r="L74" t="n">
-        <v>72</v>
+        <v>85.93000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>73.22</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>37.89</v>
+        <v>48.38</v>
       </c>
       <c r="L75" t="n">
-        <v>82.45</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-61.69</v>
+        <v>-85.86</v>
       </c>
       <c r="K76" t="n">
-        <v>-50.55</v>
+        <v>-70.36</v>
       </c>
       <c r="L76" t="n">
-        <v>79.76000000000001</v>
+        <v>111.01</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>79.06999999999999</v>
+        <v>104.18</v>
       </c>
       <c r="K77" t="n">
-        <v>-27.67</v>
+        <v>-36.46</v>
       </c>
       <c r="L77" t="n">
-        <v>83.77</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-16.39</v>
+        <v>-22.33</v>
       </c>
       <c r="K78" t="n">
-        <v>-86.97</v>
+        <v>-118.47</v>
       </c>
       <c r="L78" t="n">
-        <v>88.5</v>
+        <v>120.55</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-17.92</v>
+        <v>-20.37</v>
       </c>
       <c r="K79" t="n">
-        <v>-86.11</v>
+        <v>-97.87</v>
       </c>
       <c r="L79" t="n">
-        <v>87.95999999999999</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="80">
